--- a/web/flask/static/annual_report_template.xlsx
+++ b/web/flask/static/annual_report_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inpdenaterm01\climberdb\git\web\flask\static\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\apps\climberdb\git\web\flask\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF430706-FD80-4E5F-A559-4AC456459C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABE8CC8-E191-4D3A-8C80-1749A39B9F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28545" yWindow="-38400" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="8" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="326">
   <si>
     <t>Total</t>
   </si>
@@ -943,9 +943,6 @@
     <t xml:space="preserve">2024 Climbing Season - General Statistics                                                                            </t>
   </si>
   <si>
-    <t xml:space="preserve">2025 Climbing Season - General Statistics                                                                            </t>
-  </si>
-  <si>
     <t>3 or fewer climbers from each country</t>
   </si>
   <si>
@@ -985,9 +982,6 @@
     <t>WHO ARE THE NPS MOUNTAINEERING RANGERS?</t>
   </si>
   <si>
-    <t>WHAT ROUTES WERE CLIMBED IN 2025?</t>
-  </si>
-  <si>
     <t>Summit Rate</t>
   </si>
   <si>
@@ -1049,6 +1043,15 @@
   </si>
   <si>
     <t>{{denali_routes_table::include_header}}</t>
+  </si>
+  <si>
+    <t>{{foraker_routes_table::include_header}}</t>
+  </si>
+  <si>
+    <t>{{routes_climbed_title}}</t>
+  </si>
+  <si>
+    <t>{{report_title}}</t>
   </si>
 </sst>
 </file>
@@ -1719,7 +1722,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="348">
+  <cellXfs count="339">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2326,6 +2329,88 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2344,87 +2429,18 @@
     <xf numFmtId="0" fontId="19" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2443,6 +2459,39 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2461,39 +2510,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2506,6 +2522,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2521,41 +2540,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2851,36 +2835,36 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L58"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="24.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="54.42578125" customWidth="1"/>
-    <col min="2" max="5" width="12.85546875" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" style="202" customWidth="1"/>
+    <col min="1" max="1" width="54.453125" customWidth="1"/>
+    <col min="2" max="5" width="12.81640625" customWidth="1"/>
+    <col min="6" max="6" width="12.81640625" style="202" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="268" t="s">
-        <v>289</v>
-      </c>
-      <c r="B1" s="269"/>
-      <c r="C1" s="269"/>
-      <c r="D1" s="269"/>
-      <c r="E1" s="269"/>
-      <c r="F1" s="270"/>
-    </row>
-    <row r="2" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="271" t="s">
-        <v>291</v>
-      </c>
-      <c r="B2" s="272"/>
-      <c r="C2" s="272"/>
-      <c r="D2" s="272"/>
-      <c r="E2" s="272"/>
-      <c r="F2" s="273"/>
-    </row>
-    <row r="3" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="296" t="s">
+        <v>325</v>
+      </c>
+      <c r="B1" s="297"/>
+      <c r="C1" s="297"/>
+      <c r="D1" s="297"/>
+      <c r="E1" s="297"/>
+      <c r="F1" s="298"/>
+    </row>
+    <row r="2" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="299" t="s">
+        <v>290</v>
+      </c>
+      <c r="B2" s="300"/>
+      <c r="C2" s="300"/>
+      <c r="D2" s="300"/>
+      <c r="E2" s="300"/>
+      <c r="F2" s="301"/>
+    </row>
+    <row r="3" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="229" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B3" s="230"/>
       <c r="C3" s="231"/>
@@ -2888,7 +2872,7 @@
       <c r="E3" s="230"/>
       <c r="F3" s="232"/>
     </row>
-    <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="197"/>
       <c r="B4" s="258"/>
       <c r="C4" s="249"/>
@@ -2896,91 +2880,91 @@
       <c r="E4" s="258"/>
       <c r="F4" s="261"/>
     </row>
-    <row r="5" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="278"/>
-      <c r="B5" s="279"/>
-      <c r="C5" s="279"/>
+    <row r="5" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="287"/>
+      <c r="B5" s="288"/>
+      <c r="C5" s="288"/>
       <c r="D5" s="217"/>
       <c r="E5" s="218"/>
       <c r="F5" s="219"/>
     </row>
-    <row r="6" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="284" t="s">
+    <row r="6" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="285" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="285"/>
-      <c r="C6" s="285"/>
+      <c r="B6" s="286"/>
+      <c r="C6" s="286"/>
       <c r="D6" s="220"/>
       <c r="E6" s="221"/>
       <c r="F6" s="221"/>
     </row>
-    <row r="7" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="282" t="s">
+    <row r="7" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="283" t="s">
+        <v>291</v>
+      </c>
+      <c r="B7" s="284"/>
+      <c r="C7" s="284"/>
+      <c r="D7" s="277"/>
+      <c r="E7" s="278"/>
+      <c r="F7" s="278"/>
+    </row>
+    <row r="8" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="241" t="s">
         <v>292</v>
       </c>
-      <c r="B7" s="283"/>
-      <c r="C7" s="283"/>
-      <c r="D7" s="274"/>
-      <c r="E7" s="275"/>
-      <c r="F7" s="275"/>
-    </row>
-    <row r="8" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="241" t="s">
-        <v>293</v>
-      </c>
       <c r="B8" s="241" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C8" s="243"/>
       <c r="D8" s="208"/>
       <c r="E8" s="222"/>
       <c r="F8" s="200"/>
     </row>
-    <row r="9" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="241" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B9" s="241" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C9" s="243"/>
       <c r="D9" s="210"/>
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
     </row>
-    <row r="10" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="241" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B10" s="241" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C10" s="243"/>
       <c r="D10" s="210"/>
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
     </row>
-    <row r="11" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="278"/>
-      <c r="B11" s="279"/>
-      <c r="C11" s="279"/>
+    <row r="11" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="287"/>
+      <c r="B11" s="288"/>
+      <c r="C11" s="288"/>
       <c r="D11" s="210"/>
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
     </row>
-    <row r="12" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="281" t="s">
+    <row r="12" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="304" t="s">
         <v>231</v>
       </c>
-      <c r="B12" s="281"/>
-      <c r="C12" s="281"/>
+      <c r="B12" s="304"/>
+      <c r="C12" s="304"/>
       <c r="D12" s="210"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
     </row>
-    <row r="13" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="244" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B13" s="262"/>
       <c r="C13" s="263"/>
@@ -2988,7 +2972,7 @@
       <c r="E13" s="199"/>
       <c r="F13" s="51"/>
     </row>
-    <row r="14" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="257"/>
       <c r="B14" s="242"/>
       <c r="C14" s="267"/>
@@ -2996,81 +2980,81 @@
       <c r="E14" s="199"/>
       <c r="F14" s="51"/>
     </row>
-    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="278"/>
-      <c r="B15" s="279"/>
-      <c r="C15" s="279"/>
+    <row r="15" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="287"/>
+      <c r="B15" s="288"/>
+      <c r="C15" s="288"/>
       <c r="D15" s="223"/>
       <c r="E15" s="224"/>
       <c r="F15" s="224"/>
     </row>
-    <row r="16" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="282" t="s">
-        <v>297</v>
-      </c>
-      <c r="B16" s="286"/>
-      <c r="C16" s="286"/>
-      <c r="D16" s="274"/>
-      <c r="E16" s="275"/>
-      <c r="F16" s="275"/>
-    </row>
-    <row r="17" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="283" t="s">
+        <v>296</v>
+      </c>
+      <c r="B16" s="305"/>
+      <c r="C16" s="305"/>
+      <c r="D16" s="277"/>
+      <c r="E16" s="278"/>
+      <c r="F16" s="278"/>
+    </row>
+    <row r="17" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="241" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B17" s="241" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C17" s="243"/>
       <c r="D17" s="208"/>
       <c r="E17" s="222"/>
       <c r="F17" s="200"/>
     </row>
-    <row r="18" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="241" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B18" s="241" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C18" s="243"/>
       <c r="D18" s="210"/>
       <c r="E18" s="18"/>
       <c r="F18" s="18"/>
     </row>
-    <row r="19" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="241" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B19" s="241" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C19" s="243"/>
       <c r="D19" s="210"/>
       <c r="E19" s="18"/>
       <c r="F19" s="18"/>
     </row>
-    <row r="20" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="278"/>
-      <c r="B20" s="279"/>
-      <c r="C20" s="279"/>
+    <row r="20" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="287"/>
+      <c r="B20" s="288"/>
+      <c r="C20" s="288"/>
       <c r="D20" s="207"/>
       <c r="E20" s="51"/>
       <c r="F20" s="201"/>
     </row>
-    <row r="21" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="281" t="s">
-        <v>299</v>
-      </c>
-      <c r="B21" s="281"/>
-      <c r="C21" s="281"/>
+    <row r="21" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="304" t="s">
+        <v>298</v>
+      </c>
+      <c r="B21" s="304"/>
+      <c r="C21" s="304"/>
       <c r="D21" s="207"/>
       <c r="E21" s="18"/>
       <c r="F21" s="18"/>
     </row>
-    <row r="22" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="244" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B22" s="262"/>
       <c r="C22" s="263"/>
@@ -3078,7 +3062,7 @@
       <c r="E22" s="204"/>
       <c r="F22" s="203"/>
     </row>
-    <row r="23" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="249"/>
       <c r="B23" s="264"/>
       <c r="C23" s="265"/>
@@ -3086,77 +3070,77 @@
       <c r="E23" s="204"/>
       <c r="F23" s="203"/>
     </row>
-    <row r="24" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="278"/>
-      <c r="B24" s="279"/>
-      <c r="C24" s="280"/>
+    <row r="24" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="287"/>
+      <c r="B24" s="288"/>
+      <c r="C24" s="289"/>
       <c r="D24" s="207"/>
       <c r="E24" s="204"/>
       <c r="F24" s="203"/>
       <c r="K24" s="29"/>
       <c r="L24" s="18"/>
     </row>
-    <row r="25" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="282" t="s">
-        <v>298</v>
-      </c>
-      <c r="B25" s="283"/>
-      <c r="C25" s="283"/>
+    <row r="25" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="283" t="s">
+        <v>297</v>
+      </c>
+      <c r="B25" s="284"/>
+      <c r="C25" s="284"/>
       <c r="D25" s="223"/>
       <c r="E25" s="224"/>
       <c r="F25" s="224"/>
       <c r="K25" s="29"/>
       <c r="L25" s="18"/>
     </row>
-    <row r="26" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="245" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B26" s="246" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C26" s="247" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D26" s="225"/>
       <c r="E26" s="215"/>
       <c r="F26" s="215"/>
     </row>
-    <row r="27" spans="1:12" s="106" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" s="106" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="245" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B27" s="246" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C27" s="247" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D27" s="226"/>
       <c r="E27" s="227"/>
       <c r="F27" s="227"/>
     </row>
-    <row r="28" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="278"/>
-      <c r="B28" s="279"/>
-      <c r="C28" s="279"/>
+    <row r="28" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="287"/>
+      <c r="B28" s="288"/>
+      <c r="C28" s="288"/>
       <c r="D28" s="207"/>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
     </row>
-    <row r="29" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="284" t="s">
-        <v>301</v>
-      </c>
-      <c r="B29" s="285"/>
-      <c r="C29" s="285"/>
+    <row r="29" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="285" t="s">
+        <v>300</v>
+      </c>
+      <c r="B29" s="286"/>
+      <c r="C29" s="286"/>
       <c r="D29" s="205"/>
       <c r="E29" s="37"/>
       <c r="F29" s="37"/>
     </row>
-    <row r="30" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="233" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B30" s="234"/>
       <c r="C30" s="234"/>
@@ -3164,7 +3148,7 @@
       <c r="E30" s="37"/>
       <c r="F30" s="37"/>
     </row>
-    <row r="31" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="259"/>
       <c r="B31" s="260"/>
       <c r="C31" s="260"/>
@@ -3172,27 +3156,27 @@
       <c r="E31" s="37"/>
       <c r="F31" s="37"/>
     </row>
-    <row r="32" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="279"/>
-      <c r="B32" s="279"/>
-      <c r="C32" s="280"/>
+    <row r="32" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="288"/>
+      <c r="B32" s="288"/>
+      <c r="C32" s="289"/>
       <c r="D32" s="207"/>
       <c r="E32" s="18"/>
       <c r="F32" s="18"/>
     </row>
-    <row r="33" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="284" t="s">
+    <row r="33" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="285" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="285"/>
-      <c r="C33" s="285"/>
+      <c r="B33" s="286"/>
+      <c r="C33" s="286"/>
       <c r="D33" s="205"/>
       <c r="E33" s="37"/>
       <c r="F33" s="37"/>
     </row>
-    <row r="34" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="248" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B34" s="249"/>
       <c r="C34" s="250"/>
@@ -3200,75 +3184,75 @@
       <c r="E34" s="37"/>
       <c r="F34" s="37"/>
     </row>
-    <row r="35" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="295"/>
-      <c r="B35" s="296"/>
-      <c r="C35" s="297"/>
+    <row r="35" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="290"/>
+      <c r="B35" s="291"/>
+      <c r="C35" s="292"/>
       <c r="D35" s="208"/>
       <c r="F35" s="209"/>
     </row>
-    <row r="36" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="276" t="s">
-        <v>302</v>
-      </c>
-      <c r="B36" s="277"/>
-      <c r="C36" s="277"/>
+    <row r="36" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="302" t="s">
+        <v>301</v>
+      </c>
+      <c r="B36" s="303"/>
+      <c r="C36" s="303"/>
       <c r="D36" s="208"/>
     </row>
-    <row r="37" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="249" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B37" s="257"/>
       <c r="C37" s="251"/>
       <c r="D37" s="208"/>
     </row>
-    <row r="38" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="298"/>
-      <c r="B38" s="299"/>
-      <c r="C38" s="300"/>
+    <row r="38" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="293"/>
+      <c r="B38" s="294"/>
+      <c r="C38" s="295"/>
       <c r="D38" s="208"/>
       <c r="F38" s="209"/>
     </row>
-    <row r="39" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="276" t="s">
+    <row r="39" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="302" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="277"/>
-      <c r="C39" s="277"/>
+      <c r="B39" s="303"/>
+      <c r="C39" s="303"/>
       <c r="D39" s="208"/>
       <c r="F39" s="209"/>
     </row>
-    <row r="40" spans="1:6" s="216" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="293" t="s">
+    <row r="40" spans="1:6" s="216" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="279" t="s">
         <v>74</v>
       </c>
-      <c r="B40" s="294"/>
+      <c r="B40" s="280"/>
       <c r="C40" s="235"/>
       <c r="D40" s="211"/>
       <c r="F40" s="212"/>
     </row>
-    <row r="41" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="196" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B41" s="244"/>
       <c r="C41" s="251"/>
       <c r="D41" s="208"/>
     </row>
-    <row r="42" spans="1:6" s="216" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="293" t="s">
+    <row r="42" spans="1:6" s="216" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="279" t="s">
         <v>75</v>
       </c>
-      <c r="B42" s="294"/>
+      <c r="B42" s="280"/>
       <c r="C42" s="236"/>
       <c r="D42" s="213"/>
       <c r="E42" s="228"/>
       <c r="F42" s="228"/>
     </row>
-    <row r="43" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="196" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B43" s="197"/>
       <c r="C43" s="252"/>
@@ -3276,37 +3260,37 @@
       <c r="E43" s="18"/>
       <c r="F43" s="198"/>
     </row>
-    <row r="44" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="278"/>
-      <c r="B44" s="279"/>
-      <c r="C44" s="280"/>
+    <row r="44" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="287"/>
+      <c r="B44" s="288"/>
+      <c r="C44" s="289"/>
       <c r="D44" s="207"/>
       <c r="E44" s="18"/>
       <c r="F44" s="198"/>
     </row>
-    <row r="45" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="291" t="s">
-        <v>303</v>
-      </c>
-      <c r="B45" s="292"/>
-      <c r="C45" s="292"/>
-      <c r="D45" s="292"/>
+    <row r="45" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="281" t="s">
+        <v>324</v>
+      </c>
+      <c r="B45" s="282"/>
+      <c r="C45" s="282"/>
+      <c r="D45" s="282"/>
       <c r="E45" s="207"/>
       <c r="F45" s="198"/>
     </row>
-    <row r="46" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="135"/>
-      <c r="B46" s="287" t="s">
-        <v>319</v>
-      </c>
-      <c r="C46" s="288"/>
-      <c r="D46" s="288"/>
+      <c r="B46" s="273" t="s">
+        <v>317</v>
+      </c>
+      <c r="C46" s="274"/>
+      <c r="D46" s="274"/>
       <c r="E46" s="208"/>
       <c r="F46"/>
     </row>
-    <row r="47" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="197" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B47" s="237" t="s">
         <v>52</v>
@@ -3315,12 +3299,12 @@
         <v>51</v>
       </c>
       <c r="D47" s="239" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E47" s="205"/>
       <c r="F47" s="37"/>
     </row>
-    <row r="48" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="196"/>
       <c r="B48" s="197"/>
       <c r="C48" s="249"/>
@@ -3328,7 +3312,7 @@
       <c r="E48" s="207"/>
       <c r="F48" s="201"/>
     </row>
-    <row r="49" spans="1:10" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="253"/>
       <c r="B49" s="255"/>
       <c r="C49" s="254"/>
@@ -3336,20 +3320,20 @@
       <c r="E49" s="207"/>
       <c r="F49" s="201"/>
     </row>
-    <row r="50" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="253"/>
-      <c r="B50" s="289" t="s">
+      <c r="B50" s="275" t="s">
         <v>4</v>
       </c>
-      <c r="C50" s="290"/>
-      <c r="D50" s="290"/>
+      <c r="C50" s="276"/>
+      <c r="D50" s="276"/>
       <c r="E50" s="206"/>
       <c r="F50" s="28"/>
       <c r="J50" s="202"/>
     </row>
-    <row r="51" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="196" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B51" s="237" t="s">
         <v>52</v>
@@ -3358,78 +3342,65 @@
         <v>51</v>
       </c>
       <c r="D51" s="240" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E51" s="206"/>
       <c r="F51" s="28"/>
       <c r="J51" s="202"/>
     </row>
-    <row r="52" spans="1:10" s="347" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="334"/>
-      <c r="B52" s="335"/>
-      <c r="C52" s="336"/>
-      <c r="D52" s="337"/>
+    <row r="52" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="268"/>
+      <c r="B52" s="269"/>
+      <c r="C52" s="270"/>
+      <c r="D52" s="271"/>
       <c r="E52" s="206"/>
-      <c r="F52" s="346"/>
+      <c r="F52" s="28"/>
       <c r="J52" s="202"/>
     </row>
-    <row r="53" spans="1:10" s="338" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="345"/>
-      <c r="B53" s="345"/>
-      <c r="C53" s="345"/>
-      <c r="D53" s="345"/>
-      <c r="E53" s="339"/>
+    <row r="53" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="218"/>
+      <c r="B53" s="218"/>
+      <c r="C53" s="218"/>
+      <c r="D53" s="218"/>
+      <c r="E53" s="18"/>
       <c r="F53" s="198"/>
     </row>
-    <row r="54" spans="1:10" s="338" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="344"/>
-      <c r="B54" s="344"/>
-      <c r="C54" s="344"/>
-      <c r="D54" s="344"/>
-      <c r="E54" s="339"/>
+    <row r="54" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="221"/>
+      <c r="B54" s="221"/>
+      <c r="C54" s="221"/>
+      <c r="D54" s="221"/>
+      <c r="E54" s="18"/>
       <c r="F54" s="198"/>
     </row>
-    <row r="55" spans="1:10" s="338" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="344"/>
-      <c r="B55" s="344"/>
-      <c r="C55" s="344"/>
-      <c r="D55" s="344"/>
-      <c r="E55" s="339"/>
+    <row r="55" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="221"/>
+      <c r="B55" s="221"/>
+      <c r="C55" s="221"/>
+      <c r="D55" s="221"/>
+      <c r="E55" s="18"/>
       <c r="F55" s="198"/>
     </row>
-    <row r="56" spans="1:10" s="338" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="339"/>
-      <c r="B56" s="340"/>
-      <c r="C56" s="341"/>
-      <c r="D56" s="342"/>
-      <c r="E56" s="342"/>
+    <row r="56" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="18"/>
+      <c r="B56" s="122"/>
+      <c r="C56" s="37"/>
+      <c r="D56" s="272"/>
+      <c r="E56" s="272"/>
       <c r="F56" s="214"/>
     </row>
-    <row r="57" spans="1:10" s="338" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="339"/>
-      <c r="B57" s="343"/>
-      <c r="C57" s="343"/>
+    <row r="57" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="18"/>
+      <c r="B57" s="120"/>
+      <c r="C57" s="120"/>
       <c r="F57" s="209"/>
     </row>
-    <row r="58" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="28"/>
       <c r="F58" s="209"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A44:C44"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="D7:F7"/>
@@ -3446,6 +3417,19 @@
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A21:C21"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A44:C44"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup scale="69" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -3459,28 +3443,28 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AU102"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="56.28515625" style="127" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="127" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="127" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" style="127" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="127" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" style="155" customWidth="1"/>
-    <col min="48" max="16384" width="8.85546875" style="127"/>
+    <col min="1" max="1" width="56.26953125" style="127" customWidth="1"/>
+    <col min="2" max="2" width="8.453125" style="127" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" style="127" customWidth="1"/>
+    <col min="4" max="4" width="8.81640625" style="127" customWidth="1"/>
+    <col min="5" max="5" width="10.81640625" style="127" customWidth="1"/>
+    <col min="6" max="6" width="10.81640625" style="155" customWidth="1"/>
+    <col min="48" max="16384" width="8.81640625" style="127"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="304" t="s">
+    <row r="1" spans="1:9" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="309" t="s">
         <v>288</v>
       </c>
-      <c r="B1" s="304"/>
-      <c r="C1" s="304"/>
-      <c r="D1" s="304"/>
-      <c r="E1" s="304"/>
-      <c r="F1" s="304"/>
-    </row>
-    <row r="2" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="309"/>
+      <c r="C1" s="309"/>
+      <c r="D1" s="309"/>
+      <c r="E1" s="309"/>
+      <c r="F1" s="309"/>
+    </row>
+    <row r="2" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="128"/>
       <c r="B2" s="129" t="s">
         <v>3</v>
@@ -3498,7 +3482,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="132" t="s">
         <v>32</v>
       </c>
@@ -3508,7 +3492,7 @@
       <c r="E3" s="133"/>
       <c r="F3" s="134"/>
     </row>
-    <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="135" t="s">
         <v>41</v>
       </c>
@@ -3530,7 +3514,7 @@
         <v>2.6973026973026972E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="135" t="s">
         <v>5</v>
       </c>
@@ -3552,7 +3536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="135" t="s">
         <v>42</v>
       </c>
@@ -3575,7 +3559,7 @@
       </c>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="141" t="s">
         <v>208</v>
       </c>
@@ -3597,7 +3581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="135" t="s">
         <v>24</v>
       </c>
@@ -3619,7 +3603,7 @@
         <v>3.7037037037037035E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="135" t="s">
         <v>49</v>
       </c>
@@ -3640,7 +3624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="135" t="s">
         <v>50</v>
       </c>
@@ -3661,7 +3645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="135" t="s">
         <v>209</v>
       </c>
@@ -3671,7 +3655,7 @@
       <c r="E11" s="142"/>
       <c r="F11" s="142"/>
     </row>
-    <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="143" t="s">
         <v>205</v>
       </c>
@@ -3692,7 +3676,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="143" t="s">
         <v>18</v>
       </c>
@@ -3713,7 +3697,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="135" t="s">
         <v>96</v>
       </c>
@@ -3733,7 +3717,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="135" t="s">
         <v>97</v>
       </c>
@@ -3753,7 +3737,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="146"/>
       <c r="B16" s="146"/>
       <c r="C16" s="146"/>
@@ -3761,7 +3745,7 @@
       <c r="E16" s="146"/>
       <c r="F16" s="147"/>
     </row>
-    <row r="17" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="132" t="s">
         <v>31</v>
       </c>
@@ -3771,7 +3755,7 @@
       <c r="E17" s="148"/>
       <c r="F17" s="148"/>
     </row>
-    <row r="18" spans="1:16" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="132"/>
       <c r="B18" s="148"/>
       <c r="C18" s="149" t="s">
@@ -3781,7 +3765,7 @@
       <c r="E18" s="148"/>
       <c r="F18" s="148"/>
     </row>
-    <row r="19" spans="1:16" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="150" t="s">
         <v>228</v>
       </c>
@@ -3796,7 +3780,7 @@
       <c r="E19" s="153"/>
       <c r="F19" s="139"/>
     </row>
-    <row r="20" spans="1:16" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="150"/>
       <c r="B20" s="151"/>
       <c r="C20" s="152"/>
@@ -3804,7 +3788,7 @@
       <c r="E20" s="153"/>
       <c r="F20" s="139"/>
     </row>
-    <row r="21" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="154" t="s">
         <v>231</v>
       </c>
@@ -3818,7 +3802,7 @@
       <c r="E21" s="153"/>
       <c r="F21" s="139"/>
     </row>
-    <row r="22" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="143" t="s">
         <v>187</v>
       </c>
@@ -3833,7 +3817,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="143" t="s">
         <v>264</v>
       </c>
@@ -3849,7 +3833,7 @@
       </c>
       <c r="J23" s="114"/>
     </row>
-    <row r="24" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="143" t="s">
         <v>265</v>
       </c>
@@ -3864,7 +3848,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="143" t="s">
         <v>47</v>
       </c>
@@ -3882,15 +3866,15 @@
       <c r="O25" s="29"/>
       <c r="P25" s="18"/>
     </row>
-    <row r="26" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="305"/>
-      <c r="B26" s="305"/>
-      <c r="C26" s="305"/>
-      <c r="D26" s="305"/>
-      <c r="E26" s="305"/>
-      <c r="F26" s="305"/>
-    </row>
-    <row r="27" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="310"/>
+      <c r="B26" s="310"/>
+      <c r="C26" s="310"/>
+      <c r="D26" s="310"/>
+      <c r="E26" s="310"/>
+      <c r="F26" s="310"/>
+    </row>
+    <row r="27" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="135" t="s">
         <v>230</v>
       </c>
@@ -3900,7 +3884,7 @@
       <c r="E27" s="139"/>
       <c r="F27" s="140"/>
     </row>
-    <row r="28" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="157" t="s">
         <v>216</v>
       </c>
@@ -3910,7 +3894,7 @@
       <c r="E28" s="135"/>
       <c r="F28" s="135"/>
     </row>
-    <row r="29" spans="1:16" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="143" t="s">
         <v>55</v>
       </c>
@@ -3922,7 +3906,7 @@
       <c r="E29" s="158"/>
       <c r="F29" s="156"/>
     </row>
-    <row r="30" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="143" t="s">
         <v>268</v>
       </c>
@@ -3936,7 +3920,7 @@
       <c r="K30" s="29"/>
       <c r="L30" s="18"/>
     </row>
-    <row r="31" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="143" t="s">
         <v>56</v>
       </c>
@@ -3950,7 +3934,7 @@
       <c r="K31" s="29"/>
       <c r="L31" s="18"/>
     </row>
-    <row r="32" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="143" t="s">
         <v>269</v>
       </c>
@@ -3964,7 +3948,7 @@
       <c r="K32" s="29"/>
       <c r="L32" s="18"/>
     </row>
-    <row r="33" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="143" t="s">
         <v>270</v>
       </c>
@@ -3978,19 +3962,19 @@
       <c r="K33" s="29"/>
       <c r="L33" s="18"/>
     </row>
-    <row r="34" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="157" t="s">
         <v>238</v>
       </c>
-      <c r="B34" s="305"/>
-      <c r="C34" s="305"/>
-      <c r="D34" s="305"/>
-      <c r="E34" s="305"/>
-      <c r="F34" s="305"/>
+      <c r="B34" s="310"/>
+      <c r="C34" s="310"/>
+      <c r="D34" s="310"/>
+      <c r="E34" s="310"/>
+      <c r="F34" s="310"/>
       <c r="K34" s="29"/>
       <c r="L34" s="18"/>
     </row>
-    <row r="35" spans="1:47" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:47" ht="48.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="187" t="s">
         <v>271</v>
       </c>
@@ -4002,7 +3986,7 @@
       <c r="E35" s="159"/>
       <c r="F35" s="159"/>
     </row>
-    <row r="36" spans="1:47" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:47" ht="0.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="160" t="s">
         <v>239</v>
       </c>
@@ -4014,7 +3998,7 @@
       <c r="E36" s="162"/>
       <c r="F36" s="162"/>
     </row>
-    <row r="37" spans="1:47" s="163" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:47" s="163" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="187" t="s">
         <v>272</v>
       </c>
@@ -4067,7 +4051,7 @@
       <c r="AT37" s="106"/>
       <c r="AU37" s="106"/>
     </row>
-    <row r="38" spans="1:47" s="163" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:47" s="163" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="160"/>
       <c r="B38" s="135"/>
       <c r="C38" s="138"/>
@@ -4116,15 +4100,15 @@
       <c r="AT38" s="106"/>
       <c r="AU38" s="106"/>
     </row>
-    <row r="39" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="306"/>
-      <c r="B39" s="306"/>
-      <c r="C39" s="306"/>
-      <c r="D39" s="306"/>
-      <c r="E39" s="306"/>
-      <c r="F39" s="306"/>
-    </row>
-    <row r="40" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="311"/>
+      <c r="B39" s="311"/>
+      <c r="C39" s="311"/>
+      <c r="D39" s="311"/>
+      <c r="E39" s="311"/>
+      <c r="F39" s="311"/>
+    </row>
+    <row r="40" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="165" t="s">
         <v>217</v>
       </c>
@@ -4134,7 +4118,7 @@
       <c r="E40" s="148"/>
       <c r="F40" s="148"/>
     </row>
-    <row r="41" spans="1:47" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:47" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="166" t="s">
         <v>43</v>
       </c>
@@ -4148,7 +4132,7 @@
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
     </row>
-    <row r="42" spans="1:47" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:47" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="166" t="s">
         <v>44</v>
       </c>
@@ -4163,7 +4147,7 @@
       <c r="E42" s="148"/>
       <c r="F42" s="148"/>
     </row>
-    <row r="43" spans="1:47" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:47" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="135" t="s">
         <v>60</v>
       </c>
@@ -4177,7 +4161,7 @@
       <c r="E43" s="135"/>
       <c r="F43" s="139"/>
     </row>
-    <row r="44" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="135" t="s">
         <v>197</v>
       </c>
@@ -4191,7 +4175,7 @@
       <c r="E44" s="135"/>
       <c r="F44" s="139"/>
     </row>
-    <row r="45" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="135" t="s">
         <v>9</v>
       </c>
@@ -4205,7 +4189,7 @@
       <c r="E45" s="135"/>
       <c r="F45" s="139"/>
     </row>
-    <row r="46" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="135" t="s">
         <v>196</v>
       </c>
@@ -4219,7 +4203,7 @@
       <c r="E46" s="135"/>
       <c r="F46" s="139"/>
     </row>
-    <row r="47" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="135" t="s">
         <v>10</v>
       </c>
@@ -4233,7 +4217,7 @@
       <c r="E47" s="135"/>
       <c r="F47" s="139"/>
     </row>
-    <row r="48" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="135" t="s">
         <v>194</v>
       </c>
@@ -4247,7 +4231,7 @@
       <c r="E48" s="135"/>
       <c r="F48" s="139"/>
     </row>
-    <row r="49" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="135" t="s">
         <v>61</v>
       </c>
@@ -4261,7 +4245,7 @@
       <c r="E49" s="135"/>
       <c r="F49" s="139"/>
     </row>
-    <row r="50" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="135" t="s">
         <v>195</v>
       </c>
@@ -4275,15 +4259,15 @@
       <c r="E50" s="135"/>
       <c r="F50" s="139"/>
     </row>
-    <row r="51" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="306"/>
-      <c r="B51" s="306"/>
-      <c r="C51" s="306"/>
-      <c r="D51" s="306"/>
-      <c r="E51" s="306"/>
-      <c r="F51" s="306"/>
-    </row>
-    <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="311"/>
+      <c r="B51" s="311"/>
+      <c r="C51" s="311"/>
+      <c r="D51" s="311"/>
+      <c r="E51" s="311"/>
+      <c r="F51" s="311"/>
+    </row>
+    <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="132" t="s">
         <v>45</v>
       </c>
@@ -4293,7 +4277,7 @@
       <c r="E52" s="148"/>
       <c r="F52" s="148"/>
     </row>
-    <row r="53" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="166" t="s">
         <v>88</v>
       </c>
@@ -4303,7 +4287,7 @@
       <c r="E53" s="148"/>
       <c r="F53" s="148"/>
     </row>
-    <row r="54" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="143" t="s">
         <v>25</v>
       </c>
@@ -4313,7 +4297,7 @@
       </c>
       <c r="E54" s="155"/>
     </row>
-    <row r="55" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="143" t="s">
         <v>26</v>
       </c>
@@ -4323,7 +4307,7 @@
       </c>
       <c r="E55" s="155"/>
     </row>
-    <row r="56" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="135" t="s">
         <v>80</v>
       </c>
@@ -4333,7 +4317,7 @@
       <c r="E56" s="135"/>
       <c r="F56" s="139"/>
     </row>
-    <row r="57" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="143" t="s">
         <v>25</v>
       </c>
@@ -4341,7 +4325,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="143" t="s">
         <v>26</v>
       </c>
@@ -4349,7 +4333,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="168"/>
       <c r="B59" s="169"/>
       <c r="C59" s="170"/>
@@ -4357,18 +4341,18 @@
       <c r="E59" s="170"/>
       <c r="F59" s="171"/>
     </row>
-    <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="132" t="s">
         <v>46</v>
       </c>
       <c r="B60" s="138"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="172" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="143" t="s">
         <v>25</v>
       </c>
@@ -4377,7 +4361,7 @@
       </c>
       <c r="E62" s="155"/>
     </row>
-    <row r="63" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="143" t="s">
         <v>26</v>
       </c>
@@ -4386,12 +4370,12 @@
       </c>
       <c r="E63" s="155"/>
     </row>
-    <row r="64" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="143"/>
       <c r="B64" s="138"/>
       <c r="E64" s="155"/>
     </row>
-    <row r="65" spans="1:47" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:47" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="135" t="s">
         <v>35</v>
       </c>
@@ -4401,7 +4385,7 @@
       <c r="E65" s="135"/>
       <c r="F65" s="139"/>
     </row>
-    <row r="66" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="143" t="s">
         <v>25</v>
       </c>
@@ -4413,7 +4397,7 @@
       <c r="E66" s="135"/>
       <c r="F66" s="139"/>
     </row>
-    <row r="67" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="143" t="s">
         <v>26</v>
       </c>
@@ -4425,7 +4409,7 @@
       <c r="E67" s="135"/>
       <c r="F67" s="139"/>
     </row>
-    <row r="68" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="170"/>
       <c r="B68" s="170"/>
       <c r="C68" s="170"/>
@@ -4433,18 +4417,18 @@
       <c r="E68" s="170"/>
       <c r="F68" s="171"/>
     </row>
-    <row r="69" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="132" t="s">
         <v>40</v>
       </c>
       <c r="F69" s="173"/>
     </row>
-    <row r="70" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="135" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="71" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="143" t="s">
         <v>37</v>
       </c>
@@ -4452,7 +4436,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="72" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="143" t="s">
         <v>38</v>
       </c>
@@ -4460,7 +4444,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="73" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="143" t="s">
         <v>168</v>
       </c>
@@ -4472,7 +4456,7 @@
       <c r="E73" s="143"/>
       <c r="F73" s="175"/>
     </row>
-    <row r="74" spans="1:47" s="143" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:47" s="143" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C74" s="138"/>
       <c r="F74" s="175"/>
       <c r="G74" s="29"/>
@@ -4517,17 +4501,17 @@
       <c r="AT74" s="29"/>
       <c r="AU74" s="29"/>
     </row>
-    <row r="75" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="301" t="s">
+    <row r="75" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="306" t="s">
         <v>75</v>
       </c>
-      <c r="B75" s="301"/>
-      <c r="C75" s="301"/>
-      <c r="D75" s="301"/>
-      <c r="E75" s="301"/>
-      <c r="F75" s="301"/>
-    </row>
-    <row r="76" spans="1:47" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="306"/>
+      <c r="C75" s="306"/>
+      <c r="D75" s="306"/>
+      <c r="E75" s="306"/>
+      <c r="F75" s="306"/>
+    </row>
+    <row r="76" spans="1:47" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="143" t="s">
         <v>275</v>
       </c>
@@ -4539,7 +4523,7 @@
       <c r="E76" s="135"/>
       <c r="F76" s="177"/>
     </row>
-    <row r="77" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="143" t="s">
         <v>276</v>
       </c>
@@ -4551,7 +4535,7 @@
       <c r="E77" s="135"/>
       <c r="F77" s="177"/>
     </row>
-    <row r="78" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="143" t="s">
         <v>277</v>
       </c>
@@ -4563,7 +4547,7 @@
       <c r="E78" s="135"/>
       <c r="F78" s="177"/>
     </row>
-    <row r="79" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="146"/>
       <c r="B79" s="146"/>
       <c r="C79" s="146"/>
@@ -4571,7 +4555,7 @@
       <c r="E79" s="146"/>
       <c r="F79" s="147"/>
     </row>
-    <row r="80" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="132" t="s">
         <v>234</v>
       </c>
@@ -4581,21 +4565,21 @@
       <c r="E80" s="135"/>
       <c r="F80" s="177"/>
     </row>
-    <row r="81" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="301" t="s">
+    <row r="81" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="306" t="s">
         <v>68</v>
       </c>
-      <c r="B81" s="302" t="s">
+      <c r="B81" s="307" t="s">
         <v>3</v>
       </c>
-      <c r="C81" s="302"/>
-      <c r="E81" s="303" t="s">
+      <c r="C81" s="307"/>
+      <c r="E81" s="308" t="s">
         <v>4</v>
       </c>
-      <c r="F81" s="303"/>
-    </row>
-    <row r="82" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="301"/>
+      <c r="F81" s="308"/>
+    </row>
+    <row r="82" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="306"/>
       <c r="B82" s="149" t="s">
         <v>52</v>
       </c>
@@ -4612,7 +4596,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="143" t="s">
         <v>253</v>
       </c>
@@ -4629,7 +4613,7 @@
       <c r="E83" s="135"/>
       <c r="F83" s="140"/>
     </row>
-    <row r="84" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="143" t="s">
         <v>254</v>
       </c>
@@ -4646,7 +4630,7 @@
       <c r="E84" s="135"/>
       <c r="F84" s="140"/>
     </row>
-    <row r="85" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="143" t="s">
         <v>204</v>
       </c>
@@ -4662,7 +4646,7 @@
       <c r="E85" s="135"/>
       <c r="F85" s="140"/>
     </row>
-    <row r="86" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="143" t="s">
         <v>129</v>
       </c>
@@ -4679,7 +4663,7 @@
       <c r="E86" s="135"/>
       <c r="F86" s="140"/>
     </row>
-    <row r="87" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="143" t="s">
         <v>257</v>
       </c>
@@ -4696,7 +4680,7 @@
       <c r="E87" s="135"/>
       <c r="F87" s="140"/>
     </row>
-    <row r="88" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="143" t="s">
         <v>278</v>
       </c>
@@ -4712,7 +4696,7 @@
       </c>
       <c r="F88" s="135"/>
     </row>
-    <row r="89" spans="1:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="192" t="s">
         <v>279</v>
       </c>
@@ -4730,7 +4714,7 @@
       <c r="F89" s="194"/>
       <c r="J89" s="5"/>
     </row>
-    <row r="90" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="188" t="s">
         <v>280</v>
       </c>
@@ -4747,7 +4731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="143" t="s">
         <v>281</v>
       </c>
@@ -4763,7 +4747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="143" t="s">
         <v>283</v>
       </c>
@@ -4779,7 +4763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="143" t="s">
         <v>282</v>
       </c>
@@ -4795,7 +4779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="146"/>
       <c r="B94" s="146"/>
       <c r="C94" s="146"/>
@@ -4803,7 +4787,7 @@
       <c r="E94" s="146"/>
       <c r="F94" s="147"/>
     </row>
-    <row r="95" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="179" t="s">
         <v>39</v>
       </c>
@@ -4813,7 +4797,7 @@
       <c r="E95" s="135"/>
       <c r="F95" s="177"/>
     </row>
-    <row r="96" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="135" t="s">
         <v>226</v>
       </c>
@@ -4827,7 +4811,7 @@
       <c r="E96" s="180"/>
       <c r="F96" s="181"/>
     </row>
-    <row r="97" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="143" t="s">
         <v>16</v>
       </c>
@@ -4838,7 +4822,7 @@
       <c r="E97" s="138"/>
       <c r="F97" s="139"/>
     </row>
-    <row r="98" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="143" t="s">
         <v>4</v>
       </c>
@@ -4850,12 +4834,12 @@
       <c r="E98" s="138"/>
       <c r="F98" s="139"/>
     </row>
-    <row r="99" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="135" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="143" t="s">
         <v>16</v>
       </c>
@@ -4864,12 +4848,12 @@
       </c>
       <c r="C100" s="138"/>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="143"/>
       <c r="B101" s="174"/>
       <c r="C101" s="174"/>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="135" t="s">
         <v>262</v>
       </c>
@@ -4901,26 +4885,26 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AU99"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="127" customWidth="1"/>
-    <col min="2" max="4" width="9.85546875" style="127" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="127" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" style="155" customWidth="1"/>
-    <col min="48" max="16384" width="8.85546875" style="127"/>
+    <col min="1" max="1" width="50.81640625" style="127" customWidth="1"/>
+    <col min="2" max="4" width="9.81640625" style="127" customWidth="1"/>
+    <col min="5" max="5" width="10.81640625" style="127" customWidth="1"/>
+    <col min="6" max="6" width="10.81640625" style="155" customWidth="1"/>
+    <col min="48" max="16384" width="8.81640625" style="127"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="304" t="s">
+    <row r="1" spans="1:6" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="309" t="s">
         <v>235</v>
       </c>
-      <c r="B1" s="304"/>
-      <c r="C1" s="304"/>
-      <c r="D1" s="304"/>
-      <c r="E1" s="304"/>
-      <c r="F1" s="304"/>
-    </row>
-    <row r="2" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="309"/>
+      <c r="C1" s="309"/>
+      <c r="D1" s="309"/>
+      <c r="E1" s="309"/>
+      <c r="F1" s="309"/>
+    </row>
+    <row r="2" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="128"/>
       <c r="B2" s="129" t="s">
         <v>3</v>
@@ -4938,7 +4922,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="132" t="s">
         <v>32</v>
       </c>
@@ -4948,7 +4932,7 @@
       <c r="E3" s="133"/>
       <c r="F3" s="134"/>
     </row>
-    <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="135" t="s">
         <v>41</v>
       </c>
@@ -4970,7 +4954,7 @@
         <v>1.1753183153770812E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="135" t="s">
         <v>5</v>
       </c>
@@ -4992,7 +4976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="135" t="s">
         <v>42</v>
       </c>
@@ -5014,7 +4998,7 @@
         <v>1.4869888475836431E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="141" t="s">
         <v>208</v>
       </c>
@@ -5036,7 +5020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="135" t="s">
         <v>24</v>
       </c>
@@ -5058,7 +5042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="135" t="s">
         <v>49</v>
       </c>
@@ -5079,7 +5063,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="135" t="s">
         <v>50</v>
       </c>
@@ -5101,7 +5085,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="135" t="s">
         <v>209</v>
       </c>
@@ -5111,7 +5095,7 @@
       <c r="E11" s="142"/>
       <c r="F11" s="142"/>
     </row>
-    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="143" t="s">
         <v>205</v>
       </c>
@@ -5131,7 +5115,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="143" t="s">
         <v>18</v>
       </c>
@@ -5151,7 +5135,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="143" t="s">
         <v>210</v>
       </c>
@@ -5171,7 +5155,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="135" t="s">
         <v>96</v>
       </c>
@@ -5191,7 +5175,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="135" t="s">
         <v>97</v>
       </c>
@@ -5211,7 +5195,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="146"/>
       <c r="B17" s="146"/>
       <c r="C17" s="146"/>
@@ -5219,7 +5203,7 @@
       <c r="E17" s="146"/>
       <c r="F17" s="147"/>
     </row>
-    <row r="18" spans="1:16" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="132" t="s">
         <v>31</v>
       </c>
@@ -5229,7 +5213,7 @@
       <c r="E18" s="148"/>
       <c r="F18" s="148"/>
     </row>
-    <row r="19" spans="1:16" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="132"/>
       <c r="B19" s="148"/>
       <c r="C19" s="149" t="s">
@@ -5239,7 +5223,7 @@
       <c r="E19" s="148"/>
       <c r="F19" s="148"/>
     </row>
-    <row r="20" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="150" t="s">
         <v>228</v>
       </c>
@@ -5254,7 +5238,7 @@
       <c r="E20" s="153"/>
       <c r="F20" s="139"/>
     </row>
-    <row r="21" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="154" t="s">
         <v>231</v>
       </c>
@@ -5264,7 +5248,7 @@
       <c r="E21" s="153"/>
       <c r="F21" s="139"/>
     </row>
-    <row r="22" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="143" t="s">
         <v>7</v>
       </c>
@@ -5275,7 +5259,7 @@
       <c r="D22" s="135"/>
       <c r="E22" s="139"/>
     </row>
-    <row r="23" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="143" t="s">
         <v>187</v>
       </c>
@@ -5286,7 +5270,7 @@
       <c r="D23" s="135"/>
       <c r="E23" s="139"/>
     </row>
-    <row r="24" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="143" t="s">
         <v>6</v>
       </c>
@@ -5299,7 +5283,7 @@
       <c r="O24" s="29"/>
       <c r="P24" s="18"/>
     </row>
-    <row r="25" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="143" t="s">
         <v>47</v>
       </c>
@@ -5311,15 +5295,15 @@
       <c r="E25" s="139"/>
       <c r="F25" s="156"/>
     </row>
-    <row r="26" spans="1:16" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="305"/>
-      <c r="B26" s="305"/>
-      <c r="C26" s="305"/>
-      <c r="D26" s="305"/>
-      <c r="E26" s="305"/>
-      <c r="F26" s="305"/>
-    </row>
-    <row r="27" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="310"/>
+      <c r="B26" s="310"/>
+      <c r="C26" s="310"/>
+      <c r="D26" s="310"/>
+      <c r="E26" s="310"/>
+      <c r="F26" s="310"/>
+    </row>
+    <row r="27" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="135" t="s">
         <v>230</v>
       </c>
@@ -5334,7 +5318,7 @@
       <c r="E27" s="139"/>
       <c r="F27" s="140"/>
     </row>
-    <row r="28" spans="1:16" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="157" t="s">
         <v>216</v>
       </c>
@@ -5344,7 +5328,7 @@
       <c r="E28" s="135"/>
       <c r="F28" s="135"/>
     </row>
-    <row r="29" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="143" t="s">
         <v>55</v>
       </c>
@@ -5358,7 +5342,7 @@
       <c r="K29" s="29"/>
       <c r="L29" s="18"/>
     </row>
-    <row r="30" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="143" t="s">
         <v>56</v>
       </c>
@@ -5372,7 +5356,7 @@
       <c r="K30" s="29"/>
       <c r="L30" s="18"/>
     </row>
-    <row r="31" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="143" t="s">
         <v>236</v>
       </c>
@@ -5386,7 +5370,7 @@
       <c r="K31" s="29"/>
       <c r="L31" s="18"/>
     </row>
-    <row r="32" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="143" t="s">
         <v>237</v>
       </c>
@@ -5400,7 +5384,7 @@
       <c r="K32" s="29"/>
       <c r="L32" s="18"/>
     </row>
-    <row r="33" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="143" t="s">
         <v>191</v>
       </c>
@@ -5414,17 +5398,17 @@
       <c r="K33" s="29"/>
       <c r="L33" s="18"/>
     </row>
-    <row r="34" spans="1:47" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:47" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="157" t="s">
         <v>238</v>
       </c>
-      <c r="B34" s="305"/>
-      <c r="C34" s="305"/>
-      <c r="D34" s="305"/>
-      <c r="E34" s="305"/>
-      <c r="F34" s="305"/>
-    </row>
-    <row r="35" spans="1:47" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="310"/>
+      <c r="C34" s="310"/>
+      <c r="D34" s="310"/>
+      <c r="E34" s="310"/>
+      <c r="F34" s="310"/>
+    </row>
+    <row r="35" spans="1:47" ht="0.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="157"/>
       <c r="B35" s="159"/>
       <c r="C35" s="159"/>
@@ -5432,7 +5416,7 @@
       <c r="E35" s="159"/>
       <c r="F35" s="159"/>
     </row>
-    <row r="36" spans="1:47" s="163" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:47" s="163" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="160" t="s">
         <v>239</v>
       </c>
@@ -5485,7 +5469,7 @@
       <c r="AT36" s="106"/>
       <c r="AU36" s="106"/>
     </row>
-    <row r="37" spans="1:47" s="163" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:47" s="163" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="160" t="s">
         <v>240</v>
       </c>
@@ -5538,7 +5522,7 @@
       <c r="AT37" s="106"/>
       <c r="AU37" s="106"/>
     </row>
-    <row r="38" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="160"/>
       <c r="B38" s="135"/>
       <c r="C38" s="138"/>
@@ -5546,15 +5530,15 @@
       <c r="E38" s="164"/>
       <c r="F38" s="164"/>
     </row>
-    <row r="39" spans="1:47" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="306"/>
-      <c r="B39" s="306"/>
-      <c r="C39" s="306"/>
-      <c r="D39" s="306"/>
-      <c r="E39" s="306"/>
-      <c r="F39" s="306"/>
-    </row>
-    <row r="40" spans="1:47" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:47" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="311"/>
+      <c r="B39" s="311"/>
+      <c r="C39" s="311"/>
+      <c r="D39" s="311"/>
+      <c r="E39" s="311"/>
+      <c r="F39" s="311"/>
+    </row>
+    <row r="40" spans="1:47" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="165" t="s">
         <v>217</v>
       </c>
@@ -5564,7 +5548,7 @@
       <c r="E40" s="148"/>
       <c r="F40" s="148"/>
     </row>
-    <row r="41" spans="1:47" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:47" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="166" t="s">
         <v>43</v>
       </c>
@@ -5578,7 +5562,7 @@
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
     </row>
-    <row r="42" spans="1:47" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:47" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="166" t="s">
         <v>44</v>
       </c>
@@ -5592,7 +5576,7 @@
       <c r="E42" s="148"/>
       <c r="F42" s="148"/>
     </row>
-    <row r="43" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="135" t="s">
         <v>60</v>
       </c>
@@ -5606,7 +5590,7 @@
       <c r="E43" s="135"/>
       <c r="F43" s="139"/>
     </row>
-    <row r="44" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="135" t="s">
         <v>197</v>
       </c>
@@ -5620,7 +5604,7 @@
       <c r="E44" s="135"/>
       <c r="F44" s="139"/>
     </row>
-    <row r="45" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="135" t="s">
         <v>9</v>
       </c>
@@ -5634,7 +5618,7 @@
       <c r="E45" s="135"/>
       <c r="F45" s="139"/>
     </row>
-    <row r="46" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="135" t="s">
         <v>196</v>
       </c>
@@ -5648,7 +5632,7 @@
       <c r="E46" s="135"/>
       <c r="F46" s="139"/>
     </row>
-    <row r="47" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="135" t="s">
         <v>10</v>
       </c>
@@ -5662,7 +5646,7 @@
       <c r="E47" s="135"/>
       <c r="F47" s="139"/>
     </row>
-    <row r="48" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="135" t="s">
         <v>194</v>
       </c>
@@ -5676,7 +5660,7 @@
       <c r="E48" s="135"/>
       <c r="F48" s="139"/>
     </row>
-    <row r="49" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="135" t="s">
         <v>61</v>
       </c>
@@ -5690,7 +5674,7 @@
       <c r="E49" s="135"/>
       <c r="F49" s="139"/>
     </row>
-    <row r="50" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="135" t="s">
         <v>195</v>
       </c>
@@ -5704,15 +5688,15 @@
       <c r="E50" s="135"/>
       <c r="F50" s="139"/>
     </row>
-    <row r="51" spans="1:6" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="306"/>
-      <c r="B51" s="306"/>
-      <c r="C51" s="306"/>
-      <c r="D51" s="306"/>
-      <c r="E51" s="306"/>
-      <c r="F51" s="306"/>
-    </row>
-    <row r="52" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="311"/>
+      <c r="B51" s="311"/>
+      <c r="C51" s="311"/>
+      <c r="D51" s="311"/>
+      <c r="E51" s="311"/>
+      <c r="F51" s="311"/>
+    </row>
+    <row r="52" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="132" t="s">
         <v>45</v>
       </c>
@@ -5722,7 +5706,7 @@
       <c r="E52" s="148"/>
       <c r="F52" s="148"/>
     </row>
-    <row r="53" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="166" t="s">
         <v>88</v>
       </c>
@@ -5732,7 +5716,7 @@
       <c r="E53" s="148"/>
       <c r="F53" s="148"/>
     </row>
-    <row r="54" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="143" t="s">
         <v>25</v>
       </c>
@@ -5741,7 +5725,7 @@
       </c>
       <c r="E54" s="155"/>
     </row>
-    <row r="55" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="143" t="s">
         <v>26</v>
       </c>
@@ -5750,7 +5734,7 @@
       </c>
       <c r="E55" s="155"/>
     </row>
-    <row r="56" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="135" t="s">
         <v>80</v>
       </c>
@@ -5760,7 +5744,7 @@
       <c r="E56" s="135"/>
       <c r="F56" s="139"/>
     </row>
-    <row r="57" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="143" t="s">
         <v>25</v>
       </c>
@@ -5768,7 +5752,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="143" t="s">
         <v>26</v>
       </c>
@@ -5776,7 +5760,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="168"/>
       <c r="B59" s="169"/>
       <c r="C59" s="170"/>
@@ -5784,18 +5768,18 @@
       <c r="E59" s="170"/>
       <c r="F59" s="171"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="132" t="s">
         <v>46</v>
       </c>
       <c r="B60" s="138"/>
     </row>
-    <row r="61" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="172" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="143" t="s">
         <v>25</v>
       </c>
@@ -5804,7 +5788,7 @@
       </c>
       <c r="E62" s="155"/>
     </row>
-    <row r="63" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="143" t="s">
         <v>26</v>
       </c>
@@ -5813,14 +5797,14 @@
       </c>
       <c r="E63" s="155"/>
     </row>
-    <row r="64" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="143"/>
       <c r="B64" s="138">
         <v>41</v>
       </c>
       <c r="E64" s="155"/>
     </row>
-    <row r="65" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="135" t="s">
         <v>35</v>
       </c>
@@ -5830,7 +5814,7 @@
       <c r="E65" s="135"/>
       <c r="F65" s="139"/>
     </row>
-    <row r="66" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="143" t="s">
         <v>25</v>
       </c>
@@ -5842,7 +5826,7 @@
       <c r="E66" s="135"/>
       <c r="F66" s="139"/>
     </row>
-    <row r="67" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="143" t="s">
         <v>26</v>
       </c>
@@ -5854,7 +5838,7 @@
       <c r="E67" s="135"/>
       <c r="F67" s="139"/>
     </row>
-    <row r="68" spans="1:47" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:47" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="170"/>
       <c r="B68" s="170"/>
       <c r="C68" s="170"/>
@@ -5862,18 +5846,18 @@
       <c r="E68" s="170"/>
       <c r="F68" s="171"/>
     </row>
-    <row r="69" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="132" t="s">
         <v>40</v>
       </c>
       <c r="F69" s="173"/>
     </row>
-    <row r="70" spans="1:47" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:47" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="135" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="71" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="138" t="s">
         <v>252</v>
       </c>
@@ -5885,7 +5869,7 @@
       <c r="E71" s="174"/>
       <c r="F71" s="156"/>
     </row>
-    <row r="72" spans="1:47" s="143" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:47" s="143" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="143" t="s">
         <v>37</v>
       </c>
@@ -5936,7 +5920,7 @@
       <c r="AT72" s="29"/>
       <c r="AU72" s="29"/>
     </row>
-    <row r="73" spans="1:47" s="143" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:47" s="143" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="143" t="s">
         <v>38</v>
       </c>
@@ -5987,7 +5971,7 @@
       <c r="AT73" s="29"/>
       <c r="AU73" s="29"/>
     </row>
-    <row r="74" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="143" t="s">
         <v>1</v>
       </c>
@@ -5999,17 +5983,17 @@
       <c r="E74" s="138"/>
       <c r="F74" s="140"/>
     </row>
-    <row r="75" spans="1:47" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="301" t="s">
+    <row r="75" spans="1:47" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="306" t="s">
         <v>75</v>
       </c>
-      <c r="B75" s="301"/>
-      <c r="C75" s="301"/>
-      <c r="D75" s="301"/>
-      <c r="E75" s="301"/>
-      <c r="F75" s="301"/>
-    </row>
-    <row r="76" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="306"/>
+      <c r="C75" s="306"/>
+      <c r="D75" s="306"/>
+      <c r="E75" s="306"/>
+      <c r="F75" s="306"/>
+    </row>
+    <row r="76" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="176">
         <v>45075</v>
       </c>
@@ -6021,7 +6005,7 @@
       <c r="E76" s="135"/>
       <c r="F76" s="177"/>
     </row>
-    <row r="77" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="176">
         <v>45082</v>
       </c>
@@ -6033,7 +6017,7 @@
       <c r="E77" s="135"/>
       <c r="F77" s="177"/>
     </row>
-    <row r="78" spans="1:47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="176">
         <v>45108</v>
       </c>
@@ -6045,7 +6029,7 @@
       <c r="E78" s="135"/>
       <c r="F78" s="177"/>
     </row>
-    <row r="79" spans="1:47" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:47" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="146"/>
       <c r="B79" s="146"/>
       <c r="C79" s="146"/>
@@ -6053,7 +6037,7 @@
       <c r="E79" s="146"/>
       <c r="F79" s="147"/>
     </row>
-    <row r="80" spans="1:47" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:47" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="132" t="s">
         <v>234</v>
       </c>
@@ -6063,21 +6047,21 @@
       <c r="E80" s="135"/>
       <c r="F80" s="177"/>
     </row>
-    <row r="81" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="301" t="s">
+    <row r="81" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="306" t="s">
         <v>68</v>
       </c>
-      <c r="B81" s="302" t="s">
+      <c r="B81" s="307" t="s">
         <v>3</v>
       </c>
-      <c r="C81" s="302"/>
-      <c r="E81" s="303" t="s">
+      <c r="C81" s="307"/>
+      <c r="E81" s="308" t="s">
         <v>4</v>
       </c>
-      <c r="F81" s="303"/>
-    </row>
-    <row r="82" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="301"/>
+      <c r="F81" s="308"/>
+    </row>
+    <row r="82" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="306"/>
       <c r="B82" s="149" t="s">
         <v>52</v>
       </c>
@@ -6094,7 +6078,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="143" t="s">
         <v>253</v>
       </c>
@@ -6111,7 +6095,7 @@
       <c r="E83" s="135"/>
       <c r="F83" s="140"/>
     </row>
-    <row r="84" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="143" t="s">
         <v>254</v>
       </c>
@@ -6128,7 +6112,7 @@
       <c r="E84" s="135"/>
       <c r="F84" s="140"/>
     </row>
-    <row r="85" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="143" t="s">
         <v>255</v>
       </c>
@@ -6144,7 +6128,7 @@
       <c r="E85" s="135"/>
       <c r="F85" s="140"/>
     </row>
-    <row r="86" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="143" t="s">
         <v>204</v>
       </c>
@@ -6161,7 +6145,7 @@
       <c r="E86" s="135"/>
       <c r="F86" s="140"/>
     </row>
-    <row r="87" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="143" t="s">
         <v>256</v>
       </c>
@@ -6178,7 +6162,7 @@
       <c r="E87" s="135"/>
       <c r="F87" s="140"/>
     </row>
-    <row r="88" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="143" t="s">
         <v>257</v>
       </c>
@@ -6195,11 +6179,11 @@
       <c r="E88" s="135"/>
       <c r="F88" s="140"/>
     </row>
-    <row r="89" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D89" s="167"/>
       <c r="F89" s="135"/>
     </row>
-    <row r="90" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="143" t="s">
         <v>258</v>
       </c>
@@ -6213,7 +6197,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="146"/>
       <c r="B91" s="146"/>
       <c r="C91" s="146"/>
@@ -6221,7 +6205,7 @@
       <c r="E91" s="146"/>
       <c r="F91" s="147"/>
     </row>
-    <row r="92" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="179" t="s">
         <v>39</v>
       </c>
@@ -6231,7 +6215,7 @@
       <c r="E92" s="135"/>
       <c r="F92" s="177"/>
     </row>
-    <row r="93" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="135" t="s">
         <v>226</v>
       </c>
@@ -6245,7 +6229,7 @@
       <c r="E93" s="180"/>
       <c r="F93" s="181"/>
     </row>
-    <row r="94" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="143" t="s">
         <v>16</v>
       </c>
@@ -6258,7 +6242,7 @@
       <c r="E94" s="138"/>
       <c r="F94" s="139"/>
     </row>
-    <row r="95" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="143" t="s">
         <v>4</v>
       </c>
@@ -6272,12 +6256,12 @@
       <c r="E95" s="138"/>
       <c r="F95" s="139"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="135" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="143" t="s">
         <v>16</v>
       </c>
@@ -6288,12 +6272,12 @@
         <v>261</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="143"/>
       <c r="B98" s="174"/>
       <c r="C98" s="174"/>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="135" t="s">
         <v>262</v>
       </c>
@@ -6330,25 +6314,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O95"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" customWidth="1"/>
-    <col min="2" max="4" width="9.85546875" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="50.81640625" customWidth="1"/>
+    <col min="2" max="4" width="9.81640625" customWidth="1"/>
+    <col min="5" max="5" width="10.81640625" customWidth="1"/>
+    <col min="6" max="6" width="10.81640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="309" t="s">
+    <row r="1" spans="1:7" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="325" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="309"/>
-      <c r="C1" s="309"/>
-      <c r="D1" s="309"/>
-      <c r="E1" s="309"/>
-      <c r="F1" s="309"/>
-    </row>
-    <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="325"/>
+      <c r="C1" s="325"/>
+      <c r="D1" s="325"/>
+      <c r="E1" s="325"/>
+      <c r="F1" s="325"/>
+    </row>
+    <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="3" t="s">
         <v>3</v>
@@ -6366,7 +6350,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="39" t="s">
         <v>32</v>
       </c>
@@ -6376,7 +6360,7 @@
       <c r="E3" s="35"/>
       <c r="F3" s="36"/>
     </row>
-    <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>41</v>
       </c>
@@ -6399,7 +6383,7 @@
       </c>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
@@ -6422,7 +6406,7 @@
       </c>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>42</v>
       </c>
@@ -6445,7 +6429,7 @@
       </c>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="97" t="s">
         <v>208</v>
       </c>
@@ -6468,7 +6452,7 @@
       </c>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>24</v>
       </c>
@@ -6492,7 +6476,7 @@
       </c>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
         <v>49</v>
       </c>
@@ -6515,7 +6499,7 @@
       </c>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
         <v>50</v>
       </c>
@@ -6538,7 +6522,7 @@
       </c>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="17" t="s">
         <v>209</v>
       </c>
@@ -6549,7 +6533,7 @@
       <c r="F11" s="94"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
         <v>205</v>
       </c>
@@ -6570,7 +6554,7 @@
       </c>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
         <v>18</v>
       </c>
@@ -6591,7 +6575,7 @@
       </c>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="48" t="s">
         <v>210</v>
       </c>
@@ -6612,7 +6596,7 @@
       </c>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="59" t="s">
         <v>96</v>
       </c>
@@ -6633,7 +6617,7 @@
       </c>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="59" t="s">
         <v>97</v>
       </c>
@@ -6654,7 +6638,7 @@
       </c>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -6663,7 +6647,7 @@
       <c r="F17" s="15"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="38" t="s">
         <v>31</v>
       </c>
@@ -6674,7 +6658,7 @@
       <c r="F18" s="34"/>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="40"/>
       <c r="B19" s="37"/>
       <c r="C19" s="122" t="s">
@@ -6685,7 +6669,7 @@
       <c r="F19" s="37"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="86" t="s">
         <v>228</v>
       </c>
@@ -6701,7 +6685,7 @@
       <c r="F20" s="23"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="126" t="s">
         <v>231</v>
       </c>
@@ -6712,7 +6696,7 @@
       <c r="F21" s="23"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
         <v>187</v>
       </c>
@@ -6724,7 +6708,7 @@
       <c r="E22" s="8"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
         <v>6</v>
       </c>
@@ -6736,7 +6720,7 @@
       <c r="E23" s="8"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
         <v>7</v>
       </c>
@@ -6748,7 +6732,7 @@
       <c r="E24" s="8"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
         <v>47</v>
       </c>
@@ -6761,16 +6745,16 @@
       <c r="F25" s="91"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="310"/>
-      <c r="B26" s="311"/>
-      <c r="C26" s="311"/>
-      <c r="D26" s="311"/>
-      <c r="E26" s="311"/>
-      <c r="F26" s="311"/>
+    <row r="26" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="326"/>
+      <c r="B26" s="327"/>
+      <c r="C26" s="327"/>
+      <c r="D26" s="327"/>
+      <c r="E26" s="327"/>
+      <c r="F26" s="327"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>230</v>
       </c>
@@ -6786,7 +6770,7 @@
       <c r="F27" s="90"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="108" t="s">
         <v>216</v>
       </c>
@@ -6797,7 +6781,7 @@
       <c r="F28" s="65"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
         <v>232</v>
       </c>
@@ -6810,7 +6794,7 @@
       <c r="F29" s="91"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="29" t="s">
         <v>55</v>
       </c>
@@ -6823,7 +6807,7 @@
       <c r="F30" s="91"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
         <v>56</v>
       </c>
@@ -6836,7 +6820,7 @@
       <c r="F31" s="91"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="29" t="s">
         <v>211</v>
       </c>
@@ -6849,27 +6833,27 @@
       <c r="F32" s="91"/>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="312"/>
-      <c r="B33" s="307"/>
-      <c r="C33" s="307"/>
-      <c r="D33" s="307"/>
-      <c r="E33" s="307"/>
-      <c r="F33" s="308"/>
+    <row r="33" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="328"/>
+      <c r="B33" s="323"/>
+      <c r="C33" s="323"/>
+      <c r="D33" s="323"/>
+      <c r="E33" s="323"/>
+      <c r="F33" s="324"/>
       <c r="G33" s="1"/>
     </row>
-    <row r="34" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="307"/>
-      <c r="C34" s="307"/>
-      <c r="D34" s="307"/>
-      <c r="E34" s="307"/>
-      <c r="F34" s="308"/>
+      <c r="B34" s="323"/>
+      <c r="C34" s="323"/>
+      <c r="D34" s="323"/>
+      <c r="E34" s="323"/>
+      <c r="F34" s="324"/>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="1:7" s="106" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" s="106" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="100" t="s">
         <v>214</v>
       </c>
@@ -6882,7 +6866,7 @@
       <c r="F35" s="104"/>
       <c r="G35" s="105"/>
     </row>
-    <row r="36" spans="1:7" s="106" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" s="106" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="107" t="s">
         <v>215</v>
       </c>
@@ -6895,7 +6879,7 @@
       <c r="F36" s="104"/>
       <c r="G36" s="105"/>
     </row>
-    <row r="37" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="48"/>
       <c r="B37" s="18"/>
       <c r="C37" s="22"/>
@@ -6904,16 +6888,16 @@
       <c r="F37" s="27"/>
       <c r="G37" s="1"/>
     </row>
-    <row r="38" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="313"/>
-      <c r="B38" s="314"/>
-      <c r="C38" s="314"/>
-      <c r="D38" s="314"/>
-      <c r="E38" s="314"/>
-      <c r="F38" s="315"/>
+    <row r="38" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="312"/>
+      <c r="B38" s="313"/>
+      <c r="C38" s="313"/>
+      <c r="D38" s="313"/>
+      <c r="E38" s="313"/>
+      <c r="F38" s="314"/>
       <c r="G38" s="1"/>
     </row>
-    <row r="39" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="110" t="s">
         <v>217</v>
       </c>
@@ -6924,7 +6908,7 @@
       <c r="F39" s="34"/>
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="49" t="s">
         <v>43</v>
       </c>
@@ -6939,7 +6923,7 @@
       <c r="F40" s="34"/>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="49" t="s">
         <v>44</v>
       </c>
@@ -6954,7 +6938,7 @@
       <c r="F41" s="34"/>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
         <v>60</v>
       </c>
@@ -6969,7 +6953,7 @@
       <c r="F42" s="8"/>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
         <v>197</v>
       </c>
@@ -6984,7 +6968,7 @@
       <c r="F43" s="8"/>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
         <v>9</v>
       </c>
@@ -6999,7 +6983,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="1"/>
     </row>
-    <row r="45" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
         <v>196</v>
       </c>
@@ -7014,7 +6998,7 @@
       <c r="F45" s="8"/>
       <c r="G45" s="1"/>
     </row>
-    <row r="46" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
         <v>10</v>
       </c>
@@ -7029,7 +7013,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="1"/>
     </row>
-    <row r="47" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
         <v>194</v>
       </c>
@@ -7044,7 +7028,7 @@
       <c r="F47" s="8"/>
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
         <v>61</v>
       </c>
@@ -7059,7 +7043,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="1"/>
     </row>
-    <row r="49" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="17" t="s">
         <v>195</v>
       </c>
@@ -7074,16 +7058,16 @@
       <c r="F49" s="8"/>
       <c r="G49" s="1"/>
     </row>
-    <row r="50" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="313"/>
-      <c r="B50" s="314"/>
-      <c r="C50" s="314"/>
-      <c r="D50" s="314"/>
-      <c r="E50" s="314"/>
-      <c r="F50" s="315"/>
+    <row r="50" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="312"/>
+      <c r="B50" s="313"/>
+      <c r="C50" s="313"/>
+      <c r="D50" s="313"/>
+      <c r="E50" s="313"/>
+      <c r="F50" s="314"/>
       <c r="G50" s="1"/>
     </row>
-    <row r="51" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="40" t="s">
         <v>45</v>
       </c>
@@ -7093,7 +7077,7 @@
       <c r="E51" s="37"/>
       <c r="F51" s="37"/>
     </row>
-    <row r="52" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="54" t="s">
         <v>88</v>
       </c>
@@ -7103,7 +7087,7 @@
       <c r="E52" s="37"/>
       <c r="F52" s="37"/>
     </row>
-    <row r="53" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="29" t="s">
         <v>25</v>
       </c>
@@ -7112,7 +7096,7 @@
       </c>
       <c r="E53" s="5"/>
     </row>
-    <row r="54" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="29" t="s">
         <v>26</v>
       </c>
@@ -7121,7 +7105,7 @@
       </c>
       <c r="E54" s="5"/>
     </row>
-    <row r="55" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="18" t="s">
         <v>80</v>
       </c>
@@ -7131,7 +7115,7 @@
       <c r="E55" s="18"/>
       <c r="F55" s="23"/>
     </row>
-    <row r="56" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="29" t="s">
         <v>25</v>
       </c>
@@ -7139,7 +7123,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="29" t="s">
         <v>26</v>
       </c>
@@ -7147,7 +7131,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="42"/>
       <c r="B58" s="43"/>
       <c r="C58" s="30"/>
@@ -7155,18 +7139,18 @@
       <c r="E58" s="30"/>
       <c r="F58" s="31"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="40" t="s">
         <v>46</v>
       </c>
       <c r="B59" s="28"/>
     </row>
-    <row r="60" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="32" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="29" t="s">
         <v>25</v>
       </c>
@@ -7175,7 +7159,7 @@
       </c>
       <c r="E61" s="5"/>
     </row>
-    <row r="62" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="29" t="s">
         <v>26</v>
       </c>
@@ -7184,7 +7168,7 @@
       </c>
       <c r="E62" s="5"/>
     </row>
-    <row r="63" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="18" t="s">
         <v>35</v>
       </c>
@@ -7194,7 +7178,7 @@
       <c r="E63" s="18"/>
       <c r="F63" s="23"/>
     </row>
-    <row r="64" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="29" t="s">
         <v>25</v>
       </c>
@@ -7206,7 +7190,7 @@
       <c r="E64" s="18"/>
       <c r="F64" s="23"/>
     </row>
-    <row r="65" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="29" t="s">
         <v>26</v>
       </c>
@@ -7218,7 +7202,7 @@
       <c r="E65" s="18"/>
       <c r="F65" s="23"/>
     </row>
-    <row r="66" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="30"/>
       <c r="B66" s="30"/>
       <c r="C66" s="30"/>
@@ -7226,18 +7210,18 @@
       <c r="E66" s="30"/>
       <c r="F66" s="31"/>
     </row>
-    <row r="67" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="40" t="s">
         <v>40</v>
       </c>
       <c r="F67" s="47"/>
     </row>
-    <row r="68" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="18" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="69" spans="1:15" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:15" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="29" t="s">
         <v>37</v>
       </c>
@@ -7247,7 +7231,7 @@
       <c r="C69" s="28"/>
       <c r="F69" s="41"/>
     </row>
-    <row r="70" spans="1:15" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:15" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="29" t="s">
         <v>38</v>
       </c>
@@ -7257,7 +7241,7 @@
       <c r="C70" s="28"/>
       <c r="F70" s="41"/>
     </row>
-    <row r="71" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="9" t="s">
         <v>1</v>
       </c>
@@ -7270,18 +7254,18 @@
       <c r="F71" s="8"/>
       <c r="G71" s="1"/>
     </row>
-    <row r="72" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="316" t="s">
+    <row r="72" spans="1:15" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="315" t="s">
         <v>75</v>
       </c>
-      <c r="B72" s="317"/>
-      <c r="C72" s="317"/>
-      <c r="D72" s="317"/>
-      <c r="E72" s="317"/>
-      <c r="F72" s="318"/>
+      <c r="B72" s="316"/>
+      <c r="C72" s="316"/>
+      <c r="D72" s="316"/>
+      <c r="E72" s="316"/>
+      <c r="F72" s="317"/>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="58">
         <v>44709</v>
       </c>
@@ -7294,7 +7278,7 @@
       <c r="F73" s="44"/>
       <c r="G73" s="1"/>
     </row>
-    <row r="74" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="58">
         <v>44715</v>
       </c>
@@ -7311,7 +7295,7 @@
       <c r="M74" s="114"/>
       <c r="O74" s="114"/>
     </row>
-    <row r="75" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="58">
         <v>44741</v>
       </c>
@@ -7327,7 +7311,7 @@
       <c r="K75" s="114"/>
       <c r="M75" s="114"/>
     </row>
-    <row r="76" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="13"/>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
@@ -7336,7 +7320,7 @@
       <c r="F76" s="15"/>
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="38" t="s">
         <v>225</v>
       </c>
@@ -7347,22 +7331,22 @@
       <c r="F77" s="44"/>
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="319" t="s">
+    <row r="78" spans="1:15" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="318" t="s">
         <v>68</v>
       </c>
-      <c r="B78" s="321" t="s">
+      <c r="B78" s="320" t="s">
         <v>3</v>
       </c>
-      <c r="C78" s="321"/>
-      <c r="E78" s="322" t="s">
+      <c r="C78" s="320"/>
+      <c r="E78" s="321" t="s">
         <v>4</v>
       </c>
-      <c r="F78" s="323"/>
+      <c r="F78" s="322"/>
       <c r="G78" s="1"/>
     </row>
-    <row r="79" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="320"/>
+    <row r="79" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="319"/>
       <c r="B79" s="52" t="s">
         <v>52</v>
       </c>
@@ -7380,7 +7364,7 @@
       </c>
       <c r="G79" s="1"/>
     </row>
-    <row r="80" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="9" t="s">
         <v>11</v>
       </c>
@@ -7398,7 +7382,7 @@
       <c r="F80" s="53"/>
       <c r="G80" s="1"/>
     </row>
-    <row r="81" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="9" t="s">
         <v>63</v>
       </c>
@@ -7416,7 +7400,7 @@
       <c r="F81" s="53"/>
       <c r="G81" s="1"/>
     </row>
-    <row r="82" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="9" t="s">
         <v>13</v>
       </c>
@@ -7434,7 +7418,7 @@
       <c r="F82" s="53"/>
       <c r="G82" s="1"/>
     </row>
-    <row r="83" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="9" t="s">
         <v>12</v>
       </c>
@@ -7452,7 +7436,7 @@
       <c r="F83" s="53"/>
       <c r="G83" s="1"/>
     </row>
-    <row r="84" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="16" t="s">
         <v>199</v>
       </c>
@@ -7470,7 +7454,7 @@
       <c r="F84" s="53"/>
       <c r="G84" s="1"/>
     </row>
-    <row r="85" spans="1:7" s="106" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" s="106" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="115" t="s">
         <v>233</v>
       </c>
@@ -7487,11 +7471,11 @@
       <c r="F85" s="119"/>
       <c r="G85" s="105"/>
     </row>
-    <row r="86" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F86" s="6"/>
       <c r="G86" s="1"/>
     </row>
-    <row r="87" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="9" t="s">
         <v>67</v>
       </c>
@@ -7506,7 +7490,7 @@
       </c>
       <c r="G87" s="1"/>
     </row>
-    <row r="88" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="13"/>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
@@ -7515,7 +7499,7 @@
       <c r="F88" s="15"/>
       <c r="G88" s="1"/>
     </row>
-    <row r="89" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="46" t="s">
         <v>39</v>
       </c>
@@ -7526,7 +7510,7 @@
       <c r="F89" s="45"/>
       <c r="G89" s="1"/>
     </row>
-    <row r="90" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="6" t="s">
         <v>226</v>
       </c>
@@ -7541,7 +7525,7 @@
       <c r="F90" s="50"/>
       <c r="G90" s="1"/>
     </row>
-    <row r="91" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="21" t="s">
         <v>16</v>
       </c>
@@ -7556,7 +7540,7 @@
       <c r="F91" s="12"/>
       <c r="G91" s="1"/>
     </row>
-    <row r="92" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="21" t="s">
         <v>4</v>
       </c>
@@ -7571,12 +7555,12 @@
       <c r="F92" s="12"/>
       <c r="G92" s="1"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="18" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="21" t="s">
         <v>16</v>
       </c>
@@ -7587,23 +7571,23 @@
         <v>17</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="29"/>
       <c r="B95" s="120"/>
       <c r="C95" s="120"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A50:F50"/>
     <mergeCell ref="A72:F72"/>
     <mergeCell ref="A78:A79"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="E78:F78"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A38:F38"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7625,25 +7609,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G96"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="2" max="4" width="9.85546875" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="50.7265625" customWidth="1"/>
+    <col min="2" max="4" width="9.81640625" customWidth="1"/>
+    <col min="5" max="5" width="10.81640625" customWidth="1"/>
+    <col min="6" max="6" width="10.81640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="309" t="s">
+    <row r="1" spans="1:7" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="325" t="s">
         <v>185</v>
       </c>
-      <c r="B1" s="309"/>
-      <c r="C1" s="309"/>
-      <c r="D1" s="309"/>
-      <c r="E1" s="309"/>
-      <c r="F1" s="309"/>
-    </row>
-    <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="325"/>
+      <c r="C1" s="325"/>
+      <c r="D1" s="325"/>
+      <c r="E1" s="325"/>
+      <c r="F1" s="325"/>
+    </row>
+    <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="3" t="s">
         <v>3</v>
@@ -7661,7 +7645,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="39" t="s">
         <v>32</v>
       </c>
@@ -7671,7 +7655,7 @@
       <c r="E3" s="35"/>
       <c r="F3" s="36"/>
     </row>
-    <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>41</v>
       </c>
@@ -7689,7 +7673,7 @@
       <c r="F4" s="7"/>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
@@ -7710,7 +7694,7 @@
       </c>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>42</v>
       </c>
@@ -7732,7 +7716,7 @@
       </c>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>24</v>
       </c>
@@ -7753,7 +7737,7 @@
       </c>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="s">
         <v>49</v>
       </c>
@@ -7775,7 +7759,7 @@
       </c>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
         <v>206</v>
       </c>
@@ -7786,7 +7770,7 @@
       <c r="F9" s="23"/>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
         <v>205</v>
       </c>
@@ -7799,7 +7783,7 @@
       <c r="F10" s="23"/>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
         <v>18</v>
       </c>
@@ -7812,7 +7796,7 @@
       <c r="F11" s="23"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="17" t="s">
         <v>50</v>
       </c>
@@ -7833,7 +7817,7 @@
       </c>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="59" t="s">
         <v>96</v>
       </c>
@@ -7848,7 +7832,7 @@
       <c r="F13" s="56"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="59" t="s">
         <v>97</v>
       </c>
@@ -7863,7 +7847,7 @@
       <c r="F14" s="56"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
@@ -7872,7 +7856,7 @@
       <c r="F15" s="15"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="38" t="s">
         <v>31</v>
       </c>
@@ -7883,7 +7867,7 @@
       <c r="F16" s="34"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="86" t="s">
         <v>186</v>
       </c>
@@ -7907,18 +7891,18 @@
       </c>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="324"/>
-      <c r="C18" s="322"/>
-      <c r="D18" s="322"/>
-      <c r="E18" s="322"/>
-      <c r="F18" s="323"/>
+      <c r="B18" s="329"/>
+      <c r="C18" s="321"/>
+      <c r="D18" s="321"/>
+      <c r="E18" s="321"/>
+      <c r="F18" s="322"/>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>7</v>
       </c>
@@ -7939,7 +7923,7 @@
       </c>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>6</v>
       </c>
@@ -7960,7 +7944,7 @@
       </c>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>47</v>
       </c>
@@ -7980,7 +7964,7 @@
       </c>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
         <v>187</v>
       </c>
@@ -8001,16 +7985,16 @@
       </c>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="310"/>
-      <c r="B23" s="311"/>
-      <c r="C23" s="311"/>
-      <c r="D23" s="311"/>
-      <c r="E23" s="311"/>
-      <c r="F23" s="311"/>
+    <row r="23" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="326"/>
+      <c r="B23" s="327"/>
+      <c r="C23" s="327"/>
+      <c r="D23" s="327"/>
+      <c r="E23" s="327"/>
+      <c r="F23" s="327"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>188</v>
       </c>
@@ -8030,18 +8014,18 @@
       </c>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="324"/>
-      <c r="C25" s="322"/>
-      <c r="D25" s="322"/>
-      <c r="E25" s="322"/>
-      <c r="F25" s="323"/>
+      <c r="B25" s="329"/>
+      <c r="C25" s="321"/>
+      <c r="D25" s="321"/>
+      <c r="E25" s="321"/>
+      <c r="F25" s="322"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
         <v>55</v>
       </c>
@@ -8061,7 +8045,7 @@
       </c>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
         <v>58</v>
       </c>
@@ -8081,7 +8065,7 @@
       </c>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="29" t="s">
         <v>191</v>
       </c>
@@ -8101,7 +8085,7 @@
       </c>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
         <v>190</v>
       </c>
@@ -8121,7 +8105,7 @@
       </c>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
         <v>189</v>
       </c>
@@ -8141,27 +8125,27 @@
       </c>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="312"/>
-      <c r="B31" s="307"/>
-      <c r="C31" s="307"/>
-      <c r="D31" s="307"/>
-      <c r="E31" s="307"/>
-      <c r="F31" s="308"/>
+    <row r="31" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="328"/>
+      <c r="B31" s="323"/>
+      <c r="C31" s="323"/>
+      <c r="D31" s="323"/>
+      <c r="E31" s="323"/>
+      <c r="F31" s="324"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="307"/>
-      <c r="C32" s="307"/>
-      <c r="D32" s="307"/>
-      <c r="E32" s="307"/>
-      <c r="F32" s="308"/>
+      <c r="B32" s="323"/>
+      <c r="C32" s="323"/>
+      <c r="D32" s="323"/>
+      <c r="E32" s="323"/>
+      <c r="F32" s="324"/>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="29" t="s">
         <v>160</v>
       </c>
@@ -8176,7 +8160,7 @@
       <c r="F33" s="27"/>
       <c r="G33" s="1"/>
     </row>
-    <row r="34" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="21" t="s">
         <v>192</v>
       </c>
@@ -8191,7 +8175,7 @@
       <c r="F34" s="27"/>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="48" t="s">
         <v>193</v>
       </c>
@@ -8206,16 +8190,16 @@
       <c r="F35" s="27"/>
       <c r="G35" s="1"/>
     </row>
-    <row r="36" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="313"/>
-      <c r="B36" s="314"/>
-      <c r="C36" s="314"/>
-      <c r="D36" s="314"/>
-      <c r="E36" s="314"/>
-      <c r="F36" s="315"/>
+    <row r="36" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="312"/>
+      <c r="B36" s="313"/>
+      <c r="C36" s="313"/>
+      <c r="D36" s="313"/>
+      <c r="E36" s="313"/>
+      <c r="F36" s="314"/>
       <c r="G36" s="1"/>
     </row>
-    <row r="37" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="38" t="s">
         <v>59</v>
       </c>
@@ -8226,7 +8210,7 @@
       <c r="F37" s="34"/>
       <c r="G37" s="1"/>
     </row>
-    <row r="38" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="49" t="s">
         <v>43</v>
       </c>
@@ -8241,7 +8225,7 @@
       <c r="F38" s="34"/>
       <c r="G38" s="1"/>
     </row>
-    <row r="39" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="49" t="s">
         <v>44</v>
       </c>
@@ -8256,7 +8240,7 @@
       <c r="F39" s="34"/>
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
         <v>60</v>
       </c>
@@ -8271,7 +8255,7 @@
       <c r="F40" s="8"/>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
         <v>197</v>
       </c>
@@ -8286,7 +8270,7 @@
       <c r="F41" s="8"/>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
         <v>9</v>
       </c>
@@ -8301,7 +8285,7 @@
       <c r="F42" s="8"/>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
         <v>196</v>
       </c>
@@ -8316,7 +8300,7 @@
       <c r="F43" s="8"/>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
         <v>10</v>
       </c>
@@ -8331,7 +8315,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="1"/>
     </row>
-    <row r="45" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
         <v>194</v>
       </c>
@@ -8346,7 +8330,7 @@
       <c r="F45" s="8"/>
       <c r="G45" s="1"/>
     </row>
-    <row r="46" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
         <v>61</v>
       </c>
@@ -8361,7 +8345,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="1"/>
     </row>
-    <row r="47" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="17" t="s">
         <v>195</v>
       </c>
@@ -8376,16 +8360,16 @@
       <c r="F47" s="8"/>
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="313"/>
-      <c r="B48" s="314"/>
-      <c r="C48" s="314"/>
-      <c r="D48" s="314"/>
-      <c r="E48" s="314"/>
-      <c r="F48" s="315"/>
+    <row r="48" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="312"/>
+      <c r="B48" s="313"/>
+      <c r="C48" s="313"/>
+      <c r="D48" s="313"/>
+      <c r="E48" s="313"/>
+      <c r="F48" s="314"/>
       <c r="G48" s="1"/>
     </row>
-    <row r="49" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="40" t="s">
         <v>45</v>
       </c>
@@ -8395,7 +8379,7 @@
       <c r="E49" s="37"/>
       <c r="F49" s="37"/>
     </row>
-    <row r="50" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="54" t="s">
         <v>88</v>
       </c>
@@ -8407,7 +8391,7 @@
       <c r="E50" s="37"/>
       <c r="F50" s="37"/>
     </row>
-    <row r="51" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="29" t="s">
         <v>25</v>
       </c>
@@ -8418,7 +8402,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="29" t="s">
         <v>26</v>
       </c>
@@ -8429,7 +8413,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="18" t="s">
         <v>80</v>
       </c>
@@ -8439,7 +8423,7 @@
       <c r="E53" s="18"/>
       <c r="F53" s="23"/>
     </row>
-    <row r="54" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="29" t="s">
         <v>25</v>
       </c>
@@ -8447,7 +8431,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="29" t="s">
         <v>26</v>
       </c>
@@ -8455,7 +8439,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="42"/>
       <c r="B56" s="43"/>
       <c r="C56" s="30"/>
@@ -8463,13 +8447,13 @@
       <c r="E56" s="30"/>
       <c r="F56" s="31"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="40" t="s">
         <v>46</v>
       </c>
       <c r="B57" s="28"/>
     </row>
-    <row r="58" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="32" t="s">
         <v>34</v>
       </c>
@@ -8477,7 +8461,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="29" t="s">
         <v>25</v>
       </c>
@@ -8486,7 +8470,7 @@
       </c>
       <c r="E59" s="5"/>
     </row>
-    <row r="60" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="29" t="s">
         <v>26</v>
       </c>
@@ -8495,7 +8479,7 @@
       </c>
       <c r="E60" s="5"/>
     </row>
-    <row r="61" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="18" t="s">
         <v>35</v>
       </c>
@@ -8505,7 +8489,7 @@
       <c r="E61" s="18"/>
       <c r="F61" s="23"/>
     </row>
-    <row r="62" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="29" t="s">
         <v>25</v>
       </c>
@@ -8517,7 +8501,7 @@
       <c r="E62" s="18"/>
       <c r="F62" s="23"/>
     </row>
-    <row r="63" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="29" t="s">
         <v>26</v>
       </c>
@@ -8529,7 +8513,7 @@
       <c r="E63" s="18"/>
       <c r="F63" s="23"/>
     </row>
-    <row r="64" spans="1:6" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="30"/>
       <c r="B64" s="30"/>
       <c r="C64" s="30"/>
@@ -8537,18 +8521,18 @@
       <c r="E64" s="30"/>
       <c r="F64" s="31"/>
     </row>
-    <row r="65" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="40" t="s">
         <v>40</v>
       </c>
       <c r="F65" s="47"/>
     </row>
-    <row r="66" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="18" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="67" spans="1:7" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="29" t="s">
         <v>37</v>
       </c>
@@ -8560,7 +8544,7 @@
       </c>
       <c r="F67" s="41"/>
     </row>
-    <row r="68" spans="1:7" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="29" t="s">
         <v>38</v>
       </c>
@@ -8572,7 +8556,7 @@
       </c>
       <c r="F68" s="41"/>
     </row>
-    <row r="69" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="9" t="s">
         <v>1</v>
       </c>
@@ -8587,18 +8571,18 @@
       <c r="F69" s="8"/>
       <c r="G69" s="1"/>
     </row>
-    <row r="70" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="316" t="s">
+    <row r="70" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="315" t="s">
         <v>75</v>
       </c>
-      <c r="B70" s="317"/>
-      <c r="C70" s="317"/>
-      <c r="D70" s="317"/>
-      <c r="E70" s="317"/>
-      <c r="F70" s="318"/>
+      <c r="B70" s="316"/>
+      <c r="C70" s="316"/>
+      <c r="D70" s="316"/>
+      <c r="E70" s="316"/>
+      <c r="F70" s="317"/>
       <c r="G70" s="1"/>
     </row>
-    <row r="71" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="58">
         <v>44347</v>
       </c>
@@ -8611,7 +8595,7 @@
       <c r="F71" s="44"/>
       <c r="G71" s="1"/>
     </row>
-    <row r="72" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="58">
         <v>44349</v>
       </c>
@@ -8624,7 +8608,7 @@
       <c r="F72" s="44"/>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="58">
         <v>44358</v>
       </c>
@@ -8637,7 +8621,7 @@
       <c r="F73" s="44"/>
       <c r="G73" s="1"/>
     </row>
-    <row r="74" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="58">
         <v>44359</v>
       </c>
@@ -8650,7 +8634,7 @@
       <c r="F74" s="44"/>
       <c r="G74" s="1"/>
     </row>
-    <row r="75" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="13"/>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
@@ -8659,7 +8643,7 @@
       <c r="F75" s="15"/>
       <c r="G75" s="1"/>
     </row>
-    <row r="76" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="38" t="s">
         <v>62</v>
       </c>
@@ -8670,22 +8654,22 @@
       <c r="F76" s="44"/>
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="319" t="s">
+    <row r="77" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="318" t="s">
         <v>68</v>
       </c>
-      <c r="B77" s="321" t="s">
+      <c r="B77" s="320" t="s">
         <v>3</v>
       </c>
-      <c r="C77" s="321"/>
-      <c r="E77" s="322" t="s">
+      <c r="C77" s="320"/>
+      <c r="E77" s="321" t="s">
         <v>4</v>
       </c>
-      <c r="F77" s="323"/>
+      <c r="F77" s="322"/>
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="320"/>
+    <row r="78" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="319"/>
       <c r="B78" s="52" t="s">
         <v>52</v>
       </c>
@@ -8703,7 +8687,7 @@
       </c>
       <c r="G78" s="1"/>
     </row>
-    <row r="79" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="9" t="s">
         <v>11</v>
       </c>
@@ -8721,7 +8705,7 @@
       <c r="F79" s="53"/>
       <c r="G79" s="1"/>
     </row>
-    <row r="80" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="9" t="s">
         <v>63</v>
       </c>
@@ -8739,7 +8723,7 @@
       <c r="F80" s="53"/>
       <c r="G80" s="1"/>
     </row>
-    <row r="81" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="9" t="s">
         <v>13</v>
       </c>
@@ -8757,7 +8741,7 @@
       <c r="F81" s="6"/>
       <c r="G81" s="1"/>
     </row>
-    <row r="82" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="9" t="s">
         <v>12</v>
       </c>
@@ -8775,7 +8759,7 @@
       <c r="F82" s="6"/>
       <c r="G82" s="1"/>
     </row>
-    <row r="83" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="16" t="s">
         <v>199</v>
       </c>
@@ -8793,7 +8777,7 @@
       <c r="F83" s="6"/>
       <c r="G83" s="1"/>
     </row>
-    <row r="84" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="16" t="s">
         <v>200</v>
       </c>
@@ -8810,7 +8794,7 @@
       <c r="E84" s="18"/>
       <c r="F84" s="18"/>
     </row>
-    <row r="85" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="16" t="s">
         <v>204</v>
       </c>
@@ -8831,7 +8815,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="16" t="s">
         <v>201</v>
       </c>
@@ -8848,7 +8832,7 @@
       <c r="E86" s="28"/>
       <c r="F86" s="28"/>
     </row>
-    <row r="87" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="9" t="s">
         <v>203</v>
       </c>
@@ -8870,7 +8854,7 @@
       </c>
       <c r="G87" s="1"/>
     </row>
-    <row r="88" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="16" t="s">
         <v>202</v>
       </c>
@@ -8888,7 +8872,7 @@
       <c r="F88" s="10"/>
       <c r="G88" s="1"/>
     </row>
-    <row r="89" spans="1:7" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="16"/>
       <c r="B89" s="6"/>
       <c r="C89" s="10"/>
@@ -8897,7 +8881,7 @@
       <c r="F89" s="10"/>
       <c r="G89" s="1"/>
     </row>
-    <row r="90" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="16" t="s">
         <v>66</v>
       </c>
@@ -8912,7 +8896,7 @@
       </c>
       <c r="G90" s="1"/>
     </row>
-    <row r="91" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="9" t="s">
         <v>67</v>
       </c>
@@ -8927,7 +8911,7 @@
       </c>
       <c r="G91" s="1"/>
     </row>
-    <row r="92" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="13"/>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
@@ -8936,7 +8920,7 @@
       <c r="F92" s="15"/>
       <c r="G92" s="1"/>
     </row>
-    <row r="93" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="46" t="s">
         <v>39</v>
       </c>
@@ -8947,7 +8931,7 @@
       <c r="F93" s="45"/>
       <c r="G93" s="1"/>
     </row>
-    <row r="94" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="6" t="s">
         <v>53</v>
       </c>
@@ -8962,7 +8946,7 @@
       <c r="F94" s="50"/>
       <c r="G94" s="1"/>
     </row>
-    <row r="95" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="21" t="s">
         <v>16</v>
       </c>
@@ -8977,7 +8961,7 @@
       <c r="F95" s="12"/>
       <c r="G95" s="1"/>
     </row>
-    <row r="96" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="21" t="s">
         <v>4</v>
       </c>
@@ -8994,18 +8978,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="E77:F77"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A70:F70"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="E77:F77"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9024,25 +9008,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G90"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="43.42578125" customWidth="1"/>
-    <col min="2" max="4" width="9.85546875" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="43.453125" customWidth="1"/>
+    <col min="2" max="4" width="9.81640625" customWidth="1"/>
+    <col min="5" max="5" width="10.81640625" customWidth="1"/>
+    <col min="6" max="6" width="10.81640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="309" t="s">
+    <row r="1" spans="1:7" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="325" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="309"/>
-      <c r="C1" s="309"/>
-      <c r="D1" s="309"/>
-      <c r="E1" s="309"/>
-      <c r="F1" s="309"/>
-    </row>
-    <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="325"/>
+      <c r="C1" s="325"/>
+      <c r="D1" s="325"/>
+      <c r="E1" s="325"/>
+      <c r="F1" s="325"/>
+    </row>
+    <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="3" t="s">
         <v>3</v>
@@ -9060,7 +9044,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="39" t="s">
         <v>32</v>
       </c>
@@ -9070,7 +9054,7 @@
       <c r="E3" s="35"/>
       <c r="F3" s="36"/>
     </row>
-    <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>41</v>
       </c>
@@ -9088,7 +9072,7 @@
       <c r="F4" s="7"/>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
@@ -9108,7 +9092,7 @@
       <c r="F5" s="56"/>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>42</v>
       </c>
@@ -9128,7 +9112,7 @@
       <c r="F6" s="23"/>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>2</v>
       </c>
@@ -9148,7 +9132,7 @@
       <c r="F7" s="56"/>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>24</v>
       </c>
@@ -9171,7 +9155,7 @@
       </c>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
         <v>49</v>
       </c>
@@ -9194,7 +9178,7 @@
       </c>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
         <v>50</v>
       </c>
@@ -9214,7 +9198,7 @@
       <c r="F10" s="56"/>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="59" t="s">
         <v>96</v>
       </c>
@@ -9229,7 +9213,7 @@
       <c r="F11" s="56"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="59" t="s">
         <v>97</v>
       </c>
@@ -9244,7 +9228,7 @@
       <c r="F12" s="56"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="13"/>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
@@ -9253,7 +9237,7 @@
       <c r="F13" s="15"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="38" t="s">
         <v>31</v>
       </c>
@@ -9264,7 +9248,7 @@
       <c r="F14" s="34"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="61" t="s">
         <v>98</v>
       </c>
@@ -9283,18 +9267,18 @@
       </c>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="324"/>
-      <c r="C16" s="322"/>
-      <c r="D16" s="322"/>
-      <c r="E16" s="322"/>
-      <c r="F16" s="323"/>
+      <c r="B16" s="329"/>
+      <c r="C16" s="321"/>
+      <c r="D16" s="321"/>
+      <c r="E16" s="321"/>
+      <c r="F16" s="322"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
         <v>7</v>
       </c>
@@ -9304,7 +9288,7 @@
       <c r="E17" s="8"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>6</v>
       </c>
@@ -9314,7 +9298,7 @@
       <c r="E18" s="8"/>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>8</v>
       </c>
@@ -9324,7 +9308,7 @@
       <c r="E19" s="8"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>47</v>
       </c>
@@ -9334,16 +9318,16 @@
       <c r="E20" s="8"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="310"/>
-      <c r="B21" s="311"/>
-      <c r="C21" s="311"/>
-      <c r="D21" s="311"/>
-      <c r="E21" s="311"/>
-      <c r="F21" s="311"/>
+    <row r="21" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="326"/>
+      <c r="B21" s="327"/>
+      <c r="C21" s="327"/>
+      <c r="D21" s="327"/>
+      <c r="E21" s="327"/>
+      <c r="F21" s="327"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>54</v>
       </c>
@@ -9366,18 +9350,18 @@
       </c>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="324"/>
-      <c r="C23" s="322"/>
-      <c r="D23" s="322"/>
-      <c r="E23" s="322"/>
-      <c r="F23" s="323"/>
+      <c r="B23" s="329"/>
+      <c r="C23" s="321"/>
+      <c r="D23" s="321"/>
+      <c r="E23" s="321"/>
+      <c r="F23" s="322"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
         <v>55</v>
       </c>
@@ -9394,7 +9378,7 @@
       </c>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
         <v>56</v>
       </c>
@@ -9411,7 +9395,7 @@
       </c>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
         <v>48</v>
       </c>
@@ -9428,7 +9412,7 @@
       </c>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
         <v>57</v>
       </c>
@@ -9444,7 +9428,7 @@
       </c>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="21" t="s">
         <v>58</v>
       </c>
@@ -9460,27 +9444,27 @@
       </c>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="312"/>
-      <c r="B29" s="307"/>
-      <c r="C29" s="307"/>
-      <c r="D29" s="307"/>
-      <c r="E29" s="307"/>
-      <c r="F29" s="308"/>
+    <row r="29" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="328"/>
+      <c r="B29" s="323"/>
+      <c r="C29" s="323"/>
+      <c r="D29" s="323"/>
+      <c r="E29" s="323"/>
+      <c r="F29" s="324"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="307"/>
-      <c r="C30" s="307"/>
-      <c r="D30" s="307"/>
-      <c r="E30" s="307"/>
-      <c r="F30" s="308"/>
+      <c r="B30" s="323"/>
+      <c r="C30" s="323"/>
+      <c r="D30" s="323"/>
+      <c r="E30" s="323"/>
+      <c r="F30" s="324"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="21" t="s">
         <v>71</v>
       </c>
@@ -9491,7 +9475,7 @@
       <c r="F31" s="27"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="48" t="s">
         <v>72</v>
       </c>
@@ -9502,7 +9486,7 @@
       <c r="F32" s="27"/>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="21" t="s">
         <v>73</v>
       </c>
@@ -9513,16 +9497,16 @@
       <c r="F33" s="27"/>
       <c r="G33" s="1"/>
     </row>
-    <row r="34" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="313"/>
-      <c r="B34" s="314"/>
-      <c r="C34" s="314"/>
-      <c r="D34" s="314"/>
-      <c r="E34" s="314"/>
-      <c r="F34" s="315"/>
+    <row r="34" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="312"/>
+      <c r="B34" s="313"/>
+      <c r="C34" s="313"/>
+      <c r="D34" s="313"/>
+      <c r="E34" s="313"/>
+      <c r="F34" s="314"/>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="38" t="s">
         <v>59</v>
       </c>
@@ -9533,7 +9517,7 @@
       <c r="F35" s="34"/>
       <c r="G35" s="1"/>
     </row>
-    <row r="36" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="49" t="s">
         <v>43</v>
       </c>
@@ -9548,7 +9532,7 @@
       <c r="F36" s="34"/>
       <c r="G36" s="1"/>
     </row>
-    <row r="37" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="49" t="s">
         <v>44</v>
       </c>
@@ -9563,7 +9547,7 @@
       <c r="F37" s="34"/>
       <c r="G37" s="1"/>
     </row>
-    <row r="38" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
         <v>60</v>
       </c>
@@ -9578,7 +9562,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="1"/>
     </row>
-    <row r="39" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
         <v>9</v>
       </c>
@@ -9593,7 +9577,7 @@
       <c r="F39" s="8"/>
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
         <v>10</v>
       </c>
@@ -9608,7 +9592,7 @@
       <c r="F40" s="8"/>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
         <v>61</v>
       </c>
@@ -9623,16 +9607,16 @@
       <c r="F41" s="8"/>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="313"/>
-      <c r="B42" s="314"/>
-      <c r="C42" s="314"/>
-      <c r="D42" s="314"/>
-      <c r="E42" s="314"/>
-      <c r="F42" s="315"/>
+    <row r="42" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="312"/>
+      <c r="B42" s="313"/>
+      <c r="C42" s="313"/>
+      <c r="D42" s="313"/>
+      <c r="E42" s="313"/>
+      <c r="F42" s="314"/>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="40" t="s">
         <v>45</v>
       </c>
@@ -9642,7 +9626,7 @@
       <c r="E43" s="37"/>
       <c r="F43" s="37"/>
     </row>
-    <row r="44" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="54" t="s">
         <v>88</v>
       </c>
@@ -9654,7 +9638,7 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="29" t="s">
         <v>25</v>
       </c>
@@ -9665,7 +9649,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="29" t="s">
         <v>26</v>
       </c>
@@ -9676,7 +9660,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="18" t="s">
         <v>80</v>
       </c>
@@ -9686,7 +9670,7 @@
       <c r="E47" s="18"/>
       <c r="F47" s="23"/>
     </row>
-    <row r="48" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="29" t="s">
         <v>25</v>
       </c>
@@ -9694,7 +9678,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="29" t="s">
         <v>26</v>
       </c>
@@ -9702,7 +9686,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="42"/>
       <c r="B50" s="43"/>
       <c r="C50" s="30"/>
@@ -9710,18 +9694,18 @@
       <c r="E50" s="30"/>
       <c r="F50" s="31"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="40" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="28"/>
     </row>
-    <row r="52" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="32" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="29" t="s">
         <v>25</v>
       </c>
@@ -9732,7 +9716,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="29" t="s">
         <v>26</v>
       </c>
@@ -9743,7 +9727,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="18" t="s">
         <v>35</v>
       </c>
@@ -9753,7 +9737,7 @@
       <c r="E55" s="18"/>
       <c r="F55" s="23"/>
     </row>
-    <row r="56" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="29" t="s">
         <v>25</v>
       </c>
@@ -9765,7 +9749,7 @@
       <c r="E56" s="18"/>
       <c r="F56" s="23"/>
     </row>
-    <row r="57" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="29" t="s">
         <v>26</v>
       </c>
@@ -9777,7 +9761,7 @@
       <c r="E57" s="18"/>
       <c r="F57" s="23"/>
     </row>
-    <row r="58" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="30"/>
       <c r="B58" s="30"/>
       <c r="C58" s="30"/>
@@ -9785,18 +9769,18 @@
       <c r="E58" s="30"/>
       <c r="F58" s="31"/>
     </row>
-    <row r="59" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="40" t="s">
         <v>40</v>
       </c>
       <c r="F59" s="47"/>
     </row>
-    <row r="60" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="18" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="61" spans="1:7" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="29" t="s">
         <v>37</v>
       </c>
@@ -9806,7 +9790,7 @@
       <c r="C61" s="28"/>
       <c r="F61" s="41"/>
     </row>
-    <row r="62" spans="1:7" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="29" t="s">
         <v>38</v>
       </c>
@@ -9816,7 +9800,7 @@
       <c r="C62" s="28"/>
       <c r="F62" s="41"/>
     </row>
-    <row r="63" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="9" t="s">
         <v>1</v>
       </c>
@@ -9829,18 +9813,18 @@
       <c r="F63" s="8"/>
       <c r="G63" s="1"/>
     </row>
-    <row r="64" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="316" t="s">
+    <row r="64" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="315" t="s">
         <v>75</v>
       </c>
-      <c r="B64" s="317"/>
-      <c r="C64" s="317"/>
-      <c r="D64" s="317"/>
-      <c r="E64" s="317"/>
-      <c r="F64" s="318"/>
+      <c r="B64" s="316"/>
+      <c r="C64" s="316"/>
+      <c r="D64" s="316"/>
+      <c r="E64" s="316"/>
+      <c r="F64" s="317"/>
       <c r="G64" s="1"/>
     </row>
-    <row r="65" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="58">
         <v>43614</v>
       </c>
@@ -9853,7 +9837,7 @@
       <c r="F65" s="44"/>
       <c r="G65" s="1"/>
     </row>
-    <row r="66" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="58">
         <v>43623</v>
       </c>
@@ -9866,7 +9850,7 @@
       <c r="F66" s="44"/>
       <c r="G66" s="1"/>
     </row>
-    <row r="67" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="58">
         <v>43629</v>
       </c>
@@ -9879,7 +9863,7 @@
       <c r="F67" s="44"/>
       <c r="G67" s="1"/>
     </row>
-    <row r="68" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="58">
         <v>43637</v>
       </c>
@@ -9892,7 +9876,7 @@
       <c r="F68" s="44"/>
       <c r="G68" s="1"/>
     </row>
-    <row r="69" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="13"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
@@ -9901,7 +9885,7 @@
       <c r="F69" s="15"/>
       <c r="G69" s="1"/>
     </row>
-    <row r="70" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="38" t="s">
         <v>62</v>
       </c>
@@ -9912,22 +9896,22 @@
       <c r="F70" s="44"/>
       <c r="G70" s="1"/>
     </row>
-    <row r="71" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="319" t="s">
+    <row r="71" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="318" t="s">
         <v>68</v>
       </c>
-      <c r="B71" s="321" t="s">
+      <c r="B71" s="320" t="s">
         <v>3</v>
       </c>
-      <c r="C71" s="321"/>
-      <c r="E71" s="322" t="s">
+      <c r="C71" s="320"/>
+      <c r="E71" s="321" t="s">
         <v>4</v>
       </c>
-      <c r="F71" s="323"/>
+      <c r="F71" s="322"/>
       <c r="G71" s="1"/>
     </row>
-    <row r="72" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="320"/>
+    <row r="72" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="319"/>
       <c r="B72" s="52" t="s">
         <v>52</v>
       </c>
@@ -9945,7 +9929,7 @@
       </c>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="9" t="s">
         <v>11</v>
       </c>
@@ -9963,7 +9947,7 @@
       <c r="F73" s="53"/>
       <c r="G73" s="1"/>
     </row>
-    <row r="74" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="9" t="s">
         <v>13</v>
       </c>
@@ -9977,7 +9961,7 @@
       <c r="F74" s="6"/>
       <c r="G74" s="1"/>
     </row>
-    <row r="75" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="9" t="s">
         <v>14</v>
       </c>
@@ -9991,7 +9975,7 @@
       <c r="F75" s="6"/>
       <c r="G75" s="1"/>
     </row>
-    <row r="76" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="9" t="s">
         <v>69</v>
       </c>
@@ -10005,7 +9989,7 @@
       <c r="F76" s="6"/>
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="9" t="s">
         <v>63</v>
       </c>
@@ -10019,7 +10003,7 @@
       <c r="F77" s="6"/>
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="9" t="s">
         <v>12</v>
       </c>
@@ -10033,7 +10017,7 @@
       <c r="F78" s="6"/>
       <c r="G78" s="1"/>
     </row>
-    <row r="79" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="9" t="s">
         <v>15</v>
       </c>
@@ -10046,7 +10030,7 @@
       <c r="E79" s="18"/>
       <c r="F79" s="18"/>
     </row>
-    <row r="80" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="16" t="s">
         <v>64</v>
       </c>
@@ -10059,7 +10043,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="16" t="s">
         <v>65</v>
       </c>
@@ -10073,7 +10057,7 @@
       </c>
       <c r="G81" s="1"/>
     </row>
-    <row r="82" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="16" t="s">
         <v>66</v>
       </c>
@@ -10087,7 +10071,7 @@
       </c>
       <c r="G82" s="1"/>
     </row>
-    <row r="83" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="9" t="s">
         <v>67</v>
       </c>
@@ -10101,7 +10085,7 @@
       </c>
       <c r="G83" s="1"/>
     </row>
-    <row r="84" spans="1:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="13"/>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
@@ -10110,7 +10094,7 @@
       <c r="F84" s="15"/>
       <c r="G84" s="1"/>
     </row>
-    <row r="85" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="46" t="s">
         <v>39</v>
       </c>
@@ -10121,7 +10105,7 @@
       <c r="F85" s="45"/>
       <c r="G85" s="1"/>
     </row>
-    <row r="86" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="6" t="s">
         <v>53</v>
       </c>
@@ -10138,7 +10122,7 @@
       <c r="F86" s="50"/>
       <c r="G86" s="1"/>
     </row>
-    <row r="87" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="21" t="s">
         <v>16</v>
       </c>
@@ -10155,7 +10139,7 @@
       <c r="F87" s="12"/>
       <c r="G87" s="1"/>
     </row>
-    <row r="88" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="21" t="s">
         <v>17</v>
       </c>
@@ -10172,7 +10156,7 @@
       <c r="F88" s="12"/>
       <c r="G88" s="1"/>
     </row>
-    <row r="89" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="21" t="s">
         <v>70</v>
       </c>
@@ -10189,7 +10173,7 @@
       <c r="F89" s="12"/>
       <c r="G89" s="1"/>
     </row>
-    <row r="90" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="21" t="s">
         <v>4</v>
       </c>
@@ -10237,23 +10221,23 @@
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:F85"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="47.140625" customWidth="1"/>
-    <col min="2" max="4" width="9.85546875" customWidth="1"/>
+    <col min="1" max="1" width="47.1796875" customWidth="1"/>
+    <col min="2" max="4" width="9.81640625" customWidth="1"/>
     <col min="5" max="5" width="12" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="325" t="s">
+    <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="330" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="325"/>
-      <c r="C1" s="325"/>
-      <c r="D1" s="325"/>
-      <c r="E1" s="325"/>
-    </row>
-    <row r="2" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="330"/>
+      <c r="C1" s="330"/>
+      <c r="D1" s="330"/>
+      <c r="E1" s="330"/>
+    </row>
+    <row r="2" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="3" t="s">
         <v>3</v>
@@ -10268,7 +10252,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="39" t="s">
         <v>32</v>
       </c>
@@ -10277,7 +10261,7 @@
       <c r="D3" s="35"/>
       <c r="E3" s="64"/>
     </row>
-    <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>41</v>
       </c>
@@ -10296,7 +10280,7 @@
       </c>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>101</v>
       </c>
@@ -10316,7 +10300,7 @@
       </c>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>102</v>
       </c>
@@ -10336,7 +10320,7 @@
       </c>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>5</v>
       </c>
@@ -10355,7 +10339,7 @@
       </c>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>42</v>
       </c>
@@ -10375,7 +10359,7 @@
       </c>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>2</v>
       </c>
@@ -10394,7 +10378,7 @@
       </c>
       <c r="F9" s="1"/>
     </row>
-    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -10414,7 +10398,7 @@
       </c>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="17" t="s">
         <v>49</v>
       </c>
@@ -10428,7 +10412,7 @@
       </c>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="17" t="s">
         <v>50</v>
       </c>
@@ -10440,7 +10424,7 @@
       </c>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:6" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="13"/>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
@@ -10448,7 +10432,7 @@
       <c r="E13" s="15"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="38" t="s">
         <v>31</v>
       </c>
@@ -10458,17 +10442,17 @@
       <c r="E14" s="34"/>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="326" t="s">
+    <row r="15" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="331" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="326"/>
-      <c r="C15" s="326"/>
-      <c r="D15" s="326"/>
-      <c r="E15" s="326"/>
+      <c r="B15" s="331"/>
+      <c r="C15" s="331"/>
+      <c r="D15" s="331"/>
+      <c r="E15" s="331"/>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>7</v>
       </c>
@@ -10487,7 +10471,7 @@
       </c>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
         <v>6</v>
       </c>
@@ -10507,7 +10491,7 @@
       </c>
       <c r="F17" s="1"/>
     </row>
-    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>8</v>
       </c>
@@ -10526,7 +10510,7 @@
       </c>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>47</v>
       </c>
@@ -10545,17 +10529,17 @@
       </c>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="326" t="s">
+    <row r="20" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="331" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="326"/>
-      <c r="C20" s="326"/>
-      <c r="D20" s="326"/>
-      <c r="E20" s="326"/>
+      <c r="B20" s="331"/>
+      <c r="C20" s="331"/>
+      <c r="D20" s="331"/>
+      <c r="E20" s="331"/>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>103</v>
       </c>
@@ -10574,7 +10558,7 @@
       </c>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
         <v>104</v>
       </c>
@@ -10593,7 +10577,7 @@
       </c>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
         <v>105</v>
       </c>
@@ -10612,7 +10596,7 @@
       </c>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
         <v>106</v>
       </c>
@@ -10631,7 +10615,7 @@
       </c>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="21" t="s">
         <v>48</v>
       </c>
@@ -10649,7 +10633,7 @@
       </c>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="21"/>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -10657,7 +10641,7 @@
       <c r="E26" s="12"/>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="25" t="s">
         <v>36</v>
       </c>
@@ -10667,7 +10651,7 @@
       <c r="E27" s="27"/>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="21" t="s">
         <v>107</v>
       </c>
@@ -10679,7 +10663,7 @@
       <c r="E28" s="27"/>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="48" t="s">
         <v>108</v>
       </c>
@@ -10691,7 +10675,7 @@
       <c r="E29" s="27"/>
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="21" t="s">
         <v>109</v>
       </c>
@@ -10703,15 +10687,15 @@
       <c r="E30" s="27"/>
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="1:6" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="313"/>
-      <c r="B31" s="314"/>
-      <c r="C31" s="314"/>
-      <c r="D31" s="314"/>
-      <c r="E31" s="315"/>
+    <row r="31" spans="1:6" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="312"/>
+      <c r="B31" s="313"/>
+      <c r="C31" s="313"/>
+      <c r="D31" s="313"/>
+      <c r="E31" s="314"/>
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="38" t="s">
         <v>110</v>
       </c>
@@ -10721,7 +10705,7 @@
       <c r="E32" s="34"/>
       <c r="F32" s="1"/>
     </row>
-    <row r="33" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="49" t="s">
         <v>43</v>
       </c>
@@ -10733,7 +10717,7 @@
       <c r="E33" s="34"/>
       <c r="F33" s="1"/>
     </row>
-    <row r="34" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="49" t="s">
         <v>44</v>
       </c>
@@ -10745,7 +10729,7 @@
       <c r="E34" s="34"/>
       <c r="F34" s="1"/>
     </row>
-    <row r="35" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
         <v>112</v>
       </c>
@@ -10759,7 +10743,7 @@
       <c r="E35" s="8"/>
       <c r="F35" s="1"/>
     </row>
-    <row r="36" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
         <v>9</v>
       </c>
@@ -10773,7 +10757,7 @@
       <c r="E36" s="8"/>
       <c r="F36" s="1"/>
     </row>
-    <row r="37" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
         <v>10</v>
       </c>
@@ -10787,7 +10771,7 @@
       <c r="E37" s="8"/>
       <c r="F37" s="1"/>
     </row>
-    <row r="38" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
         <v>117</v>
       </c>
@@ -10801,15 +10785,15 @@
       <c r="E38" s="8"/>
       <c r="F38" s="1"/>
     </row>
-    <row r="39" spans="1:6" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="313"/>
-      <c r="B39" s="314"/>
-      <c r="C39" s="314"/>
-      <c r="D39" s="314"/>
-      <c r="E39" s="315"/>
+    <row r="39" spans="1:6" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="312"/>
+      <c r="B39" s="313"/>
+      <c r="C39" s="313"/>
+      <c r="D39" s="313"/>
+      <c r="E39" s="314"/>
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="40" t="s">
         <v>45</v>
       </c>
@@ -10818,7 +10802,7 @@
       <c r="D40" s="37"/>
       <c r="E40" s="37"/>
     </row>
-    <row r="41" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="32" t="s">
         <v>120</v>
       </c>
@@ -10826,7 +10810,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="29" t="s">
         <v>25</v>
       </c>
@@ -10837,7 +10821,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="29" t="s">
         <v>26</v>
       </c>
@@ -10848,7 +10832,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="18" t="s">
         <v>121</v>
       </c>
@@ -10857,7 +10841,7 @@
       <c r="D44" s="18"/>
       <c r="E44" s="23"/>
     </row>
-    <row r="45" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="29" t="s">
         <v>25</v>
       </c>
@@ -10865,7 +10849,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="29" t="s">
         <v>26</v>
       </c>
@@ -10873,25 +10857,25 @@
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="42"/>
       <c r="B47" s="43"/>
       <c r="C47" s="30"/>
       <c r="D47" s="30"/>
       <c r="E47" s="31"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="40" t="s">
         <v>46</v>
       </c>
       <c r="B48" s="28"/>
     </row>
-    <row r="49" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="32" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="29" t="s">
         <v>25</v>
       </c>
@@ -10902,7 +10886,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="29" t="s">
         <v>26</v>
       </c>
@@ -10913,7 +10897,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="18" t="s">
         <v>35</v>
       </c>
@@ -10922,7 +10906,7 @@
       <c r="D52" s="18"/>
       <c r="E52" s="23"/>
     </row>
-    <row r="53" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="29" t="s">
         <v>25</v>
       </c>
@@ -10933,7 +10917,7 @@
       <c r="D53" s="18"/>
       <c r="E53" s="23"/>
     </row>
-    <row r="54" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="29" t="s">
         <v>26</v>
       </c>
@@ -10944,24 +10928,24 @@
       <c r="D54" s="18"/>
       <c r="E54" s="23"/>
     </row>
-    <row r="55" spans="1:6" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="30"/>
       <c r="B55" s="30"/>
       <c r="C55" s="30"/>
       <c r="D55" s="30"/>
       <c r="E55" s="31"/>
     </row>
-    <row r="56" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="40" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="18" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="58" spans="1:6" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="29" t="s">
         <v>123</v>
       </c>
@@ -10973,7 +10957,7 @@
       </c>
       <c r="E58" s="41"/>
     </row>
-    <row r="59" spans="1:6" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="29" t="s">
         <v>37</v>
       </c>
@@ -10985,7 +10969,7 @@
       </c>
       <c r="E59" s="41"/>
     </row>
-    <row r="60" spans="1:6" s="29" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" s="29" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="29" t="s">
         <v>38</v>
       </c>
@@ -10997,7 +10981,7 @@
       </c>
       <c r="E60" s="41"/>
     </row>
-    <row r="61" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="9" t="s">
         <v>1</v>
       </c>
@@ -11011,17 +10995,17 @@
       <c r="E61" s="8"/>
       <c r="F61" s="1"/>
     </row>
-    <row r="62" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="316" t="s">
+    <row r="62" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="315" t="s">
         <v>124</v>
       </c>
-      <c r="B62" s="317"/>
-      <c r="C62" s="317"/>
-      <c r="D62" s="317"/>
-      <c r="E62" s="318"/>
+      <c r="B62" s="316"/>
+      <c r="C62" s="316"/>
+      <c r="D62" s="316"/>
+      <c r="E62" s="317"/>
       <c r="F62" s="1"/>
     </row>
-    <row r="63" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="58">
         <v>43248</v>
       </c>
@@ -11035,7 +11019,7 @@
       <c r="E63" s="12"/>
       <c r="F63" s="1"/>
     </row>
-    <row r="64" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="58">
         <v>43255</v>
       </c>
@@ -11049,7 +11033,7 @@
       <c r="E64" s="12"/>
       <c r="F64" s="1"/>
     </row>
-    <row r="65" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="58">
         <v>43259</v>
       </c>
@@ -11063,7 +11047,7 @@
       <c r="E65" s="12"/>
       <c r="F65" s="1"/>
     </row>
-    <row r="66" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="58">
         <v>43274</v>
       </c>
@@ -11077,7 +11061,7 @@
       <c r="E66" s="12"/>
       <c r="F66" s="1"/>
     </row>
-    <row r="67" spans="1:6" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="13"/>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
@@ -11085,7 +11069,7 @@
       <c r="E67" s="15"/>
       <c r="F67" s="1"/>
     </row>
-    <row r="68" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="38" t="s">
         <v>125</v>
       </c>
@@ -11095,22 +11079,22 @@
       <c r="E68" s="12"/>
       <c r="F68" s="1"/>
     </row>
-    <row r="69" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="319" t="s">
+    <row r="69" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="318" t="s">
         <v>126</v>
       </c>
-      <c r="B69" s="321" t="s">
+      <c r="B69" s="320" t="s">
         <v>3</v>
       </c>
-      <c r="C69" s="321"/>
+      <c r="C69" s="320"/>
       <c r="D69" s="33" t="s">
         <v>4</v>
       </c>
       <c r="E69" s="65"/>
       <c r="F69" s="1"/>
     </row>
-    <row r="70" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="320"/>
+    <row r="70" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="319"/>
       <c r="B70" s="52" t="s">
         <v>52</v>
       </c>
@@ -11123,7 +11107,7 @@
       <c r="E70" s="65"/>
       <c r="F70" s="1"/>
     </row>
-    <row r="71" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="9" t="s">
         <v>11</v>
       </c>
@@ -11139,7 +11123,7 @@
       </c>
       <c r="F71" s="1"/>
     </row>
-    <row r="72" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="9" t="s">
         <v>13</v>
       </c>
@@ -11155,7 +11139,7 @@
       </c>
       <c r="F72" s="1"/>
     </row>
-    <row r="73" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="9" t="s">
         <v>14</v>
       </c>
@@ -11171,7 +11155,7 @@
       </c>
       <c r="F73" s="1"/>
     </row>
-    <row r="74" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="9" t="s">
         <v>127</v>
       </c>
@@ -11187,7 +11171,7 @@
       </c>
       <c r="F74" s="1"/>
     </row>
-    <row r="75" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="9" t="s">
         <v>12</v>
       </c>
@@ -11203,7 +11187,7 @@
       </c>
       <c r="F75" s="1"/>
     </row>
-    <row r="76" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="9" t="s">
         <v>128</v>
       </c>
@@ -11219,7 +11203,7 @@
       </c>
       <c r="F76" s="1"/>
     </row>
-    <row r="77" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="16" t="s">
         <v>129</v>
       </c>
@@ -11234,7 +11218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="9" t="s">
         <v>15</v>
       </c>
@@ -11250,7 +11234,7 @@
       </c>
       <c r="F78" s="1"/>
     </row>
-    <row r="79" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="9" t="s">
         <v>130</v>
       </c>
@@ -11268,7 +11252,7 @@
       </c>
       <c r="F79" s="1"/>
     </row>
-    <row r="80" spans="1:6" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="13"/>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
@@ -11276,7 +11260,7 @@
       <c r="E80" s="15"/>
       <c r="F80" s="1"/>
     </row>
-    <row r="81" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="46" t="s">
         <v>39</v>
       </c>
@@ -11286,7 +11270,7 @@
       <c r="E81" s="8"/>
       <c r="F81" s="1"/>
     </row>
-    <row r="82" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="6" t="s">
         <v>53</v>
       </c>
@@ -11302,7 +11286,7 @@
       <c r="E82" s="50"/>
       <c r="F82" s="1"/>
     </row>
-    <row r="83" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="21" t="s">
         <v>16</v>
       </c>
@@ -11318,7 +11302,7 @@
       <c r="E83" s="12"/>
       <c r="F83" s="1"/>
     </row>
-    <row r="84" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="21" t="s">
         <v>17</v>
       </c>
@@ -11334,7 +11318,7 @@
       <c r="E84" s="12"/>
       <c r="F84" s="1"/>
     </row>
-    <row r="85" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="21" t="s">
         <v>4</v>
       </c>
@@ -11372,55 +11356,55 @@
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:P77"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="67" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="18" customWidth="1"/>
-    <col min="3" max="5" width="9.140625" style="18"/>
-    <col min="6" max="6" width="18.5703125" style="18" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="18"/>
-    <col min="8" max="8" width="4.42578125" style="18" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="18"/>
-    <col min="10" max="10" width="4.42578125" style="18" customWidth="1"/>
-    <col min="11" max="11" width="11.85546875" style="18" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="18"/>
+    <col min="1" max="1" width="14.81640625" style="67" customWidth="1"/>
+    <col min="2" max="2" width="13.81640625" style="18" customWidth="1"/>
+    <col min="3" max="5" width="9.1796875" style="18"/>
+    <col min="6" max="6" width="18.54296875" style="18" customWidth="1"/>
+    <col min="7" max="7" width="9.1796875" style="18"/>
+    <col min="8" max="8" width="4.453125" style="18" customWidth="1"/>
+    <col min="9" max="9" width="9.1796875" style="18"/>
+    <col min="10" max="10" width="4.453125" style="18" customWidth="1"/>
+    <col min="11" max="11" width="11.81640625" style="18" customWidth="1"/>
+    <col min="12" max="16384" width="9.1796875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="328">
+    <row r="1" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="334">
         <v>2017</v>
       </c>
-      <c r="B1" s="329"/>
-      <c r="C1" s="329"/>
-      <c r="D1" s="329"/>
-      <c r="E1" s="329"/>
-      <c r="F1" s="329"/>
-      <c r="G1" s="329"/>
-      <c r="H1" s="329"/>
-      <c r="I1" s="329"/>
-      <c r="J1" s="329"/>
-      <c r="K1" s="330"/>
-    </row>
-    <row r="2" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="331" t="s">
+      <c r="B1" s="335"/>
+      <c r="C1" s="335"/>
+      <c r="D1" s="335"/>
+      <c r="E1" s="335"/>
+      <c r="F1" s="335"/>
+      <c r="G1" s="335"/>
+      <c r="H1" s="335"/>
+      <c r="I1" s="335"/>
+      <c r="J1" s="335"/>
+      <c r="K1" s="336"/>
+    </row>
+    <row r="2" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="337" t="s">
         <v>133</v>
       </c>
-      <c r="B2" s="331"/>
-      <c r="C2" s="331"/>
-      <c r="D2" s="331"/>
-      <c r="E2" s="331"/>
-      <c r="F2" s="331"/>
-      <c r="G2" s="331"/>
-      <c r="H2" s="331"/>
-      <c r="I2" s="331"/>
-      <c r="J2" s="331"/>
-      <c r="K2" s="331"/>
+      <c r="B2" s="337"/>
+      <c r="C2" s="337"/>
+      <c r="D2" s="337"/>
+      <c r="E2" s="337"/>
+      <c r="F2" s="337"/>
+      <c r="G2" s="337"/>
+      <c r="H2" s="337"/>
+      <c r="I2" s="337"/>
+      <c r="J2" s="337"/>
+      <c r="K2" s="337"/>
       <c r="L2" s="66"/>
       <c r="M2" s="66"/>
       <c r="N2" s="66"/>
       <c r="O2" s="66"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="67" t="s">
         <v>134</v>
       </c>
@@ -11428,7 +11412,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="67" t="s">
         <v>135</v>
       </c>
@@ -11438,13 +11422,13 @@
       <c r="E6" s="68">
         <v>0.13420000000000001</v>
       </c>
-      <c r="F6" s="332" t="s">
+      <c r="F6" s="338" t="s">
         <v>136</v>
       </c>
-      <c r="G6" s="332"/>
+      <c r="G6" s="338"/>
       <c r="L6" s="69"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="67" t="s">
         <v>137</v>
       </c>
@@ -11454,22 +11438,22 @@
       <c r="E7" s="70">
         <v>0.37</v>
       </c>
-      <c r="F7" s="332" t="s">
+      <c r="F7" s="338" t="s">
         <v>138</v>
       </c>
-      <c r="G7" s="332"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="G7" s="338"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E8" s="70"/>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="67" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="18" t="s">
         <v>140</v>
       </c>
@@ -11477,7 +11461,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B11" s="18" t="s">
         <v>141</v>
       </c>
@@ -11493,7 +11477,7 @@
       <c r="J11" s="67"/>
       <c r="K11" s="67"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B12" s="18" t="s">
         <v>143</v>
       </c>
@@ -11515,7 +11499,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B13" s="18" t="s">
         <v>148</v>
       </c>
@@ -11536,7 +11520,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="67" t="s">
         <v>150</v>
       </c>
@@ -11554,7 +11538,7 @@
         <v>0.62962962962962965</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="18" t="s">
         <v>152</v>
       </c>
@@ -11575,7 +11559,7 @@
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B16" s="18" t="s">
         <v>55</v>
       </c>
@@ -11596,7 +11580,7 @@
         <v>0.40868794326241137</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B17" s="18" t="s">
         <v>48</v>
       </c>
@@ -11617,7 +11601,7 @@
         <v>0.42857142857142855</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B18" s="18" t="s">
         <v>156</v>
       </c>
@@ -11638,7 +11622,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B19" s="18" t="s">
         <v>58</v>
       </c>
@@ -11648,7 +11632,7 @@
       <c r="F19" s="32"/>
       <c r="K19" s="23"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="F20" s="73" t="s">
         <v>158</v>
       </c>
@@ -11667,15 +11651,15 @@
         <v>0.4188393608074012</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A21" s="327" t="s">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A21" s="332" t="s">
         <v>159</v>
       </c>
-      <c r="B21" s="327"/>
+      <c r="B21" s="332"/>
       <c r="F21" s="29"/>
       <c r="K21" s="23"/>
     </row>
-    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B22" s="18" t="s">
         <v>160</v>
       </c>
@@ -11691,7 +11675,7 @@
       <c r="J22" s="67"/>
       <c r="K22" s="67"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B23" s="18" t="s">
         <v>162</v>
       </c>
@@ -11713,7 +11697,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B24" s="18" t="s">
         <v>163</v>
       </c>
@@ -11734,7 +11718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B25" s="18" t="s">
         <v>165</v>
       </c>
@@ -11757,7 +11741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="F27" s="73" t="s">
         <v>158</v>
       </c>
@@ -11776,12 +11760,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="67" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B29" s="18" t="s">
         <v>123</v>
       </c>
@@ -11789,7 +11773,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B30" s="18" t="s">
         <v>37</v>
       </c>
@@ -11797,7 +11781,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B31" s="18" t="s">
         <v>38</v>
       </c>
@@ -11807,7 +11791,7 @@
       <c r="K31" s="79"/>
       <c r="P31" s="23"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B32" s="18" t="s">
         <v>168</v>
       </c>
@@ -11818,20 +11802,20 @@
       <c r="K32" s="67"/>
       <c r="P32" s="23"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="G33" s="80"/>
       <c r="K33" s="79"/>
       <c r="P33" s="23"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A34" s="327" t="s">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A34" s="332" t="s">
         <v>169</v>
       </c>
-      <c r="B34" s="327"/>
+      <c r="B34" s="332"/>
       <c r="K34" s="79"/>
       <c r="P34" s="23"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B35" s="81" t="s">
         <v>170</v>
       </c>
@@ -11842,7 +11826,7 @@
       <c r="K35" s="79"/>
       <c r="P35" s="23"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B36" s="81" t="s">
         <v>171</v>
       </c>
@@ -11853,7 +11837,7 @@
       <c r="K36" s="79"/>
       <c r="P36" s="23"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B37" s="81" t="s">
         <v>172</v>
       </c>
@@ -11862,7 +11846,7 @@
       </c>
       <c r="G37" s="80"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B38" s="81" t="s">
         <v>173</v>
       </c>
@@ -11871,23 +11855,23 @@
       </c>
       <c r="G38" s="80"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B39" s="81"/>
       <c r="G39" s="80"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A40" s="327" t="s">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A40" s="332" t="s">
         <v>174</v>
       </c>
-      <c r="B40" s="327"/>
-      <c r="C40" s="327"/>
-      <c r="D40" s="327"/>
+      <c r="B40" s="332"/>
+      <c r="C40" s="332"/>
+      <c r="D40" s="332"/>
       <c r="E40" s="28"/>
       <c r="G40" s="80"/>
       <c r="I40" s="80"/>
       <c r="K40" s="80"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="79"/>
       <c r="B41" s="79"/>
       <c r="C41" s="79"/>
@@ -11897,17 +11881,17 @@
       <c r="I41" s="80"/>
       <c r="K41" s="80"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B42" s="60"/>
       <c r="G42" s="80"/>
       <c r="I42" s="80"/>
       <c r="K42" s="80"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A43" s="327" t="s">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A43" s="332" t="s">
         <v>175</v>
       </c>
-      <c r="B43" s="327"/>
+      <c r="B43" s="332"/>
       <c r="C43" s="18">
         <v>39</v>
       </c>
@@ -11918,11 +11902,11 @@
       <c r="I43" s="80"/>
       <c r="K43" s="80"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A44" s="327" t="s">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A44" s="332" t="s">
         <v>177</v>
       </c>
-      <c r="B44" s="327"/>
+      <c r="B44" s="332"/>
       <c r="C44" s="18">
         <v>11</v>
       </c>
@@ -11933,11 +11917,11 @@
       <c r="I44" s="80"/>
       <c r="K44" s="80"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A45" s="327" t="s">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A45" s="332" t="s">
         <v>178</v>
       </c>
-      <c r="B45" s="327"/>
+      <c r="B45" s="332"/>
       <c r="C45" s="18">
         <v>16</v>
       </c>
@@ -11948,11 +11932,11 @@
       <c r="I45" s="80"/>
       <c r="K45" s="80"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A46" s="327" t="s">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A46" s="332" t="s">
         <v>179</v>
       </c>
-      <c r="B46" s="327"/>
+      <c r="B46" s="332"/>
       <c r="C46" s="18">
         <v>73</v>
       </c>
@@ -11963,11 +11947,11 @@
       <c r="I46" s="80"/>
       <c r="K46" s="80"/>
     </row>
-    <row r="47" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="327" t="s">
+    <row r="47" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="332" t="s">
         <v>180</v>
       </c>
-      <c r="B47" s="327"/>
+      <c r="B47" s="332"/>
       <c r="C47" s="18">
         <v>71</v>
       </c>
@@ -11978,7 +11962,7 @@
       <c r="I47" s="80"/>
       <c r="K47" s="80"/>
     </row>
-    <row r="48" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="79"/>
       <c r="B48" s="79"/>
       <c r="D48" s="37"/>
@@ -11986,18 +11970,18 @@
       <c r="I48" s="80"/>
       <c r="K48" s="80"/>
     </row>
-    <row r="49" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="79"/>
       <c r="B49" s="79"/>
       <c r="G49" s="80"/>
       <c r="I49" s="80"/>
       <c r="K49" s="80"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A50" s="327" t="s">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" s="332" t="s">
         <v>181</v>
       </c>
-      <c r="B50" s="327"/>
+      <c r="B50" s="332"/>
       <c r="C50" s="18">
         <v>17.399999999999999</v>
       </c>
@@ -12008,7 +11992,7 @@
       <c r="I50" s="80"/>
       <c r="K50" s="80"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="79"/>
       <c r="B51" s="79"/>
       <c r="C51" s="37"/>
@@ -12017,12 +12001,12 @@
       <c r="I51" s="80"/>
       <c r="K51" s="80"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G52" s="80"/>
       <c r="I52" s="80"/>
       <c r="K52" s="80"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="333" t="s">
         <v>183</v>
       </c>
@@ -12034,12 +12018,12 @@
       <c r="I53" s="80"/>
       <c r="K53" s="80"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G54" s="80"/>
       <c r="I54" s="80"/>
       <c r="K54" s="80"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="83" t="s">
         <v>184</v>
       </c>
@@ -12050,87 +12034,93 @@
       <c r="G55" s="80"/>
       <c r="K55" s="80"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G56" s="80"/>
       <c r="K56" s="80"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G57" s="80"/>
       <c r="K57" s="80"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G58" s="80"/>
       <c r="K58" s="80"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G59" s="80"/>
       <c r="K59" s="80"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G60" s="80"/>
       <c r="K60" s="80"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G61" s="80"/>
       <c r="K61" s="80"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G62" s="80"/>
       <c r="K62" s="80"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G63" s="80"/>
       <c r="K63" s="80"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G64" s="80"/>
       <c r="K64" s="80"/>
     </row>
-    <row r="65" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G65" s="80"/>
       <c r="K65" s="80"/>
     </row>
-    <row r="66" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G66" s="80"/>
       <c r="K66" s="80"/>
     </row>
-    <row r="67" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G67" s="80"/>
       <c r="K67" s="80"/>
     </row>
-    <row r="68" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G68" s="80"/>
       <c r="K68" s="80"/>
     </row>
-    <row r="69" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="7:11" x14ac:dyDescent="0.3">
       <c r="K69" s="80"/>
     </row>
-    <row r="70" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="7:11" x14ac:dyDescent="0.3">
       <c r="K70" s="80"/>
     </row>
-    <row r="71" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="7:11" x14ac:dyDescent="0.3">
       <c r="K71" s="80"/>
     </row>
-    <row r="72" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="7:11" x14ac:dyDescent="0.3">
       <c r="K72" s="80"/>
     </row>
-    <row r="73" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="7:11" x14ac:dyDescent="0.3">
       <c r="K73" s="80"/>
     </row>
-    <row r="74" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="7:11" x14ac:dyDescent="0.3">
       <c r="K74" s="80"/>
     </row>
-    <row r="75" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="7:11" x14ac:dyDescent="0.3">
       <c r="K75" s="80"/>
     </row>
-    <row r="76" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="7:11" x14ac:dyDescent="0.3">
       <c r="K76" s="80"/>
     </row>
-    <row r="77" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="7:11" x14ac:dyDescent="0.3">
       <c r="K77" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="A21:B21"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="A40:D40"/>
@@ -12139,12 +12129,6 @@
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="A21:B21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -12153,6 +12137,6 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{0693b5ba-4b18-4d7b-9341-f32f400a5494}" enabled="0" method="" siteId="{0693b5ba-4b18-4d7b-9341-f32f400a5494}" removed="1"/>
+  <clbl:label id="{6dd02d64-b7f3-43f7-a145-cfd68d338edf}" enabled="1" method="Standard" siteId="{0693b5ba-4b18-4d7b-9341-f32f400a5494}" contentBits="0" removed="0"/>
 </clbl:labelList>
 </file>
--- a/web/flask/static/annual_report_template.xlsx
+++ b/web/flask/static/annual_report_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\apps\climberdb\git\web\flask\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABE8CC8-E191-4D3A-8C80-1749A39B9F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D332130-0012-4C53-82F4-290A1EC0F289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2342,6 +2342,63 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2354,12 +2411,6 @@
     <xf numFmtId="0" fontId="21" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -2372,27 +2423,6 @@
     <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2411,36 +2441,6 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2459,6 +2459,24 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2492,24 +2510,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2522,9 +2522,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2538,6 +2535,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2843,24 +2843,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="296" t="s">
+      <c r="A1" s="273" t="s">
         <v>325</v>
       </c>
-      <c r="B1" s="297"/>
-      <c r="C1" s="297"/>
-      <c r="D1" s="297"/>
-      <c r="E1" s="297"/>
-      <c r="F1" s="298"/>
+      <c r="B1" s="274"/>
+      <c r="C1" s="274"/>
+      <c r="D1" s="274"/>
+      <c r="E1" s="274"/>
+      <c r="F1" s="275"/>
     </row>
     <row r="2" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="299" t="s">
+      <c r="A2" s="276" t="s">
         <v>290</v>
       </c>
-      <c r="B2" s="300"/>
-      <c r="C2" s="300"/>
-      <c r="D2" s="300"/>
-      <c r="E2" s="300"/>
-      <c r="F2" s="301"/>
+      <c r="B2" s="277"/>
+      <c r="C2" s="277"/>
+      <c r="D2" s="277"/>
+      <c r="E2" s="277"/>
+      <c r="F2" s="278"/>
     </row>
     <row r="3" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="229" t="s">
@@ -2881,32 +2881,32 @@
       <c r="F4" s="261"/>
     </row>
     <row r="5" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="287"/>
-      <c r="B5" s="288"/>
-      <c r="C5" s="288"/>
+      <c r="A5" s="283"/>
+      <c r="B5" s="284"/>
+      <c r="C5" s="284"/>
       <c r="D5" s="217"/>
       <c r="E5" s="218"/>
       <c r="F5" s="219"/>
     </row>
     <row r="6" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="285" t="s">
+      <c r="A6" s="289" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="286"/>
-      <c r="C6" s="286"/>
+      <c r="B6" s="290"/>
+      <c r="C6" s="290"/>
       <c r="D6" s="220"/>
       <c r="E6" s="221"/>
       <c r="F6" s="221"/>
     </row>
     <row r="7" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="283" t="s">
+      <c r="A7" s="287" t="s">
         <v>291</v>
       </c>
-      <c r="B7" s="284"/>
-      <c r="C7" s="284"/>
-      <c r="D7" s="277"/>
-      <c r="E7" s="278"/>
-      <c r="F7" s="278"/>
+      <c r="B7" s="288"/>
+      <c r="C7" s="288"/>
+      <c r="D7" s="279"/>
+      <c r="E7" s="280"/>
+      <c r="F7" s="280"/>
     </row>
     <row r="8" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="241" t="s">
@@ -2945,19 +2945,19 @@
       <c r="F10" s="18"/>
     </row>
     <row r="11" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="287"/>
-      <c r="B11" s="288"/>
-      <c r="C11" s="288"/>
+      <c r="A11" s="283"/>
+      <c r="B11" s="284"/>
+      <c r="C11" s="284"/>
       <c r="D11" s="210"/>
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
     </row>
     <row r="12" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="304" t="s">
+      <c r="A12" s="286" t="s">
         <v>231</v>
       </c>
-      <c r="B12" s="304"/>
-      <c r="C12" s="304"/>
+      <c r="B12" s="286"/>
+      <c r="C12" s="286"/>
       <c r="D12" s="210"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
@@ -2981,22 +2981,22 @@
       <c r="F14" s="51"/>
     </row>
     <row r="15" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="287"/>
-      <c r="B15" s="288"/>
-      <c r="C15" s="288"/>
+      <c r="A15" s="283"/>
+      <c r="B15" s="284"/>
+      <c r="C15" s="284"/>
       <c r="D15" s="223"/>
       <c r="E15" s="224"/>
       <c r="F15" s="224"/>
     </row>
     <row r="16" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="283" t="s">
+      <c r="A16" s="287" t="s">
         <v>296</v>
       </c>
-      <c r="B16" s="305"/>
-      <c r="C16" s="305"/>
-      <c r="D16" s="277"/>
-      <c r="E16" s="278"/>
-      <c r="F16" s="278"/>
+      <c r="B16" s="291"/>
+      <c r="C16" s="291"/>
+      <c r="D16" s="279"/>
+      <c r="E16" s="280"/>
+      <c r="F16" s="280"/>
     </row>
     <row r="17" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="241" t="s">
@@ -3035,19 +3035,19 @@
       <c r="F19" s="18"/>
     </row>
     <row r="20" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="287"/>
-      <c r="B20" s="288"/>
-      <c r="C20" s="288"/>
+      <c r="A20" s="283"/>
+      <c r="B20" s="284"/>
+      <c r="C20" s="284"/>
       <c r="D20" s="207"/>
       <c r="E20" s="51"/>
       <c r="F20" s="201"/>
     </row>
     <row r="21" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="304" t="s">
+      <c r="A21" s="286" t="s">
         <v>298</v>
       </c>
-      <c r="B21" s="304"/>
-      <c r="C21" s="304"/>
+      <c r="B21" s="286"/>
+      <c r="C21" s="286"/>
       <c r="D21" s="207"/>
       <c r="E21" s="18"/>
       <c r="F21" s="18"/>
@@ -3071,9 +3071,9 @@
       <c r="F23" s="203"/>
     </row>
     <row r="24" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="287"/>
-      <c r="B24" s="288"/>
-      <c r="C24" s="289"/>
+      <c r="A24" s="283"/>
+      <c r="B24" s="284"/>
+      <c r="C24" s="285"/>
       <c r="D24" s="207"/>
       <c r="E24" s="204"/>
       <c r="F24" s="203"/>
@@ -3081,11 +3081,11 @@
       <c r="L24" s="18"/>
     </row>
     <row r="25" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="283" t="s">
+      <c r="A25" s="287" t="s">
         <v>297</v>
       </c>
-      <c r="B25" s="284"/>
-      <c r="C25" s="284"/>
+      <c r="B25" s="288"/>
+      <c r="C25" s="288"/>
       <c r="D25" s="223"/>
       <c r="E25" s="224"/>
       <c r="F25" s="224"/>
@@ -3121,19 +3121,19 @@
       <c r="F27" s="227"/>
     </row>
     <row r="28" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="287"/>
-      <c r="B28" s="288"/>
-      <c r="C28" s="288"/>
+      <c r="A28" s="283"/>
+      <c r="B28" s="284"/>
+      <c r="C28" s="284"/>
       <c r="D28" s="207"/>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
     </row>
     <row r="29" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="285" t="s">
+      <c r="A29" s="289" t="s">
         <v>300</v>
       </c>
-      <c r="B29" s="286"/>
-      <c r="C29" s="286"/>
+      <c r="B29" s="290"/>
+      <c r="C29" s="290"/>
       <c r="D29" s="205"/>
       <c r="E29" s="37"/>
       <c r="F29" s="37"/>
@@ -3157,19 +3157,19 @@
       <c r="F31" s="37"/>
     </row>
     <row r="32" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="288"/>
-      <c r="B32" s="288"/>
-      <c r="C32" s="289"/>
+      <c r="A32" s="284"/>
+      <c r="B32" s="284"/>
+      <c r="C32" s="285"/>
       <c r="D32" s="207"/>
       <c r="E32" s="18"/>
       <c r="F32" s="18"/>
     </row>
     <row r="33" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="285" t="s">
+      <c r="A33" s="289" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="286"/>
-      <c r="C33" s="286"/>
+      <c r="B33" s="290"/>
+      <c r="C33" s="290"/>
       <c r="D33" s="205"/>
       <c r="E33" s="37"/>
       <c r="F33" s="37"/>
@@ -3185,18 +3185,18 @@
       <c r="F34" s="37"/>
     </row>
     <row r="35" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="290"/>
-      <c r="B35" s="291"/>
-      <c r="C35" s="292"/>
+      <c r="A35" s="300"/>
+      <c r="B35" s="301"/>
+      <c r="C35" s="302"/>
       <c r="D35" s="208"/>
       <c r="F35" s="209"/>
     </row>
     <row r="36" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="302" t="s">
+      <c r="A36" s="281" t="s">
         <v>301</v>
       </c>
-      <c r="B36" s="303"/>
-      <c r="C36" s="303"/>
+      <c r="B36" s="282"/>
+      <c r="C36" s="282"/>
       <c r="D36" s="208"/>
     </row>
     <row r="37" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -3208,26 +3208,26 @@
       <c r="D37" s="208"/>
     </row>
     <row r="38" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="293"/>
-      <c r="B38" s="294"/>
-      <c r="C38" s="295"/>
+      <c r="A38" s="303"/>
+      <c r="B38" s="304"/>
+      <c r="C38" s="305"/>
       <c r="D38" s="208"/>
       <c r="F38" s="209"/>
     </row>
     <row r="39" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="302" t="s">
+      <c r="A39" s="281" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="303"/>
-      <c r="C39" s="303"/>
+      <c r="B39" s="282"/>
+      <c r="C39" s="282"/>
       <c r="D39" s="208"/>
       <c r="F39" s="209"/>
     </row>
     <row r="40" spans="1:6" s="216" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="279" t="s">
+      <c r="A40" s="296" t="s">
         <v>74</v>
       </c>
-      <c r="B40" s="280"/>
+      <c r="B40" s="297"/>
       <c r="C40" s="235"/>
       <c r="D40" s="211"/>
       <c r="F40" s="212"/>
@@ -3241,10 +3241,10 @@
       <c r="D41" s="208"/>
     </row>
     <row r="42" spans="1:6" s="216" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="279" t="s">
+      <c r="A42" s="296" t="s">
         <v>75</v>
       </c>
-      <c r="B42" s="280"/>
+      <c r="B42" s="297"/>
       <c r="C42" s="236"/>
       <c r="D42" s="213"/>
       <c r="E42" s="228"/>
@@ -3261,30 +3261,30 @@
       <c r="F43" s="198"/>
     </row>
     <row r="44" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="287"/>
-      <c r="B44" s="288"/>
-      <c r="C44" s="289"/>
+      <c r="A44" s="283"/>
+      <c r="B44" s="284"/>
+      <c r="C44" s="285"/>
       <c r="D44" s="207"/>
       <c r="E44" s="18"/>
       <c r="F44" s="198"/>
     </row>
     <row r="45" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="281" t="s">
+      <c r="A45" s="298" t="s">
         <v>324</v>
       </c>
-      <c r="B45" s="282"/>
-      <c r="C45" s="282"/>
-      <c r="D45" s="282"/>
+      <c r="B45" s="299"/>
+      <c r="C45" s="299"/>
+      <c r="D45" s="299"/>
       <c r="E45" s="207"/>
       <c r="F45" s="198"/>
     </row>
     <row r="46" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="135"/>
-      <c r="B46" s="273" t="s">
+      <c r="B46" s="292" t="s">
         <v>317</v>
       </c>
-      <c r="C46" s="274"/>
-      <c r="D46" s="274"/>
+      <c r="C46" s="293"/>
+      <c r="D46" s="293"/>
       <c r="E46" s="208"/>
       <c r="F46"/>
     </row>
@@ -3322,11 +3322,11 @@
     </row>
     <row r="50" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="253"/>
-      <c r="B50" s="275" t="s">
+      <c r="B50" s="294" t="s">
         <v>4</v>
       </c>
-      <c r="C50" s="276"/>
-      <c r="D50" s="276"/>
+      <c r="C50" s="295"/>
+      <c r="D50" s="295"/>
       <c r="E50" s="206"/>
       <c r="F50" s="28"/>
       <c r="J50" s="202"/>
@@ -3401,6 +3401,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A44:C44"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="D7:F7"/>
@@ -3417,19 +3430,6 @@
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A21:C21"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A44:C44"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup scale="69" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -6323,14 +6323,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="325" t="s">
+      <c r="A1" s="314" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="325"/>
-      <c r="C1" s="325"/>
-      <c r="D1" s="325"/>
-      <c r="E1" s="325"/>
-      <c r="F1" s="325"/>
+      <c r="B1" s="314"/>
+      <c r="C1" s="314"/>
+      <c r="D1" s="314"/>
+      <c r="E1" s="314"/>
+      <c r="F1" s="314"/>
     </row>
     <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
@@ -6746,12 +6746,12 @@
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="326"/>
-      <c r="B26" s="327"/>
-      <c r="C26" s="327"/>
-      <c r="D26" s="327"/>
-      <c r="E26" s="327"/>
-      <c r="F26" s="327"/>
+      <c r="A26" s="315"/>
+      <c r="B26" s="316"/>
+      <c r="C26" s="316"/>
+      <c r="D26" s="316"/>
+      <c r="E26" s="316"/>
+      <c r="F26" s="316"/>
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -6834,23 +6834,23 @@
       <c r="G32" s="1"/>
     </row>
     <row r="33" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="328"/>
-      <c r="B33" s="323"/>
-      <c r="C33" s="323"/>
-      <c r="D33" s="323"/>
-      <c r="E33" s="323"/>
-      <c r="F33" s="324"/>
+      <c r="A33" s="317"/>
+      <c r="B33" s="312"/>
+      <c r="C33" s="312"/>
+      <c r="D33" s="312"/>
+      <c r="E33" s="312"/>
+      <c r="F33" s="313"/>
       <c r="G33" s="1"/>
     </row>
     <row r="34" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="323"/>
-      <c r="C34" s="323"/>
-      <c r="D34" s="323"/>
-      <c r="E34" s="323"/>
-      <c r="F34" s="324"/>
+      <c r="B34" s="312"/>
+      <c r="C34" s="312"/>
+      <c r="D34" s="312"/>
+      <c r="E34" s="312"/>
+      <c r="F34" s="313"/>
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="1:7" s="106" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -6889,12 +6889,12 @@
       <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="312"/>
-      <c r="B38" s="313"/>
-      <c r="C38" s="313"/>
-      <c r="D38" s="313"/>
-      <c r="E38" s="313"/>
-      <c r="F38" s="314"/>
+      <c r="A38" s="318"/>
+      <c r="B38" s="319"/>
+      <c r="C38" s="319"/>
+      <c r="D38" s="319"/>
+      <c r="E38" s="319"/>
+      <c r="F38" s="320"/>
       <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7059,12 +7059,12 @@
       <c r="G49" s="1"/>
     </row>
     <row r="50" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="312"/>
-      <c r="B50" s="313"/>
-      <c r="C50" s="313"/>
-      <c r="D50" s="313"/>
-      <c r="E50" s="313"/>
-      <c r="F50" s="314"/>
+      <c r="A50" s="318"/>
+      <c r="B50" s="319"/>
+      <c r="C50" s="319"/>
+      <c r="D50" s="319"/>
+      <c r="E50" s="319"/>
+      <c r="F50" s="320"/>
       <c r="G50" s="1"/>
     </row>
     <row r="51" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7255,14 +7255,14 @@
       <c r="G71" s="1"/>
     </row>
     <row r="72" spans="1:15" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="315" t="s">
+      <c r="A72" s="321" t="s">
         <v>75</v>
       </c>
-      <c r="B72" s="316"/>
-      <c r="C72" s="316"/>
-      <c r="D72" s="316"/>
-      <c r="E72" s="316"/>
-      <c r="F72" s="317"/>
+      <c r="B72" s="322"/>
+      <c r="C72" s="322"/>
+      <c r="D72" s="322"/>
+      <c r="E72" s="322"/>
+      <c r="F72" s="323"/>
       <c r="G72" s="1"/>
     </row>
     <row r="73" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -7332,21 +7332,21 @@
       <c r="G77" s="1"/>
     </row>
     <row r="78" spans="1:15" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="318" t="s">
+      <c r="A78" s="324" t="s">
         <v>68</v>
       </c>
-      <c r="B78" s="320" t="s">
+      <c r="B78" s="326" t="s">
         <v>3</v>
       </c>
-      <c r="C78" s="320"/>
-      <c r="E78" s="321" t="s">
+      <c r="C78" s="326"/>
+      <c r="E78" s="327" t="s">
         <v>4</v>
       </c>
-      <c r="F78" s="322"/>
+      <c r="F78" s="328"/>
       <c r="G78" s="1"/>
     </row>
     <row r="79" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="319"/>
+      <c r="A79" s="325"/>
       <c r="B79" s="52" t="s">
         <v>52</v>
       </c>
@@ -7578,16 +7578,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="E78:F78"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="A72:F72"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="E78:F78"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7618,14 +7618,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="325" t="s">
+      <c r="A1" s="314" t="s">
         <v>185</v>
       </c>
-      <c r="B1" s="325"/>
-      <c r="C1" s="325"/>
-      <c r="D1" s="325"/>
-      <c r="E1" s="325"/>
-      <c r="F1" s="325"/>
+      <c r="B1" s="314"/>
+      <c r="C1" s="314"/>
+      <c r="D1" s="314"/>
+      <c r="E1" s="314"/>
+      <c r="F1" s="314"/>
     </row>
     <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
@@ -7896,10 +7896,10 @@
         <v>33</v>
       </c>
       <c r="B18" s="329"/>
-      <c r="C18" s="321"/>
-      <c r="D18" s="321"/>
-      <c r="E18" s="321"/>
-      <c r="F18" s="322"/>
+      <c r="C18" s="327"/>
+      <c r="D18" s="327"/>
+      <c r="E18" s="327"/>
+      <c r="F18" s="328"/>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -7986,12 +7986,12 @@
       <c r="G22" s="1"/>
     </row>
     <row r="23" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="326"/>
-      <c r="B23" s="327"/>
-      <c r="C23" s="327"/>
-      <c r="D23" s="327"/>
-      <c r="E23" s="327"/>
-      <c r="F23" s="327"/>
+      <c r="A23" s="315"/>
+      <c r="B23" s="316"/>
+      <c r="C23" s="316"/>
+      <c r="D23" s="316"/>
+      <c r="E23" s="316"/>
+      <c r="F23" s="316"/>
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -8019,10 +8019,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="329"/>
-      <c r="C25" s="321"/>
-      <c r="D25" s="321"/>
-      <c r="E25" s="321"/>
-      <c r="F25" s="322"/>
+      <c r="C25" s="327"/>
+      <c r="D25" s="327"/>
+      <c r="E25" s="327"/>
+      <c r="F25" s="328"/>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -8126,23 +8126,23 @@
       <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="328"/>
-      <c r="B31" s="323"/>
-      <c r="C31" s="323"/>
-      <c r="D31" s="323"/>
-      <c r="E31" s="323"/>
-      <c r="F31" s="324"/>
+      <c r="A31" s="317"/>
+      <c r="B31" s="312"/>
+      <c r="C31" s="312"/>
+      <c r="D31" s="312"/>
+      <c r="E31" s="312"/>
+      <c r="F31" s="313"/>
       <c r="G31" s="1"/>
     </row>
     <row r="32" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="323"/>
-      <c r="C32" s="323"/>
-      <c r="D32" s="323"/>
-      <c r="E32" s="323"/>
-      <c r="F32" s="324"/>
+      <c r="B32" s="312"/>
+      <c r="C32" s="312"/>
+      <c r="D32" s="312"/>
+      <c r="E32" s="312"/>
+      <c r="F32" s="313"/>
       <c r="G32" s="1"/>
     </row>
     <row r="33" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -8191,12 +8191,12 @@
       <c r="G35" s="1"/>
     </row>
     <row r="36" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="312"/>
-      <c r="B36" s="313"/>
-      <c r="C36" s="313"/>
-      <c r="D36" s="313"/>
-      <c r="E36" s="313"/>
-      <c r="F36" s="314"/>
+      <c r="A36" s="318"/>
+      <c r="B36" s="319"/>
+      <c r="C36" s="319"/>
+      <c r="D36" s="319"/>
+      <c r="E36" s="319"/>
+      <c r="F36" s="320"/>
       <c r="G36" s="1"/>
     </row>
     <row r="37" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8361,12 +8361,12 @@
       <c r="G47" s="1"/>
     </row>
     <row r="48" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="312"/>
-      <c r="B48" s="313"/>
-      <c r="C48" s="313"/>
-      <c r="D48" s="313"/>
-      <c r="E48" s="313"/>
-      <c r="F48" s="314"/>
+      <c r="A48" s="318"/>
+      <c r="B48" s="319"/>
+      <c r="C48" s="319"/>
+      <c r="D48" s="319"/>
+      <c r="E48" s="319"/>
+      <c r="F48" s="320"/>
       <c r="G48" s="1"/>
     </row>
     <row r="49" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8572,14 +8572,14 @@
       <c r="G69" s="1"/>
     </row>
     <row r="70" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="315" t="s">
+      <c r="A70" s="321" t="s">
         <v>75</v>
       </c>
-      <c r="B70" s="316"/>
-      <c r="C70" s="316"/>
-      <c r="D70" s="316"/>
-      <c r="E70" s="316"/>
-      <c r="F70" s="317"/>
+      <c r="B70" s="322"/>
+      <c r="C70" s="322"/>
+      <c r="D70" s="322"/>
+      <c r="E70" s="322"/>
+      <c r="F70" s="323"/>
       <c r="G70" s="1"/>
     </row>
     <row r="71" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -8655,21 +8655,21 @@
       <c r="G76" s="1"/>
     </row>
     <row r="77" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="318" t="s">
+      <c r="A77" s="324" t="s">
         <v>68</v>
       </c>
-      <c r="B77" s="320" t="s">
+      <c r="B77" s="326" t="s">
         <v>3</v>
       </c>
-      <c r="C77" s="320"/>
-      <c r="E77" s="321" t="s">
+      <c r="C77" s="326"/>
+      <c r="E77" s="327" t="s">
         <v>4</v>
       </c>
-      <c r="F77" s="322"/>
+      <c r="F77" s="328"/>
       <c r="G77" s="1"/>
     </row>
     <row r="78" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="319"/>
+      <c r="A78" s="325"/>
       <c r="B78" s="52" t="s">
         <v>52</v>
       </c>
@@ -8978,18 +8978,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A48:F48"/>
     <mergeCell ref="A70:F70"/>
     <mergeCell ref="A77:A78"/>
     <mergeCell ref="B77:C77"/>
     <mergeCell ref="E77:F77"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="A31:F31"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9017,14 +9017,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="325" t="s">
+      <c r="A1" s="314" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="325"/>
-      <c r="C1" s="325"/>
-      <c r="D1" s="325"/>
-      <c r="E1" s="325"/>
-      <c r="F1" s="325"/>
+      <c r="B1" s="314"/>
+      <c r="C1" s="314"/>
+      <c r="D1" s="314"/>
+      <c r="E1" s="314"/>
+      <c r="F1" s="314"/>
     </row>
     <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
@@ -9272,10 +9272,10 @@
         <v>33</v>
       </c>
       <c r="B16" s="329"/>
-      <c r="C16" s="321"/>
-      <c r="D16" s="321"/>
-      <c r="E16" s="321"/>
-      <c r="F16" s="322"/>
+      <c r="C16" s="327"/>
+      <c r="D16" s="327"/>
+      <c r="E16" s="327"/>
+      <c r="F16" s="328"/>
       <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -9319,12 +9319,12 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="326"/>
-      <c r="B21" s="327"/>
-      <c r="C21" s="327"/>
-      <c r="D21" s="327"/>
-      <c r="E21" s="327"/>
-      <c r="F21" s="327"/>
+      <c r="A21" s="315"/>
+      <c r="B21" s="316"/>
+      <c r="C21" s="316"/>
+      <c r="D21" s="316"/>
+      <c r="E21" s="316"/>
+      <c r="F21" s="316"/>
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -9355,10 +9355,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="329"/>
-      <c r="C23" s="321"/>
-      <c r="D23" s="321"/>
-      <c r="E23" s="321"/>
-      <c r="F23" s="322"/>
+      <c r="C23" s="327"/>
+      <c r="D23" s="327"/>
+      <c r="E23" s="327"/>
+      <c r="F23" s="328"/>
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -9445,23 +9445,23 @@
       <c r="G28" s="1"/>
     </row>
     <row r="29" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="328"/>
-      <c r="B29" s="323"/>
-      <c r="C29" s="323"/>
-      <c r="D29" s="323"/>
-      <c r="E29" s="323"/>
-      <c r="F29" s="324"/>
+      <c r="A29" s="317"/>
+      <c r="B29" s="312"/>
+      <c r="C29" s="312"/>
+      <c r="D29" s="312"/>
+      <c r="E29" s="312"/>
+      <c r="F29" s="313"/>
       <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="323"/>
-      <c r="C30" s="323"/>
-      <c r="D30" s="323"/>
-      <c r="E30" s="323"/>
-      <c r="F30" s="324"/>
+      <c r="B30" s="312"/>
+      <c r="C30" s="312"/>
+      <c r="D30" s="312"/>
+      <c r="E30" s="312"/>
+      <c r="F30" s="313"/>
       <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -9498,12 +9498,12 @@
       <c r="G33" s="1"/>
     </row>
     <row r="34" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="312"/>
-      <c r="B34" s="313"/>
-      <c r="C34" s="313"/>
-      <c r="D34" s="313"/>
-      <c r="E34" s="313"/>
-      <c r="F34" s="314"/>
+      <c r="A34" s="318"/>
+      <c r="B34" s="319"/>
+      <c r="C34" s="319"/>
+      <c r="D34" s="319"/>
+      <c r="E34" s="319"/>
+      <c r="F34" s="320"/>
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -9608,12 +9608,12 @@
       <c r="G41" s="1"/>
     </row>
     <row r="42" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="312"/>
-      <c r="B42" s="313"/>
-      <c r="C42" s="313"/>
-      <c r="D42" s="313"/>
-      <c r="E42" s="313"/>
-      <c r="F42" s="314"/>
+      <c r="A42" s="318"/>
+      <c r="B42" s="319"/>
+      <c r="C42" s="319"/>
+      <c r="D42" s="319"/>
+      <c r="E42" s="319"/>
+      <c r="F42" s="320"/>
       <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -9814,14 +9814,14 @@
       <c r="G63" s="1"/>
     </row>
     <row r="64" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="315" t="s">
+      <c r="A64" s="321" t="s">
         <v>75</v>
       </c>
-      <c r="B64" s="316"/>
-      <c r="C64" s="316"/>
-      <c r="D64" s="316"/>
-      <c r="E64" s="316"/>
-      <c r="F64" s="317"/>
+      <c r="B64" s="322"/>
+      <c r="C64" s="322"/>
+      <c r="D64" s="322"/>
+      <c r="E64" s="322"/>
+      <c r="F64" s="323"/>
       <c r="G64" s="1"/>
     </row>
     <row r="65" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -9897,21 +9897,21 @@
       <c r="G70" s="1"/>
     </row>
     <row r="71" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="318" t="s">
+      <c r="A71" s="324" t="s">
         <v>68</v>
       </c>
-      <c r="B71" s="320" t="s">
+      <c r="B71" s="326" t="s">
         <v>3</v>
       </c>
-      <c r="C71" s="320"/>
-      <c r="E71" s="321" t="s">
+      <c r="C71" s="326"/>
+      <c r="E71" s="327" t="s">
         <v>4</v>
       </c>
-      <c r="F71" s="322"/>
+      <c r="F71" s="328"/>
       <c r="G71" s="1"/>
     </row>
     <row r="72" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="319"/>
+      <c r="A72" s="325"/>
       <c r="B72" s="52" t="s">
         <v>52</v>
       </c>
@@ -10688,11 +10688,11 @@
       <c r="F30" s="1"/>
     </row>
     <row r="31" spans="1:6" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="312"/>
-      <c r="B31" s="313"/>
-      <c r="C31" s="313"/>
-      <c r="D31" s="313"/>
-      <c r="E31" s="314"/>
+      <c r="A31" s="318"/>
+      <c r="B31" s="319"/>
+      <c r="C31" s="319"/>
+      <c r="D31" s="319"/>
+      <c r="E31" s="320"/>
       <c r="F31" s="1"/>
     </row>
     <row r="32" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -10786,11 +10786,11 @@
       <c r="F38" s="1"/>
     </row>
     <row r="39" spans="1:6" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="312"/>
-      <c r="B39" s="313"/>
-      <c r="C39" s="313"/>
-      <c r="D39" s="313"/>
-      <c r="E39" s="314"/>
+      <c r="A39" s="318"/>
+      <c r="B39" s="319"/>
+      <c r="C39" s="319"/>
+      <c r="D39" s="319"/>
+      <c r="E39" s="320"/>
       <c r="F39" s="1"/>
     </row>
     <row r="40" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -10996,13 +10996,13 @@
       <c r="F61" s="1"/>
     </row>
     <row r="62" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="315" t="s">
+      <c r="A62" s="321" t="s">
         <v>124</v>
       </c>
-      <c r="B62" s="316"/>
-      <c r="C62" s="316"/>
-      <c r="D62" s="316"/>
-      <c r="E62" s="317"/>
+      <c r="B62" s="322"/>
+      <c r="C62" s="322"/>
+      <c r="D62" s="322"/>
+      <c r="E62" s="323"/>
       <c r="F62" s="1"/>
     </row>
     <row r="63" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -11080,13 +11080,13 @@
       <c r="F68" s="1"/>
     </row>
     <row r="69" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="318" t="s">
+      <c r="A69" s="324" t="s">
         <v>126</v>
       </c>
-      <c r="B69" s="320" t="s">
+      <c r="B69" s="326" t="s">
         <v>3</v>
       </c>
-      <c r="C69" s="320"/>
+      <c r="C69" s="326"/>
       <c r="D69" s="33" t="s">
         <v>4</v>
       </c>
@@ -11094,7 +11094,7 @@
       <c r="F69" s="1"/>
     </row>
     <row r="70" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="319"/>
+      <c r="A70" s="325"/>
       <c r="B70" s="52" t="s">
         <v>52</v>
       </c>
@@ -11371,34 +11371,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="334">
+      <c r="A1" s="333">
         <v>2017</v>
       </c>
-      <c r="B1" s="335"/>
-      <c r="C1" s="335"/>
-      <c r="D1" s="335"/>
-      <c r="E1" s="335"/>
-      <c r="F1" s="335"/>
-      <c r="G1" s="335"/>
-      <c r="H1" s="335"/>
-      <c r="I1" s="335"/>
-      <c r="J1" s="335"/>
-      <c r="K1" s="336"/>
+      <c r="B1" s="334"/>
+      <c r="C1" s="334"/>
+      <c r="D1" s="334"/>
+      <c r="E1" s="334"/>
+      <c r="F1" s="334"/>
+      <c r="G1" s="334"/>
+      <c r="H1" s="334"/>
+      <c r="I1" s="334"/>
+      <c r="J1" s="334"/>
+      <c r="K1" s="335"/>
     </row>
     <row r="2" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="337" t="s">
+      <c r="A2" s="336" t="s">
         <v>133</v>
       </c>
-      <c r="B2" s="337"/>
-      <c r="C2" s="337"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="337"/>
-      <c r="H2" s="337"/>
-      <c r="I2" s="337"/>
-      <c r="J2" s="337"/>
-      <c r="K2" s="337"/>
+      <c r="B2" s="336"/>
+      <c r="C2" s="336"/>
+      <c r="D2" s="336"/>
+      <c r="E2" s="336"/>
+      <c r="F2" s="336"/>
+      <c r="G2" s="336"/>
+      <c r="H2" s="336"/>
+      <c r="I2" s="336"/>
+      <c r="J2" s="336"/>
+      <c r="K2" s="336"/>
       <c r="L2" s="66"/>
       <c r="M2" s="66"/>
       <c r="N2" s="66"/>
@@ -11422,10 +11422,10 @@
       <c r="E6" s="68">
         <v>0.13420000000000001</v>
       </c>
-      <c r="F6" s="338" t="s">
+      <c r="F6" s="337" t="s">
         <v>136</v>
       </c>
-      <c r="G6" s="338"/>
+      <c r="G6" s="337"/>
       <c r="L6" s="69"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -11438,10 +11438,10 @@
       <c r="E7" s="70">
         <v>0.37</v>
       </c>
-      <c r="F7" s="338" t="s">
+      <c r="F7" s="337" t="s">
         <v>138</v>
       </c>
-      <c r="G7" s="338"/>
+      <c r="G7" s="337"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E8" s="70"/>
@@ -12007,10 +12007,10 @@
       <c r="K52" s="80"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A53" s="333" t="s">
+      <c r="A53" s="338" t="s">
         <v>183</v>
       </c>
-      <c r="B53" s="333"/>
+      <c r="B53" s="338"/>
       <c r="C53" s="82">
         <v>16.73</v>
       </c>
@@ -12115,12 +12115,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="A21:B21"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="A40:D40"/>
@@ -12129,6 +12123,12 @@
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="A21:B21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/web/flask/static/annual_report_template.xlsx
+++ b/web/flask/static/annual_report_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\apps\climberdb\git\web\flask\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D332130-0012-4C53-82F4-290A1EC0F289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A899115-AB0F-403D-9E2A-1E6683002862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2325,7 +2325,6 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2338,10 +2337,78 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2360,87 +2427,18 @@
     <xf numFmtId="0" fontId="19" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2459,6 +2457,39 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2477,39 +2508,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2522,6 +2520,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2537,8 +2538,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2843,24 +2847,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="273" t="s">
+      <c r="A1" s="294" t="s">
         <v>325</v>
       </c>
-      <c r="B1" s="274"/>
-      <c r="C1" s="274"/>
-      <c r="D1" s="274"/>
-      <c r="E1" s="274"/>
-      <c r="F1" s="275"/>
+      <c r="B1" s="295"/>
+      <c r="C1" s="295"/>
+      <c r="D1" s="295"/>
+      <c r="E1" s="295"/>
+      <c r="F1" s="296"/>
     </row>
     <row r="2" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="276" t="s">
+      <c r="A2" s="297" t="s">
         <v>290</v>
       </c>
-      <c r="B2" s="277"/>
-      <c r="C2" s="277"/>
-      <c r="D2" s="277"/>
-      <c r="E2" s="277"/>
-      <c r="F2" s="278"/>
+      <c r="B2" s="298"/>
+      <c r="C2" s="298"/>
+      <c r="D2" s="298"/>
+      <c r="E2" s="298"/>
+      <c r="F2" s="299"/>
     </row>
     <row r="3" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="229" t="s">
@@ -2881,32 +2885,32 @@
       <c r="F4" s="261"/>
     </row>
     <row r="5" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="283"/>
-      <c r="B5" s="284"/>
-      <c r="C5" s="284"/>
+      <c r="A5" s="285"/>
+      <c r="B5" s="286"/>
+      <c r="C5" s="286"/>
       <c r="D5" s="217"/>
       <c r="E5" s="218"/>
       <c r="F5" s="219"/>
     </row>
     <row r="6" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="289" t="s">
+      <c r="A6" s="283" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="290"/>
-      <c r="C6" s="290"/>
+      <c r="B6" s="284"/>
+      <c r="C6" s="284"/>
       <c r="D6" s="220"/>
       <c r="E6" s="221"/>
       <c r="F6" s="221"/>
     </row>
     <row r="7" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="287" t="s">
+      <c r="A7" s="281" t="s">
         <v>291</v>
       </c>
-      <c r="B7" s="288"/>
-      <c r="C7" s="288"/>
-      <c r="D7" s="279"/>
-      <c r="E7" s="280"/>
-      <c r="F7" s="280"/>
+      <c r="B7" s="282"/>
+      <c r="C7" s="282"/>
+      <c r="D7" s="275"/>
+      <c r="E7" s="276"/>
+      <c r="F7" s="276"/>
     </row>
     <row r="8" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="241" t="s">
@@ -2945,19 +2949,19 @@
       <c r="F10" s="18"/>
     </row>
     <row r="11" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="283"/>
-      <c r="B11" s="284"/>
-      <c r="C11" s="284"/>
+      <c r="A11" s="285"/>
+      <c r="B11" s="286"/>
+      <c r="C11" s="286"/>
       <c r="D11" s="210"/>
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
     </row>
     <row r="12" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="286" t="s">
+      <c r="A12" s="302" t="s">
         <v>231</v>
       </c>
-      <c r="B12" s="286"/>
-      <c r="C12" s="286"/>
+      <c r="B12" s="302"/>
+      <c r="C12" s="302"/>
       <c r="D12" s="210"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
@@ -2975,28 +2979,28 @@
     <row r="14" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="257"/>
       <c r="B14" s="242"/>
-      <c r="C14" s="267"/>
+      <c r="C14" s="266"/>
       <c r="D14" s="208"/>
       <c r="E14" s="199"/>
       <c r="F14" s="51"/>
     </row>
     <row r="15" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="283"/>
-      <c r="B15" s="284"/>
-      <c r="C15" s="284"/>
+      <c r="A15" s="285"/>
+      <c r="B15" s="286"/>
+      <c r="C15" s="286"/>
       <c r="D15" s="223"/>
       <c r="E15" s="224"/>
       <c r="F15" s="224"/>
     </row>
     <row r="16" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="287" t="s">
+      <c r="A16" s="281" t="s">
         <v>296</v>
       </c>
-      <c r="B16" s="291"/>
-      <c r="C16" s="291"/>
-      <c r="D16" s="279"/>
-      <c r="E16" s="280"/>
-      <c r="F16" s="280"/>
+      <c r="B16" s="303"/>
+      <c r="C16" s="303"/>
+      <c r="D16" s="275"/>
+      <c r="E16" s="276"/>
+      <c r="F16" s="276"/>
     </row>
     <row r="17" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="241" t="s">
@@ -3035,19 +3039,19 @@
       <c r="F19" s="18"/>
     </row>
     <row r="20" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="283"/>
-      <c r="B20" s="284"/>
-      <c r="C20" s="284"/>
+      <c r="A20" s="285"/>
+      <c r="B20" s="286"/>
+      <c r="C20" s="286"/>
       <c r="D20" s="207"/>
       <c r="E20" s="51"/>
       <c r="F20" s="201"/>
     </row>
     <row r="21" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="286" t="s">
+      <c r="A21" s="302" t="s">
         <v>298</v>
       </c>
-      <c r="B21" s="286"/>
-      <c r="C21" s="286"/>
+      <c r="B21" s="302"/>
+      <c r="C21" s="302"/>
       <c r="D21" s="207"/>
       <c r="E21" s="18"/>
       <c r="F21" s="18"/>
@@ -3071,9 +3075,9 @@
       <c r="F23" s="203"/>
     </row>
     <row r="24" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="283"/>
-      <c r="B24" s="284"/>
-      <c r="C24" s="285"/>
+      <c r="A24" s="285"/>
+      <c r="B24" s="286"/>
+      <c r="C24" s="287"/>
       <c r="D24" s="207"/>
       <c r="E24" s="204"/>
       <c r="F24" s="203"/>
@@ -3081,11 +3085,11 @@
       <c r="L24" s="18"/>
     </row>
     <row r="25" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="287" t="s">
+      <c r="A25" s="281" t="s">
         <v>297</v>
       </c>
-      <c r="B25" s="288"/>
-      <c r="C25" s="288"/>
+      <c r="B25" s="282"/>
+      <c r="C25" s="282"/>
       <c r="D25" s="223"/>
       <c r="E25" s="224"/>
       <c r="F25" s="224"/>
@@ -3121,19 +3125,19 @@
       <c r="F27" s="227"/>
     </row>
     <row r="28" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="283"/>
-      <c r="B28" s="284"/>
-      <c r="C28" s="284"/>
+      <c r="A28" s="285"/>
+      <c r="B28" s="286"/>
+      <c r="C28" s="286"/>
       <c r="D28" s="207"/>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
     </row>
     <row r="29" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="289" t="s">
+      <c r="A29" s="283" t="s">
         <v>300</v>
       </c>
-      <c r="B29" s="290"/>
-      <c r="C29" s="290"/>
+      <c r="B29" s="284"/>
+      <c r="C29" s="284"/>
       <c r="D29" s="205"/>
       <c r="E29" s="37"/>
       <c r="F29" s="37"/>
@@ -3157,19 +3161,19 @@
       <c r="F31" s="37"/>
     </row>
     <row r="32" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="284"/>
-      <c r="B32" s="284"/>
-      <c r="C32" s="285"/>
+      <c r="A32" s="286"/>
+      <c r="B32" s="286"/>
+      <c r="C32" s="287"/>
       <c r="D32" s="207"/>
       <c r="E32" s="18"/>
       <c r="F32" s="18"/>
     </row>
     <row r="33" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="289" t="s">
+      <c r="A33" s="283" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="290"/>
-      <c r="C33" s="290"/>
+      <c r="B33" s="284"/>
+      <c r="C33" s="284"/>
       <c r="D33" s="205"/>
       <c r="E33" s="37"/>
       <c r="F33" s="37"/>
@@ -3185,18 +3189,18 @@
       <c r="F34" s="37"/>
     </row>
     <row r="35" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="300"/>
-      <c r="B35" s="301"/>
-      <c r="C35" s="302"/>
+      <c r="A35" s="288"/>
+      <c r="B35" s="289"/>
+      <c r="C35" s="290"/>
       <c r="D35" s="208"/>
       <c r="F35" s="209"/>
     </row>
     <row r="36" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="281" t="s">
+      <c r="A36" s="300" t="s">
         <v>301</v>
       </c>
-      <c r="B36" s="282"/>
-      <c r="C36" s="282"/>
+      <c r="B36" s="301"/>
+      <c r="C36" s="301"/>
       <c r="D36" s="208"/>
     </row>
     <row r="37" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -3208,26 +3212,26 @@
       <c r="D37" s="208"/>
     </row>
     <row r="38" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="303"/>
-      <c r="B38" s="304"/>
-      <c r="C38" s="305"/>
+      <c r="A38" s="291"/>
+      <c r="B38" s="292"/>
+      <c r="C38" s="293"/>
       <c r="D38" s="208"/>
       <c r="F38" s="209"/>
     </row>
     <row r="39" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="281" t="s">
+      <c r="A39" s="300" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="282"/>
-      <c r="C39" s="282"/>
+      <c r="B39" s="301"/>
+      <c r="C39" s="301"/>
       <c r="D39" s="208"/>
       <c r="F39" s="209"/>
     </row>
     <row r="40" spans="1:6" s="216" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="296" t="s">
+      <c r="A40" s="277" t="s">
         <v>74</v>
       </c>
-      <c r="B40" s="297"/>
+      <c r="B40" s="278"/>
       <c r="C40" s="235"/>
       <c r="D40" s="211"/>
       <c r="F40" s="212"/>
@@ -3241,10 +3245,10 @@
       <c r="D41" s="208"/>
     </row>
     <row r="42" spans="1:6" s="216" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="296" t="s">
+      <c r="A42" s="277" t="s">
         <v>75</v>
       </c>
-      <c r="B42" s="297"/>
+      <c r="B42" s="278"/>
       <c r="C42" s="236"/>
       <c r="D42" s="213"/>
       <c r="E42" s="228"/>
@@ -3261,30 +3265,30 @@
       <c r="F43" s="198"/>
     </row>
     <row r="44" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="283"/>
-      <c r="B44" s="284"/>
-      <c r="C44" s="285"/>
+      <c r="A44" s="285"/>
+      <c r="B44" s="286"/>
+      <c r="C44" s="287"/>
       <c r="D44" s="207"/>
       <c r="E44" s="18"/>
       <c r="F44" s="198"/>
     </row>
     <row r="45" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="298" t="s">
+      <c r="A45" s="279" t="s">
         <v>324</v>
       </c>
-      <c r="B45" s="299"/>
-      <c r="C45" s="299"/>
-      <c r="D45" s="299"/>
+      <c r="B45" s="280"/>
+      <c r="C45" s="280"/>
+      <c r="D45" s="280"/>
       <c r="E45" s="207"/>
       <c r="F45" s="198"/>
     </row>
     <row r="46" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="135"/>
-      <c r="B46" s="292" t="s">
+      <c r="B46" s="271" t="s">
         <v>317</v>
       </c>
-      <c r="C46" s="293"/>
-      <c r="D46" s="293"/>
+      <c r="C46" s="272"/>
+      <c r="D46" s="272"/>
       <c r="E46" s="208"/>
       <c r="F46"/>
     </row>
@@ -3308,7 +3312,7 @@
       <c r="A48" s="196"/>
       <c r="B48" s="197"/>
       <c r="C48" s="249"/>
-      <c r="D48" s="266"/>
+      <c r="D48" s="337"/>
       <c r="E48" s="207"/>
       <c r="F48" s="201"/>
     </row>
@@ -3322,11 +3326,11 @@
     </row>
     <row r="50" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="253"/>
-      <c r="B50" s="294" t="s">
+      <c r="B50" s="273" t="s">
         <v>4</v>
       </c>
-      <c r="C50" s="295"/>
-      <c r="D50" s="295"/>
+      <c r="C50" s="274"/>
+      <c r="D50" s="274"/>
       <c r="E50" s="206"/>
       <c r="F50" s="28"/>
       <c r="J50" s="202"/>
@@ -3349,10 +3353,10 @@
       <c r="J51" s="202"/>
     </row>
     <row r="52" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="268"/>
-      <c r="B52" s="269"/>
-      <c r="C52" s="270"/>
-      <c r="D52" s="271"/>
+      <c r="A52" s="267"/>
+      <c r="B52" s="268"/>
+      <c r="C52" s="269"/>
+      <c r="D52" s="338"/>
       <c r="E52" s="206"/>
       <c r="F52" s="28"/>
       <c r="J52" s="202"/>
@@ -3385,8 +3389,8 @@
       <c r="A56" s="18"/>
       <c r="B56" s="122"/>
       <c r="C56" s="37"/>
-      <c r="D56" s="272"/>
-      <c r="E56" s="272"/>
+      <c r="D56" s="270"/>
+      <c r="E56" s="270"/>
       <c r="F56" s="214"/>
     </row>
     <row r="57" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3401,19 +3405,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A44:C44"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="D7:F7"/>
@@ -3430,6 +3421,19 @@
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A21:C21"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A44:C44"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup scale="69" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -3455,14 +3459,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="309" t="s">
+      <c r="A1" s="307" t="s">
         <v>288</v>
       </c>
-      <c r="B1" s="309"/>
-      <c r="C1" s="309"/>
-      <c r="D1" s="309"/>
-      <c r="E1" s="309"/>
-      <c r="F1" s="309"/>
+      <c r="B1" s="307"/>
+      <c r="C1" s="307"/>
+      <c r="D1" s="307"/>
+      <c r="E1" s="307"/>
+      <c r="F1" s="307"/>
     </row>
     <row r="2" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="128"/>
@@ -3867,12 +3871,12 @@
       <c r="P25" s="18"/>
     </row>
     <row r="26" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="310"/>
-      <c r="B26" s="310"/>
-      <c r="C26" s="310"/>
-      <c r="D26" s="310"/>
-      <c r="E26" s="310"/>
-      <c r="F26" s="310"/>
+      <c r="A26" s="308"/>
+      <c r="B26" s="308"/>
+      <c r="C26" s="308"/>
+      <c r="D26" s="308"/>
+      <c r="E26" s="308"/>
+      <c r="F26" s="308"/>
     </row>
     <row r="27" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="135" t="s">
@@ -3966,11 +3970,11 @@
       <c r="A34" s="157" t="s">
         <v>238</v>
       </c>
-      <c r="B34" s="310"/>
-      <c r="C34" s="310"/>
-      <c r="D34" s="310"/>
-      <c r="E34" s="310"/>
-      <c r="F34" s="310"/>
+      <c r="B34" s="308"/>
+      <c r="C34" s="308"/>
+      <c r="D34" s="308"/>
+      <c r="E34" s="308"/>
+      <c r="F34" s="308"/>
       <c r="K34" s="29"/>
       <c r="L34" s="18"/>
     </row>
@@ -4101,12 +4105,12 @@
       <c r="AU38" s="106"/>
     </row>
     <row r="39" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="311"/>
-      <c r="B39" s="311"/>
-      <c r="C39" s="311"/>
-      <c r="D39" s="311"/>
-      <c r="E39" s="311"/>
-      <c r="F39" s="311"/>
+      <c r="A39" s="309"/>
+      <c r="B39" s="309"/>
+      <c r="C39" s="309"/>
+      <c r="D39" s="309"/>
+      <c r="E39" s="309"/>
+      <c r="F39" s="309"/>
     </row>
     <row r="40" spans="1:47" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="165" t="s">
@@ -4260,12 +4264,12 @@
       <c r="F50" s="139"/>
     </row>
     <row r="51" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="311"/>
-      <c r="B51" s="311"/>
-      <c r="C51" s="311"/>
-      <c r="D51" s="311"/>
-      <c r="E51" s="311"/>
-      <c r="F51" s="311"/>
+      <c r="A51" s="309"/>
+      <c r="B51" s="309"/>
+      <c r="C51" s="309"/>
+      <c r="D51" s="309"/>
+      <c r="E51" s="309"/>
+      <c r="F51" s="309"/>
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="132" t="s">
@@ -4502,14 +4506,14 @@
       <c r="AU74" s="29"/>
     </row>
     <row r="75" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="306" t="s">
+      <c r="A75" s="304" t="s">
         <v>75</v>
       </c>
-      <c r="B75" s="306"/>
-      <c r="C75" s="306"/>
-      <c r="D75" s="306"/>
-      <c r="E75" s="306"/>
-      <c r="F75" s="306"/>
+      <c r="B75" s="304"/>
+      <c r="C75" s="304"/>
+      <c r="D75" s="304"/>
+      <c r="E75" s="304"/>
+      <c r="F75" s="304"/>
     </row>
     <row r="76" spans="1:47" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="143" t="s">
@@ -4566,20 +4570,20 @@
       <c r="F80" s="177"/>
     </row>
     <row r="81" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="306" t="s">
+      <c r="A81" s="304" t="s">
         <v>68</v>
       </c>
-      <c r="B81" s="307" t="s">
+      <c r="B81" s="305" t="s">
         <v>3</v>
       </c>
-      <c r="C81" s="307"/>
-      <c r="E81" s="308" t="s">
+      <c r="C81" s="305"/>
+      <c r="E81" s="306" t="s">
         <v>4</v>
       </c>
-      <c r="F81" s="308"/>
+      <c r="F81" s="306"/>
     </row>
     <row r="82" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="306"/>
+      <c r="A82" s="304"/>
       <c r="B82" s="149" t="s">
         <v>52</v>
       </c>
@@ -4895,14 +4899,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="309" t="s">
+      <c r="A1" s="307" t="s">
         <v>235</v>
       </c>
-      <c r="B1" s="309"/>
-      <c r="C1" s="309"/>
-      <c r="D1" s="309"/>
-      <c r="E1" s="309"/>
-      <c r="F1" s="309"/>
+      <c r="B1" s="307"/>
+      <c r="C1" s="307"/>
+      <c r="D1" s="307"/>
+      <c r="E1" s="307"/>
+      <c r="F1" s="307"/>
     </row>
     <row r="2" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="128"/>
@@ -5296,12 +5300,12 @@
       <c r="F25" s="156"/>
     </row>
     <row r="26" spans="1:16" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="310"/>
-      <c r="B26" s="310"/>
-      <c r="C26" s="310"/>
-      <c r="D26" s="310"/>
-      <c r="E26" s="310"/>
-      <c r="F26" s="310"/>
+      <c r="A26" s="308"/>
+      <c r="B26" s="308"/>
+      <c r="C26" s="308"/>
+      <c r="D26" s="308"/>
+      <c r="E26" s="308"/>
+      <c r="F26" s="308"/>
     </row>
     <row r="27" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="135" t="s">
@@ -5402,11 +5406,11 @@
       <c r="A34" s="157" t="s">
         <v>238</v>
       </c>
-      <c r="B34" s="310"/>
-      <c r="C34" s="310"/>
-      <c r="D34" s="310"/>
-      <c r="E34" s="310"/>
-      <c r="F34" s="310"/>
+      <c r="B34" s="308"/>
+      <c r="C34" s="308"/>
+      <c r="D34" s="308"/>
+      <c r="E34" s="308"/>
+      <c r="F34" s="308"/>
     </row>
     <row r="35" spans="1:47" ht="0.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="157"/>
@@ -5531,12 +5535,12 @@
       <c r="F38" s="164"/>
     </row>
     <row r="39" spans="1:47" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="311"/>
-      <c r="B39" s="311"/>
-      <c r="C39" s="311"/>
-      <c r="D39" s="311"/>
-      <c r="E39" s="311"/>
-      <c r="F39" s="311"/>
+      <c r="A39" s="309"/>
+      <c r="B39" s="309"/>
+      <c r="C39" s="309"/>
+      <c r="D39" s="309"/>
+      <c r="E39" s="309"/>
+      <c r="F39" s="309"/>
     </row>
     <row r="40" spans="1:47" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="165" t="s">
@@ -5689,12 +5693,12 @@
       <c r="F50" s="139"/>
     </row>
     <row r="51" spans="1:6" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="311"/>
-      <c r="B51" s="311"/>
-      <c r="C51" s="311"/>
-      <c r="D51" s="311"/>
-      <c r="E51" s="311"/>
-      <c r="F51" s="311"/>
+      <c r="A51" s="309"/>
+      <c r="B51" s="309"/>
+      <c r="C51" s="309"/>
+      <c r="D51" s="309"/>
+      <c r="E51" s="309"/>
+      <c r="F51" s="309"/>
     </row>
     <row r="52" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="132" t="s">
@@ -5984,14 +5988,14 @@
       <c r="F74" s="140"/>
     </row>
     <row r="75" spans="1:47" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="306" t="s">
+      <c r="A75" s="304" t="s">
         <v>75</v>
       </c>
-      <c r="B75" s="306"/>
-      <c r="C75" s="306"/>
-      <c r="D75" s="306"/>
-      <c r="E75" s="306"/>
-      <c r="F75" s="306"/>
+      <c r="B75" s="304"/>
+      <c r="C75" s="304"/>
+      <c r="D75" s="304"/>
+      <c r="E75" s="304"/>
+      <c r="F75" s="304"/>
     </row>
     <row r="76" spans="1:47" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="176">
@@ -6048,20 +6052,20 @@
       <c r="F80" s="177"/>
     </row>
     <row r="81" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="306" t="s">
+      <c r="A81" s="304" t="s">
         <v>68</v>
       </c>
-      <c r="B81" s="307" t="s">
+      <c r="B81" s="305" t="s">
         <v>3</v>
       </c>
-      <c r="C81" s="307"/>
-      <c r="E81" s="308" t="s">
+      <c r="C81" s="305"/>
+      <c r="E81" s="306" t="s">
         <v>4</v>
       </c>
-      <c r="F81" s="308"/>
+      <c r="F81" s="306"/>
     </row>
     <row r="82" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="306"/>
+      <c r="A82" s="304"/>
       <c r="B82" s="149" t="s">
         <v>52</v>
       </c>
@@ -6323,14 +6327,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="314" t="s">
+      <c r="A1" s="323" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="314"/>
-      <c r="C1" s="314"/>
-      <c r="D1" s="314"/>
-      <c r="E1" s="314"/>
-      <c r="F1" s="314"/>
+      <c r="B1" s="323"/>
+      <c r="C1" s="323"/>
+      <c r="D1" s="323"/>
+      <c r="E1" s="323"/>
+      <c r="F1" s="323"/>
     </row>
     <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
@@ -6746,12 +6750,12 @@
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="315"/>
-      <c r="B26" s="316"/>
-      <c r="C26" s="316"/>
-      <c r="D26" s="316"/>
-      <c r="E26" s="316"/>
-      <c r="F26" s="316"/>
+      <c r="A26" s="324"/>
+      <c r="B26" s="325"/>
+      <c r="C26" s="325"/>
+      <c r="D26" s="325"/>
+      <c r="E26" s="325"/>
+      <c r="F26" s="325"/>
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -6834,23 +6838,23 @@
       <c r="G32" s="1"/>
     </row>
     <row r="33" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="317"/>
-      <c r="B33" s="312"/>
-      <c r="C33" s="312"/>
-      <c r="D33" s="312"/>
-      <c r="E33" s="312"/>
-      <c r="F33" s="313"/>
+      <c r="A33" s="326"/>
+      <c r="B33" s="321"/>
+      <c r="C33" s="321"/>
+      <c r="D33" s="321"/>
+      <c r="E33" s="321"/>
+      <c r="F33" s="322"/>
       <c r="G33" s="1"/>
     </row>
     <row r="34" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="312"/>
-      <c r="C34" s="312"/>
-      <c r="D34" s="312"/>
-      <c r="E34" s="312"/>
-      <c r="F34" s="313"/>
+      <c r="B34" s="321"/>
+      <c r="C34" s="321"/>
+      <c r="D34" s="321"/>
+      <c r="E34" s="321"/>
+      <c r="F34" s="322"/>
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="1:7" s="106" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -6889,12 +6893,12 @@
       <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="318"/>
-      <c r="B38" s="319"/>
-      <c r="C38" s="319"/>
-      <c r="D38" s="319"/>
-      <c r="E38" s="319"/>
-      <c r="F38" s="320"/>
+      <c r="A38" s="310"/>
+      <c r="B38" s="311"/>
+      <c r="C38" s="311"/>
+      <c r="D38" s="311"/>
+      <c r="E38" s="311"/>
+      <c r="F38" s="312"/>
       <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7059,12 +7063,12 @@
       <c r="G49" s="1"/>
     </row>
     <row r="50" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="318"/>
-      <c r="B50" s="319"/>
-      <c r="C50" s="319"/>
-      <c r="D50" s="319"/>
-      <c r="E50" s="319"/>
-      <c r="F50" s="320"/>
+      <c r="A50" s="310"/>
+      <c r="B50" s="311"/>
+      <c r="C50" s="311"/>
+      <c r="D50" s="311"/>
+      <c r="E50" s="311"/>
+      <c r="F50" s="312"/>
       <c r="G50" s="1"/>
     </row>
     <row r="51" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7255,14 +7259,14 @@
       <c r="G71" s="1"/>
     </row>
     <row r="72" spans="1:15" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="321" t="s">
+      <c r="A72" s="313" t="s">
         <v>75</v>
       </c>
-      <c r="B72" s="322"/>
-      <c r="C72" s="322"/>
-      <c r="D72" s="322"/>
-      <c r="E72" s="322"/>
-      <c r="F72" s="323"/>
+      <c r="B72" s="314"/>
+      <c r="C72" s="314"/>
+      <c r="D72" s="314"/>
+      <c r="E72" s="314"/>
+      <c r="F72" s="315"/>
       <c r="G72" s="1"/>
     </row>
     <row r="73" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -7332,21 +7336,21 @@
       <c r="G77" s="1"/>
     </row>
     <row r="78" spans="1:15" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="324" t="s">
+      <c r="A78" s="316" t="s">
         <v>68</v>
       </c>
-      <c r="B78" s="326" t="s">
+      <c r="B78" s="318" t="s">
         <v>3</v>
       </c>
-      <c r="C78" s="326"/>
-      <c r="E78" s="327" t="s">
+      <c r="C78" s="318"/>
+      <c r="E78" s="319" t="s">
         <v>4</v>
       </c>
-      <c r="F78" s="328"/>
+      <c r="F78" s="320"/>
       <c r="G78" s="1"/>
     </row>
     <row r="79" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="325"/>
+      <c r="A79" s="317"/>
       <c r="B79" s="52" t="s">
         <v>52</v>
       </c>
@@ -7578,16 +7582,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A50:F50"/>
     <mergeCell ref="A72:F72"/>
     <mergeCell ref="A78:A79"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="E78:F78"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A38:F38"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7618,14 +7622,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="314" t="s">
+      <c r="A1" s="323" t="s">
         <v>185</v>
       </c>
-      <c r="B1" s="314"/>
-      <c r="C1" s="314"/>
-      <c r="D1" s="314"/>
-      <c r="E1" s="314"/>
-      <c r="F1" s="314"/>
+      <c r="B1" s="323"/>
+      <c r="C1" s="323"/>
+      <c r="D1" s="323"/>
+      <c r="E1" s="323"/>
+      <c r="F1" s="323"/>
     </row>
     <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
@@ -7895,11 +7899,11 @@
       <c r="A18" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="329"/>
-      <c r="C18" s="327"/>
-      <c r="D18" s="327"/>
-      <c r="E18" s="327"/>
-      <c r="F18" s="328"/>
+      <c r="B18" s="327"/>
+      <c r="C18" s="319"/>
+      <c r="D18" s="319"/>
+      <c r="E18" s="319"/>
+      <c r="F18" s="320"/>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -7986,12 +7990,12 @@
       <c r="G22" s="1"/>
     </row>
     <row r="23" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="315"/>
-      <c r="B23" s="316"/>
-      <c r="C23" s="316"/>
-      <c r="D23" s="316"/>
-      <c r="E23" s="316"/>
-      <c r="F23" s="316"/>
+      <c r="A23" s="324"/>
+      <c r="B23" s="325"/>
+      <c r="C23" s="325"/>
+      <c r="D23" s="325"/>
+      <c r="E23" s="325"/>
+      <c r="F23" s="325"/>
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -8018,11 +8022,11 @@
       <c r="A25" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="329"/>
-      <c r="C25" s="327"/>
-      <c r="D25" s="327"/>
-      <c r="E25" s="327"/>
-      <c r="F25" s="328"/>
+      <c r="B25" s="327"/>
+      <c r="C25" s="319"/>
+      <c r="D25" s="319"/>
+      <c r="E25" s="319"/>
+      <c r="F25" s="320"/>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -8126,23 +8130,23 @@
       <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="317"/>
-      <c r="B31" s="312"/>
-      <c r="C31" s="312"/>
-      <c r="D31" s="312"/>
-      <c r="E31" s="312"/>
-      <c r="F31" s="313"/>
+      <c r="A31" s="326"/>
+      <c r="B31" s="321"/>
+      <c r="C31" s="321"/>
+      <c r="D31" s="321"/>
+      <c r="E31" s="321"/>
+      <c r="F31" s="322"/>
       <c r="G31" s="1"/>
     </row>
     <row r="32" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="312"/>
-      <c r="C32" s="312"/>
-      <c r="D32" s="312"/>
-      <c r="E32" s="312"/>
-      <c r="F32" s="313"/>
+      <c r="B32" s="321"/>
+      <c r="C32" s="321"/>
+      <c r="D32" s="321"/>
+      <c r="E32" s="321"/>
+      <c r="F32" s="322"/>
       <c r="G32" s="1"/>
     </row>
     <row r="33" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -8191,12 +8195,12 @@
       <c r="G35" s="1"/>
     </row>
     <row r="36" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="318"/>
-      <c r="B36" s="319"/>
-      <c r="C36" s="319"/>
-      <c r="D36" s="319"/>
-      <c r="E36" s="319"/>
-      <c r="F36" s="320"/>
+      <c r="A36" s="310"/>
+      <c r="B36" s="311"/>
+      <c r="C36" s="311"/>
+      <c r="D36" s="311"/>
+      <c r="E36" s="311"/>
+      <c r="F36" s="312"/>
       <c r="G36" s="1"/>
     </row>
     <row r="37" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8361,12 +8365,12 @@
       <c r="G47" s="1"/>
     </row>
     <row r="48" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="318"/>
-      <c r="B48" s="319"/>
-      <c r="C48" s="319"/>
-      <c r="D48" s="319"/>
-      <c r="E48" s="319"/>
-      <c r="F48" s="320"/>
+      <c r="A48" s="310"/>
+      <c r="B48" s="311"/>
+      <c r="C48" s="311"/>
+      <c r="D48" s="311"/>
+      <c r="E48" s="311"/>
+      <c r="F48" s="312"/>
       <c r="G48" s="1"/>
     </row>
     <row r="49" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8572,14 +8576,14 @@
       <c r="G69" s="1"/>
     </row>
     <row r="70" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="321" t="s">
+      <c r="A70" s="313" t="s">
         <v>75</v>
       </c>
-      <c r="B70" s="322"/>
-      <c r="C70" s="322"/>
-      <c r="D70" s="322"/>
-      <c r="E70" s="322"/>
-      <c r="F70" s="323"/>
+      <c r="B70" s="314"/>
+      <c r="C70" s="314"/>
+      <c r="D70" s="314"/>
+      <c r="E70" s="314"/>
+      <c r="F70" s="315"/>
       <c r="G70" s="1"/>
     </row>
     <row r="71" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -8655,21 +8659,21 @@
       <c r="G76" s="1"/>
     </row>
     <row r="77" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="324" t="s">
+      <c r="A77" s="316" t="s">
         <v>68</v>
       </c>
-      <c r="B77" s="326" t="s">
+      <c r="B77" s="318" t="s">
         <v>3</v>
       </c>
-      <c r="C77" s="326"/>
-      <c r="E77" s="327" t="s">
+      <c r="C77" s="318"/>
+      <c r="E77" s="319" t="s">
         <v>4</v>
       </c>
-      <c r="F77" s="328"/>
+      <c r="F77" s="320"/>
       <c r="G77" s="1"/>
     </row>
     <row r="78" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="325"/>
+      <c r="A78" s="317"/>
       <c r="B78" s="52" t="s">
         <v>52</v>
       </c>
@@ -8978,18 +8982,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="E77:F77"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A70:F70"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="E77:F77"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9017,14 +9021,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="314" t="s">
+      <c r="A1" s="323" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="314"/>
-      <c r="C1" s="314"/>
-      <c r="D1" s="314"/>
-      <c r="E1" s="314"/>
-      <c r="F1" s="314"/>
+      <c r="B1" s="323"/>
+      <c r="C1" s="323"/>
+      <c r="D1" s="323"/>
+      <c r="E1" s="323"/>
+      <c r="F1" s="323"/>
     </row>
     <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
@@ -9271,11 +9275,11 @@
       <c r="A16" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="329"/>
-      <c r="C16" s="327"/>
-      <c r="D16" s="327"/>
-      <c r="E16" s="327"/>
-      <c r="F16" s="328"/>
+      <c r="B16" s="327"/>
+      <c r="C16" s="319"/>
+      <c r="D16" s="319"/>
+      <c r="E16" s="319"/>
+      <c r="F16" s="320"/>
       <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -9319,12 +9323,12 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="315"/>
-      <c r="B21" s="316"/>
-      <c r="C21" s="316"/>
-      <c r="D21" s="316"/>
-      <c r="E21" s="316"/>
-      <c r="F21" s="316"/>
+      <c r="A21" s="324"/>
+      <c r="B21" s="325"/>
+      <c r="C21" s="325"/>
+      <c r="D21" s="325"/>
+      <c r="E21" s="325"/>
+      <c r="F21" s="325"/>
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -9354,11 +9358,11 @@
       <c r="A23" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="329"/>
-      <c r="C23" s="327"/>
-      <c r="D23" s="327"/>
-      <c r="E23" s="327"/>
-      <c r="F23" s="328"/>
+      <c r="B23" s="327"/>
+      <c r="C23" s="319"/>
+      <c r="D23" s="319"/>
+      <c r="E23" s="319"/>
+      <c r="F23" s="320"/>
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -9445,23 +9449,23 @@
       <c r="G28" s="1"/>
     </row>
     <row r="29" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="317"/>
-      <c r="B29" s="312"/>
-      <c r="C29" s="312"/>
-      <c r="D29" s="312"/>
-      <c r="E29" s="312"/>
-      <c r="F29" s="313"/>
+      <c r="A29" s="326"/>
+      <c r="B29" s="321"/>
+      <c r="C29" s="321"/>
+      <c r="D29" s="321"/>
+      <c r="E29" s="321"/>
+      <c r="F29" s="322"/>
       <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="312"/>
-      <c r="C30" s="312"/>
-      <c r="D30" s="312"/>
-      <c r="E30" s="312"/>
-      <c r="F30" s="313"/>
+      <c r="B30" s="321"/>
+      <c r="C30" s="321"/>
+      <c r="D30" s="321"/>
+      <c r="E30" s="321"/>
+      <c r="F30" s="322"/>
       <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -9498,12 +9502,12 @@
       <c r="G33" s="1"/>
     </row>
     <row r="34" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="318"/>
-      <c r="B34" s="319"/>
-      <c r="C34" s="319"/>
-      <c r="D34" s="319"/>
-      <c r="E34" s="319"/>
-      <c r="F34" s="320"/>
+      <c r="A34" s="310"/>
+      <c r="B34" s="311"/>
+      <c r="C34" s="311"/>
+      <c r="D34" s="311"/>
+      <c r="E34" s="311"/>
+      <c r="F34" s="312"/>
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -9608,12 +9612,12 @@
       <c r="G41" s="1"/>
     </row>
     <row r="42" spans="1:7" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="318"/>
-      <c r="B42" s="319"/>
-      <c r="C42" s="319"/>
-      <c r="D42" s="319"/>
-      <c r="E42" s="319"/>
-      <c r="F42" s="320"/>
+      <c r="A42" s="310"/>
+      <c r="B42" s="311"/>
+      <c r="C42" s="311"/>
+      <c r="D42" s="311"/>
+      <c r="E42" s="311"/>
+      <c r="F42" s="312"/>
       <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -9814,14 +9818,14 @@
       <c r="G63" s="1"/>
     </row>
     <row r="64" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="321" t="s">
+      <c r="A64" s="313" t="s">
         <v>75</v>
       </c>
-      <c r="B64" s="322"/>
-      <c r="C64" s="322"/>
-      <c r="D64" s="322"/>
-      <c r="E64" s="322"/>
-      <c r="F64" s="323"/>
+      <c r="B64" s="314"/>
+      <c r="C64" s="314"/>
+      <c r="D64" s="314"/>
+      <c r="E64" s="314"/>
+      <c r="F64" s="315"/>
       <c r="G64" s="1"/>
     </row>
     <row r="65" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -9897,21 +9901,21 @@
       <c r="G70" s="1"/>
     </row>
     <row r="71" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="324" t="s">
+      <c r="A71" s="316" t="s">
         <v>68</v>
       </c>
-      <c r="B71" s="326" t="s">
+      <c r="B71" s="318" t="s">
         <v>3</v>
       </c>
-      <c r="C71" s="326"/>
-      <c r="E71" s="327" t="s">
+      <c r="C71" s="318"/>
+      <c r="E71" s="319" t="s">
         <v>4</v>
       </c>
-      <c r="F71" s="328"/>
+      <c r="F71" s="320"/>
       <c r="G71" s="1"/>
     </row>
     <row r="72" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="325"/>
+      <c r="A72" s="317"/>
       <c r="B72" s="52" t="s">
         <v>52</v>
       </c>
@@ -10229,13 +10233,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="330" t="s">
+      <c r="A1" s="328" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="330"/>
-      <c r="C1" s="330"/>
-      <c r="D1" s="330"/>
-      <c r="E1" s="330"/>
+      <c r="B1" s="328"/>
+      <c r="C1" s="328"/>
+      <c r="D1" s="328"/>
+      <c r="E1" s="328"/>
     </row>
     <row r="2" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
@@ -10443,13 +10447,13 @@
       <c r="F14" s="1"/>
     </row>
     <row r="15" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="331" t="s">
+      <c r="A15" s="329" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="331"/>
-      <c r="C15" s="331"/>
-      <c r="D15" s="331"/>
-      <c r="E15" s="331"/>
+      <c r="B15" s="329"/>
+      <c r="C15" s="329"/>
+      <c r="D15" s="329"/>
+      <c r="E15" s="329"/>
       <c r="F15" s="1"/>
     </row>
     <row r="16" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -10530,13 +10534,13 @@
       <c r="F19" s="1"/>
     </row>
     <row r="20" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="331" t="s">
+      <c r="A20" s="329" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="331"/>
-      <c r="C20" s="331"/>
-      <c r="D20" s="331"/>
-      <c r="E20" s="331"/>
+      <c r="B20" s="329"/>
+      <c r="C20" s="329"/>
+      <c r="D20" s="329"/>
+      <c r="E20" s="329"/>
       <c r="F20" s="1"/>
     </row>
     <row r="21" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -10688,11 +10692,11 @@
       <c r="F30" s="1"/>
     </row>
     <row r="31" spans="1:6" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="318"/>
-      <c r="B31" s="319"/>
-      <c r="C31" s="319"/>
-      <c r="D31" s="319"/>
-      <c r="E31" s="320"/>
+      <c r="A31" s="310"/>
+      <c r="B31" s="311"/>
+      <c r="C31" s="311"/>
+      <c r="D31" s="311"/>
+      <c r="E31" s="312"/>
       <c r="F31" s="1"/>
     </row>
     <row r="32" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -10786,11 +10790,11 @@
       <c r="F38" s="1"/>
     </row>
     <row r="39" spans="1:6" ht="10" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="318"/>
-      <c r="B39" s="319"/>
-      <c r="C39" s="319"/>
-      <c r="D39" s="319"/>
-      <c r="E39" s="320"/>
+      <c r="A39" s="310"/>
+      <c r="B39" s="311"/>
+      <c r="C39" s="311"/>
+      <c r="D39" s="311"/>
+      <c r="E39" s="312"/>
       <c r="F39" s="1"/>
     </row>
     <row r="40" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -10996,13 +11000,13 @@
       <c r="F61" s="1"/>
     </row>
     <row r="62" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="321" t="s">
+      <c r="A62" s="313" t="s">
         <v>124</v>
       </c>
-      <c r="B62" s="322"/>
-      <c r="C62" s="322"/>
-      <c r="D62" s="322"/>
-      <c r="E62" s="323"/>
+      <c r="B62" s="314"/>
+      <c r="C62" s="314"/>
+      <c r="D62" s="314"/>
+      <c r="E62" s="315"/>
       <c r="F62" s="1"/>
     </row>
     <row r="63" spans="1:6" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -11080,13 +11084,13 @@
       <c r="F68" s="1"/>
     </row>
     <row r="69" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="324" t="s">
+      <c r="A69" s="316" t="s">
         <v>126</v>
       </c>
-      <c r="B69" s="326" t="s">
+      <c r="B69" s="318" t="s">
         <v>3</v>
       </c>
-      <c r="C69" s="326"/>
+      <c r="C69" s="318"/>
       <c r="D69" s="33" t="s">
         <v>4</v>
       </c>
@@ -11094,7 +11098,7 @@
       <c r="F69" s="1"/>
     </row>
     <row r="70" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="325"/>
+      <c r="A70" s="317"/>
       <c r="B70" s="52" t="s">
         <v>52</v>
       </c>
@@ -11371,34 +11375,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="333">
+      <c r="A1" s="332">
         <v>2017</v>
       </c>
-      <c r="B1" s="334"/>
-      <c r="C1" s="334"/>
-      <c r="D1" s="334"/>
-      <c r="E1" s="334"/>
-      <c r="F1" s="334"/>
-      <c r="G1" s="334"/>
-      <c r="H1" s="334"/>
-      <c r="I1" s="334"/>
-      <c r="J1" s="334"/>
-      <c r="K1" s="335"/>
+      <c r="B1" s="333"/>
+      <c r="C1" s="333"/>
+      <c r="D1" s="333"/>
+      <c r="E1" s="333"/>
+      <c r="F1" s="333"/>
+      <c r="G1" s="333"/>
+      <c r="H1" s="333"/>
+      <c r="I1" s="333"/>
+      <c r="J1" s="333"/>
+      <c r="K1" s="334"/>
     </row>
     <row r="2" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="336" t="s">
+      <c r="A2" s="335" t="s">
         <v>133</v>
       </c>
-      <c r="B2" s="336"/>
-      <c r="C2" s="336"/>
-      <c r="D2" s="336"/>
-      <c r="E2" s="336"/>
-      <c r="F2" s="336"/>
-      <c r="G2" s="336"/>
-      <c r="H2" s="336"/>
-      <c r="I2" s="336"/>
-      <c r="J2" s="336"/>
-      <c r="K2" s="336"/>
+      <c r="B2" s="335"/>
+      <c r="C2" s="335"/>
+      <c r="D2" s="335"/>
+      <c r="E2" s="335"/>
+      <c r="F2" s="335"/>
+      <c r="G2" s="335"/>
+      <c r="H2" s="335"/>
+      <c r="I2" s="335"/>
+      <c r="J2" s="335"/>
+      <c r="K2" s="335"/>
       <c r="L2" s="66"/>
       <c r="M2" s="66"/>
       <c r="N2" s="66"/>
@@ -11422,10 +11426,10 @@
       <c r="E6" s="68">
         <v>0.13420000000000001</v>
       </c>
-      <c r="F6" s="337" t="s">
+      <c r="F6" s="336" t="s">
         <v>136</v>
       </c>
-      <c r="G6" s="337"/>
+      <c r="G6" s="336"/>
       <c r="L6" s="69"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -11438,10 +11442,10 @@
       <c r="E7" s="70">
         <v>0.37</v>
       </c>
-      <c r="F7" s="337" t="s">
+      <c r="F7" s="336" t="s">
         <v>138</v>
       </c>
-      <c r="G7" s="337"/>
+      <c r="G7" s="336"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E8" s="70"/>
@@ -11652,10 +11656,10 @@
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="332" t="s">
+      <c r="A21" s="330" t="s">
         <v>159</v>
       </c>
-      <c r="B21" s="332"/>
+      <c r="B21" s="330"/>
       <c r="F21" s="29"/>
       <c r="K21" s="23"/>
     </row>
@@ -11808,10 +11812,10 @@
       <c r="P33" s="23"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A34" s="332" t="s">
+      <c r="A34" s="330" t="s">
         <v>169</v>
       </c>
-      <c r="B34" s="332"/>
+      <c r="B34" s="330"/>
       <c r="K34" s="79"/>
       <c r="P34" s="23"/>
     </row>
@@ -11860,12 +11864,12 @@
       <c r="G39" s="80"/>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A40" s="332" t="s">
+      <c r="A40" s="330" t="s">
         <v>174</v>
       </c>
-      <c r="B40" s="332"/>
-      <c r="C40" s="332"/>
-      <c r="D40" s="332"/>
+      <c r="B40" s="330"/>
+      <c r="C40" s="330"/>
+      <c r="D40" s="330"/>
       <c r="E40" s="28"/>
       <c r="G40" s="80"/>
       <c r="I40" s="80"/>
@@ -11888,10 +11892,10 @@
       <c r="K42" s="80"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A43" s="332" t="s">
+      <c r="A43" s="330" t="s">
         <v>175</v>
       </c>
-      <c r="B43" s="332"/>
+      <c r="B43" s="330"/>
       <c r="C43" s="18">
         <v>39</v>
       </c>
@@ -11903,10 +11907,10 @@
       <c r="K43" s="80"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A44" s="332" t="s">
+      <c r="A44" s="330" t="s">
         <v>177</v>
       </c>
-      <c r="B44" s="332"/>
+      <c r="B44" s="330"/>
       <c r="C44" s="18">
         <v>11</v>
       </c>
@@ -11918,10 +11922,10 @@
       <c r="K44" s="80"/>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A45" s="332" t="s">
+      <c r="A45" s="330" t="s">
         <v>178</v>
       </c>
-      <c r="B45" s="332"/>
+      <c r="B45" s="330"/>
       <c r="C45" s="18">
         <v>16</v>
       </c>
@@ -11933,10 +11937,10 @@
       <c r="K45" s="80"/>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A46" s="332" t="s">
+      <c r="A46" s="330" t="s">
         <v>179</v>
       </c>
-      <c r="B46" s="332"/>
+      <c r="B46" s="330"/>
       <c r="C46" s="18">
         <v>73</v>
       </c>
@@ -11948,10 +11952,10 @@
       <c r="K46" s="80"/>
     </row>
     <row r="47" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="332" t="s">
+      <c r="A47" s="330" t="s">
         <v>180</v>
       </c>
-      <c r="B47" s="332"/>
+      <c r="B47" s="330"/>
       <c r="C47" s="18">
         <v>71</v>
       </c>
@@ -11978,10 +11982,10 @@
       <c r="K49" s="80"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="332" t="s">
+      <c r="A50" s="330" t="s">
         <v>181</v>
       </c>
-      <c r="B50" s="332"/>
+      <c r="B50" s="330"/>
       <c r="C50" s="18">
         <v>17.399999999999999</v>
       </c>
@@ -12007,10 +12011,10 @@
       <c r="K52" s="80"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A53" s="338" t="s">
+      <c r="A53" s="331" t="s">
         <v>183</v>
       </c>
-      <c r="B53" s="338"/>
+      <c r="B53" s="331"/>
       <c r="C53" s="82">
         <v>16.73</v>
       </c>
@@ -12115,6 +12119,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="A21:B21"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="A40:D40"/>
@@ -12123,12 +12133,6 @@
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="A21:B21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
